--- a/FOA Singles/Accent-Single.xlsx
+++ b/FOA Singles/Accent-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,7 +854,7 @@
 ABBEY 4' 9" X 6' 9" Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Nylon, it is finished in Alphabet or Multi tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Alphabet or Multi&lt;br&gt;
+Color: Alphabet or Multi or Sports or Solar System&lt;br&gt;
 Weight: 9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -941,7 +941,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -995,10 +995,10 @@
       <c r="G3" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ABBEY 4' 9" X 6' 9" Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Alphabet or Multi tones, the Nylon build balances durability with visual appeal.&lt;br&gt;
+ABBEY 4' 9" X 6' 9" Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Nylon, it is finished in Alphabet or Multi tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Alphabet or Multi&lt;br&gt;
+Color: Alphabet or Multi or Sports or Solar System&lt;br&gt;
 Weight: 9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1139,10 +1139,10 @@
       <c r="G4" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ABBEY 4' 9" X 6' 9" Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Nylon construction is complemented by Sports tones for a polished look.&lt;br&gt;
+ABBEY 4' 9" X 6' 9" Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Nylon, it is finished in Alphabet or Multi tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Sports&lt;br&gt;
+Color: Alphabet or Multi or Sports or Solar System&lt;br&gt;
 Weight: 9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
@@ -1283,10 +1283,10 @@
       <c r="G5" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with ABBEY 4' 9" X 6' 9" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Nylon and Solar System tones, it blends structure and softness in one clean profile.&lt;br&gt;
+ABBEY 4' 9" X 6' 9" Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Nylon, it is finished in Alphabet or Multi tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Solar System&lt;br&gt;
+Color: Alphabet or Multi or Sports or Solar System&lt;br&gt;
 Weight: 9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -1430,7 +1430,7 @@
 ABBEY 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Nylon, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Red or Multi or Us Map&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
@@ -1571,10 +1571,10 @@
       <c r="G7" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ABBEY 5' X 8' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Multi tones, the Nylon build balances durability with visual appeal.&lt;br&gt;
+ABBEY 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Nylon, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Red or Multi or Us Map&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
@@ -1715,10 +1715,10 @@
       <c r="G8" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ABBEY 5' X 8' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Nylon construction is complemented by Multi tones for a polished look.&lt;br&gt;
+ABBEY 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Nylon, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Red or Multi or Us Map&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -1859,10 +1859,10 @@
       <c r="G9" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with ABBEY 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Nylon and Us Map tones, it blends structure and softness in one clean profile.&lt;br&gt;
+ABBEY 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Nylon, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
-Color: Us Map&lt;br&gt;
+Color: Red or Multi or Us Map&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -2429,7 +2429,7 @@
       <c r="G13" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-AMOS 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Nylon, it is finished in Multi tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with AMOS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Nylon and Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Nylon.&lt;br&gt;
 Color: Multi&lt;br&gt;
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
@@ -2575,8 +2575,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ANNMARIE 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
-&lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Beige&lt;br&gt;
+&lt;p&gt;Materials: Polyester or 100% Polyester.&lt;br&gt;
+Color: Beige or Navy or Silver or White&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
@@ -2717,10 +2717,10 @@
       <c r="G15" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ANNMARIE 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Navy tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+ANNMARIE 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
-&lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Navy&lt;br&gt;
+&lt;p&gt;Materials: Polyester or 100% Polyester.&lt;br&gt;
+Color: Beige or Navy or Silver or White&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
@@ -2861,10 +2861,10 @@
       <c r="G16" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ANNMARIE 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The 100% Polyester construction is complemented by Silver tones for a polished look.&lt;br&gt;
+ANNMARIE 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
-&lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Silver&lt;br&gt;
+&lt;p&gt;Materials: Polyester or 100% Polyester.&lt;br&gt;
+Color: Beige or Navy or Silver or White&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
@@ -3005,10 +3005,10 @@
       <c r="G17" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with ANNMARIE 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Polyester and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+ANNMARIE 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
-&lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Polyester or 100% Polyester.&lt;br&gt;
+Color: Beige or Navy or Silver or White&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
@@ -3152,7 +3152,7 @@
 ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Scarlet tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Scarlet&lt;br&gt;
+Color: Scarlet or Yellow or Teal or Purple or Blue or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
@@ -3293,10 +3293,10 @@
       <c r="G19" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ANNMARIE 5' X 8' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Yellow tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Scarlet tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Yellow&lt;br&gt;
+Color: Scarlet or Yellow or Teal or Purple or Blue or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
@@ -3437,10 +3437,10 @@
       <c r="G20" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ANNMARIE 5' X 8' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Teal tones for a polished look.&lt;br&gt;
+ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Scarlet tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Teal&lt;br&gt;
+Color: Scarlet or Yellow or Teal or Purple or Blue or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
@@ -3581,10 +3581,10 @@
       <c r="G21" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with ANNMARIE 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Purple tones, it blends structure and softness in one clean profile.&lt;br&gt;
+ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Scarlet tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Purple&lt;br&gt;
+Color: Scarlet or Yellow or Teal or Purple or Blue or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
@@ -3725,10 +3725,10 @@
       <c r="G22" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Blue tones that pair easily with surrounding decor.&lt;br&gt;
+ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Scarlet tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Scarlet or Yellow or Teal or Purple or Blue or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
@@ -3869,10 +3869,10 @@
       <c r="G23" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ANNMARIE 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+ANNMARIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Scarlet tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Scarlet or Yellow or Teal or Purple or Blue or Black&lt;br&gt;
 Weight: 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
@@ -4016,7 +4016,7 @@
 BLITAR 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Dark Gray or Brown or Black or Brown&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -4157,10 +4157,10 @@
       <c r="G25" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BLITAR 5' X 7' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Brown or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+BLITAR 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Brown or Black&lt;br&gt;
+Color: Dark Gray or Brown or Black or Brown&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
@@ -4301,10 +4301,10 @@
       <c r="G26" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BLITAR 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Polyester construction is complemented by Brown tones for a polished look.&lt;br&gt;
+BLITAR 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Brown&lt;br&gt;
+Color: Dark Gray or Brown or Black or Brown&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
@@ -4448,7 +4448,7 @@
 Make the room feel complete with CALEDON 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray tones, the Polypropylene build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polypropylene.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Gray or Gray or Red&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
@@ -4589,10 +4589,10 @@
       <c r="G28" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CALEDON 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polypropylene construction is complemented by Gray or Red tones for a polished look.&lt;br&gt;
+Make the room feel complete with CALEDON 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray tones, the Polypropylene build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polypropylene.&lt;br&gt;
-Color: Gray or Red&lt;br&gt;
+Color: Gray or Gray or Red&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -4734,9 +4734,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 5.3' X 7.6'&lt;/p&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
@@ -4877,10 +4877,10 @@
       <c r="G30" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from 100% Polyester, it is finished in Charcoal tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 5.3' X 7.6'&lt;/p&gt;
+Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Charcoal&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
@@ -5021,10 +5021,10 @@
       <c r="G31" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CAPARICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Blush tones, the 100% Polyester build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 5.3' X 7.6'&lt;/p&gt;
+Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Blush&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
@@ -5165,10 +5165,10 @@
       <c r="G32" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The 100% Polyester construction is complemented by Silver tones for a polished look.&lt;br&gt;
-Product Dimensions: 5.3' X 7.6'&lt;/p&gt;
+Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
@@ -5309,10 +5309,10 @@
       <c r="G33" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With 100% Polyester and Off-White tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 5.3' X 7.6'&lt;/p&gt;
+Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Off-White&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -5457,10 +5457,10 @@
       <c r="G34" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Gold tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 5.3’ X 7.6’&lt;/p&gt;
+Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Gold&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
@@ -5601,10 +5601,10 @@
       <c r="G35" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CAPARICA 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Teal tones, the 100% Polyester build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 5.3’ X 7.6’&lt;/p&gt;
+Elevate your space with CAPARICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With 100% Polyester and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 5.3' X 7.6' / 5.3’ X 7.6’&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Teal&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5691,7 +5691,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
@@ -5748,7 +5748,7 @@
 Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Tie-Dye Beige tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5’ X 7’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Tie-Dye Beige&lt;br&gt;
+Color: Tie-Dye Beige or Tie-Dye Gray or Tie-Dye Purple or Off-White or Pink or Gray&lt;br&gt;
 Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
@@ -5889,10 +5889,10 @@
       <c r="G37" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FAMALICA 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Polyester construction is complemented by Tie-Dye Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Tie-Dye Beige tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5’ X 7’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Tie-Dye Gray&lt;br&gt;
+Color: Tie-Dye Beige or Tie-Dye Gray or Tie-Dye Purple or Off-White or Pink or Gray&lt;br&gt;
 Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
@@ -6033,10 +6033,10 @@
       <c r="G38" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with FAMALICA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Polyester and Tie-Dye Purple tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Tie-Dye Beige tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5’ X 7’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Tie-Dye Purple&lt;br&gt;
+Color: Tie-Dye Beige or Tie-Dye Gray or Tie-Dye Purple or Off-White or Pink or Gray&lt;br&gt;
 Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
@@ -6177,10 +6177,10 @@
       <c r="G39" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FAMALICA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Off-White tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Tie-Dye Beige tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5’ X 7’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Off-White&lt;br&gt;
+Color: Tie-Dye Beige or Tie-Dye Gray or Tie-Dye Purple or Off-White or Pink or Gray&lt;br&gt;
 Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
@@ -6321,10 +6321,10 @@
       <c r="G40" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Pink tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Tie-Dye Beige tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5’ X 7’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Pink&lt;br&gt;
+Color: Tie-Dye Beige or Tie-Dye Gray or Tie-Dye Purple or Off-White or Pink or Gray&lt;br&gt;
 Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
@@ -6465,10 +6465,10 @@
       <c r="G41" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FAMALICA 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with FAMALICA 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Tie-Dye Beige tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5’ X 7’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Tie-Dye Beige or Tie-Dye Gray or Tie-Dye Purple or Off-White or Pink or Gray&lt;br&gt;
 Weight: 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6555,7 +6555,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
@@ -6612,7 +6612,7 @@
 Make the room feel complete with FERMONT 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Gray or Brown Beige&lt;br&gt;
 Weight: 30 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6699,7 +6699,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
@@ -6753,10 +6753,10 @@
       <c r="G43" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FERMONT 5' X 8' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Polyester construction is complemented by Brown Beige tones for a polished look.&lt;br&gt;
+Make the room feel complete with FERMONT 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Brown Beige&lt;br&gt;
+Color: Gray or Brown Beige&lt;br&gt;
 Weight: 30 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -6843,7 +6843,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
@@ -7041,7 +7041,7 @@
 HEPSIBA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Ogee Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5'4"WX 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Ogee Beige&lt;br&gt;
+Color: Ogee Beige or Drop Taupe or Drop Wine or Dune Sienna or Diamond Taupe&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -7182,10 +7182,10 @@
       <c r="G46" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HEPSIBA 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Drop Taupe tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+HEPSIBA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Ogee Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5'4"WX 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Drop Taupe&lt;br&gt;
+Color: Ogee Beige or Drop Taupe or Drop Wine or Dune Sienna or Diamond Taupe&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
@@ -7326,10 +7326,10 @@
       <c r="G47" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HEPSIBA 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Drop Wine tones for a polished look.&lt;br&gt;
+HEPSIBA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Ogee Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5'4"WX 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Drop Wine&lt;br&gt;
+Color: Ogee Beige or Drop Taupe or Drop Wine or Dune Sienna or Diamond Taupe&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -7470,10 +7470,10 @@
       <c r="G48" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HEPSIBA 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Dune Sienna tones, it blends structure and softness in one clean profile.&lt;br&gt;
+HEPSIBA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Ogee Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5'4"WX 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Dune Sienna&lt;br&gt;
+Color: Ogee Beige or Drop Taupe or Drop Wine or Dune Sienna or Diamond Taupe&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
@@ -7614,10 +7614,10 @@
       <c r="G49" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HEPSIBA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Diamond Taupe tones that pair easily with surrounding decor.&lt;br&gt;
+HEPSIBA 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Ogee Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5'4"WX 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Diamond Taupe&lt;br&gt;
+Color: Ogee Beige or Drop Taupe or Drop Wine or Dune Sienna or Diamond Taupe&lt;br&gt;
 Weight: 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -7761,7 +7761,7 @@
 HOLLIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Gold or Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5’ X 8’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gold or Gray&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
@@ -7902,10 +7902,10 @@
       <c r="G51" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HOLLIE 5' X 8' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Blue or Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+HOLLIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Gold or Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5’ X 8’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue or Gray&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -8046,10 +8046,10 @@
       <c r="G52" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOLLIE 5' X 8' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Multi tones for a polished look.&lt;br&gt;
+HOLLIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Gold or Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5’ X 8’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
@@ -8190,10 +8190,10 @@
       <c r="G53" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HOLLIE 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
+HOLLIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Gold or Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5’ X 8’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -8334,10 +8334,10 @@
       <c r="G54" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOLLIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Multi tones that pair easily with surrounding decor.&lt;br&gt;
+HOLLIE 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Gold or Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5’ X 8’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -8481,7 +8481,7 @@
 Make the room feel complete with HOLLIE 8' X 10' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gold or Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8’ X10’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gold or Gray&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -8622,10 +8622,10 @@
       <c r="G56" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOLLIE 8' X 10' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Polyester construction is complemented by Blue or Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with HOLLIE 8' X 10' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gold or Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8’ X10’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue or Gray&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
@@ -8766,10 +8766,10 @@
       <c r="G57" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with HOLLIE 8' X 10' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with HOLLIE 8' X 10' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gold or Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8’ X10’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -8910,10 +8910,10 @@
       <c r="G58" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOLLIE 8' X 10' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Multi tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with HOLLIE 8' X 10' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gold or Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8’ X10’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
@@ -9054,10 +9054,10 @@
       <c r="G59" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with HOLLIE 8' X 10' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Multi tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with HOLLIE 8' X 10' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gold or Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8’ X10’&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Gold or Gray or Blue or Gray or Multi&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -9201,7 +9201,7 @@
 Make the room feel complete with KOZLU 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Beige tones, the Polypropylene build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5.3' X 7.4'&lt;/p&gt;
 &lt;p&gt;Materials: Polypropylene.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Gray or Beige or Dark Gray&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
@@ -9342,10 +9342,10 @@
       <c r="G61" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KOZLU 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Polypropylene construction is complemented by Gray or Beige tones for a polished look.&lt;br&gt;
+Make the room feel complete with KOZLU 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Beige tones, the Polypropylene build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5.3' X 7.4'&lt;/p&gt;
 &lt;p&gt;Materials: Polypropylene.&lt;br&gt;
-Color: Gray or Beige&lt;br&gt;
+Color: Beige or Gray or Beige or Dark Gray&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -9486,10 +9486,10 @@
       <c r="G62" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with KOZLU 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Polypropylene and Dark Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with KOZLU 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Beige tones, the Polypropylene build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5.3' X 7.4'&lt;/p&gt;
 &lt;p&gt;Materials: Polypropylene.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Beige or Gray or Beige or Dark Gray&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -9774,7 +9774,7 @@
 Make the room feel complete with MONTIJO 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Distressed Multi&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 23 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
@@ -9915,10 +9915,10 @@
       <c r="G65" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MONTIJO 5' X 8' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Recycled Polyester construction is complemented by Mediterranean Multi tones for a polished look.&lt;br&gt;
+Make the room feel complete with MONTIJO 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Mediterranean Multi&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 23 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -10059,10 +10059,10 @@
       <c r="G66" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with MONTIJO 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Concrete Umber tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with MONTIJO 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Concrete Umber&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 23 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10149,7 +10149,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
@@ -10203,10 +10203,10 @@
       <c r="G67" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MONTIJO 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Recycled Polyester, it is finished in Weave Multi tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with MONTIJO 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Weave Multi&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 23 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -10350,7 +10350,7 @@
 Make the room feel complete with MONTIJO 8' X 11' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Distressed Multi&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
@@ -10491,10 +10491,10 @@
       <c r="G69" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MONTIJO 8' X 11' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Recycled Polyester construction is complemented by Mediterranean Multi tones for a polished look.&lt;br&gt;
+Make the room feel complete with MONTIJO 8' X 11' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Mediterranean Multi&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -10635,10 +10635,10 @@
       <c r="G70" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with MONTIJO 8' X 11' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Recycled Polyester and Concrete Umber tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with MONTIJO 8' X 11' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Concrete Umber&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10725,7 +10725,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
@@ -10779,10 +10779,10 @@
       <c r="G71" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MONTIJO 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Recycled Polyester, it is finished in Weave Multi tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with MONTIJO 8' X 11' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Distressed Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Weave Multi&lt;br&gt;
+Color: Distressed Multi or Mediterranean Multi or Concrete Umber or Weave Multi&lt;br&gt;
 Weight: 55 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -10869,7 +10869,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
@@ -11067,7 +11067,7 @@
 NIKSAR 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Red tones for a polished look.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Red or Turquoise or Gray or Purple&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
@@ -11208,10 +11208,10 @@
       <c r="G74" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with NIKSAR 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Turquoise tones, it blends structure and softness in one clean profile.&lt;br&gt;
+NIKSAR 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Red tones for a polished look.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Turquoise&lt;br&gt;
+Color: Red or Turquoise or Gray or Purple&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11298,7 +11298,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
@@ -11352,10 +11352,10 @@
       <c r="G75" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-NIKSAR 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Gray or Purple tones that pair easily with surrounding decor.&lt;br&gt;
+NIKSAR 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Red tones for a polished look.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Purple&lt;br&gt;
+Color: Red or Turquoise or Gray or Purple&lt;br&gt;
 Weight: 20 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -11499,7 +11499,7 @@
 PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Blue or Multi or Multi or Red&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
@@ -11640,10 +11640,10 @@
       <c r="G77" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with PAYAS 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Blue or Multi tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue or Multi&lt;br&gt;
+Color: Beige or Blue or Multi or Multi or Red&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -11784,10 +11784,10 @@
       <c r="G78" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PAYAS 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Blue or Multi tones for a polished look.&lt;br&gt;
+PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue or Multi&lt;br&gt;
+Color: Beige or Blue or Multi or Multi or Red&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
@@ -11928,10 +11928,10 @@
       <c r="G79" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with PAYAS 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
+PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Beige or Blue or Multi or Multi or Red&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -12072,10 +12072,10 @@
       <c r="G80" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Multi tones that pair easily with surrounding decor.&lt;br&gt;
+PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Beige or Blue or Multi or Multi or Red&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12162,7 +12162,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
@@ -12216,10 +12216,10 @@
       <c r="G81" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with PAYAS 5' X 7' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Red tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+PAYAS 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Beige or Blue or Multi or Multi or Red&lt;br&gt;
 Weight: 15 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
@@ -12363,7 +12363,7 @@
 SERANG 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Gray or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Black&lt;br&gt;
+Color: Gray or Black or Gray or Red&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
@@ -12504,10 +12504,10 @@
       <c r="G83" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SERANG 5' X 7' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+SERANG 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Gray or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Black&lt;br&gt;
+Color: Gray or Black or Gray or Red&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
@@ -12648,10 +12648,10 @@
       <c r="G84" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SERANG 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Polyester construction is complemented by Gray or Red tones for a polished look.&lt;br&gt;
+SERANG 5' X 7' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Gray or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Red&lt;br&gt;
+Color: Gray or Black or Gray or Red&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
@@ -12936,7 +12936,7 @@
 SHINTA 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Burgundy tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Burgundy&lt;br&gt;
+Color: Burgundy or Red&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
@@ -13077,10 +13077,10 @@
       <c r="G87" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SHINTA 5' X 8' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Red tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+SHINTA 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Burgundy tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 8'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Burgundy or Red&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13167,7 +13167,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -13224,7 +13224,7 @@
 Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Gray or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'2"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Black&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -13365,10 +13365,10 @@
       <c r="G89" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SIVAS 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Polyester, it is finished in Gray or Red tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Gray or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'2"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Red&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
@@ -13509,10 +13509,10 @@
       <c r="G90" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SIVAS 5' X 8' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Gray or Blue tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Gray or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'2"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Blue&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
@@ -13653,10 +13653,10 @@
       <c r="G91" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SIVAS 5' X 8' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Polyester construction is complemented by Gray or Black tones for a polished look.&lt;br&gt;
+Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Gray or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'2"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Black&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
@@ -13797,10 +13797,10 @@
       <c r="G92" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Polyester and Charcoal Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Gray or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'2"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Charcoal Blue&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -13887,7 +13887,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
@@ -13941,10 +13941,10 @@
       <c r="G93" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SIVAS 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Polyester, it is finished in Charcoal Yellow tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with SIVAS 5' X 8' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Polyester and Gray or Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5' X 7'2"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Charcoal Yellow&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
@@ -14088,7 +14088,7 @@
 Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 7'9" X 10'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Black&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
@@ -14229,10 +14229,10 @@
       <c r="G95" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SIVAS 8' X 10' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Gray or Red tones for a polished look.&lt;br&gt;
+Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 7'9" X 10'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Red&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14319,7 +14319,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -14373,10 +14373,10 @@
       <c r="G96" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SIVAS 8' X 10' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Gray or Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 7'9" X 10'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Blue&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr">
@@ -14517,10 +14517,10 @@
       <c r="G97" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SIVAS 8' X 10' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Gray or Black tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 7'9" X 10'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Black&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -14661,10 +14661,10 @@
       <c r="G98" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Charcoal Blue tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 7'9" X 10'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Charcoal Blue&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr">
@@ -14805,10 +14805,10 @@
       <c r="G99" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SIVAS 8' X 10' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Polyester construction is complemented by Charcoal Yellow tones for a polished look.&lt;br&gt;
+Make the room feel complete with SIVAS 8' X 10' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Black tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 7'9" X 10'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Charcoal Yellow&lt;br&gt;
+Color: Gray or Black or Gray or Red or Gray or Blue or Charcoal Blue or Charcoal Yellow&lt;br&gt;
 Weight: 34 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -14895,7 +14895,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -14952,8 +14952,8 @@
 Make the room feel complete with VANCOUVER 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Navy tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Navy&lt;br&gt;
-Weight: 30 lbs&lt;/p&gt;</t>
+Color: Gray or Navy or Black or Gray or Red or Earth&lt;br&gt;
+Weight: 30 or 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H100" s="68" t="inlineStr">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD100" t="inlineStr">
@@ -15093,11 +15093,11 @@
       <c r="G101" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VANCOUVER 5' X 7' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Polyester construction is complemented by Black or Gray or Red tones for a polished look.&lt;br&gt;
+Make the room feel complete with VANCOUVER 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Navy tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Black or Gray or Red&lt;br&gt;
-Weight: 30 lbs&lt;/p&gt;</t>
+Color: Gray or Navy or Black or Gray or Red or Earth&lt;br&gt;
+Weight: 30 or 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H101" s="68" t="inlineStr">
@@ -15183,7 +15183,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -15237,11 +15237,11 @@
       <c r="G102" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with VANCOUVER 5' X 7' Area Rug, styled in Contemporary and designed for everyday comfort. This accent rug is made to fit naturally into the room. With Polyester and Earth tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with VANCOUVER 5' X 7' Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Gray or Navy tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Earth&lt;br&gt;
-Weight: 27 lbs&lt;/p&gt;</t>
+Color: Gray or Navy or Black or Gray or Red or Earth&lt;br&gt;
+Weight: 30 or 27 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H102" s="68" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -15384,8 +15384,8 @@
 VANCOUVER 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Gray or Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray or Beige&lt;br&gt;
-Weight: 30 lbs&lt;/p&gt;</t>
+Color: Gray or Beige or Gray&lt;br&gt;
+Weight: 30 or 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H103" s="39" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -15525,11 +15525,11 @@
       <c r="G104" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with VANCOUVER 5' X 8' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Gray tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+VANCOUVER 5' X 8' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Gray or Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 5' X 7'&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 38 lbs&lt;/p&gt;</t>
+Color: Gray or Beige or Gray&lt;br&gt;
+Weight: 30 or 38 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H104" s="39" t="inlineStr">
@@ -15615,7 +15615,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -15672,7 +15672,7 @@
 Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Doppler Teal&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -15813,10 +15813,10 @@
       <c r="G106" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 5'3 X 7'6" Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Recycled Polyester, it is finished in Spice Rose tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Spice Rose&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -15957,10 +15957,10 @@
       <c r="G107" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with WILHELM 5'3 X 7'6" Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Indigo Breach tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Indigo Breach&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16047,7 +16047,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -16101,10 +16101,10 @@
       <c r="G108" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 5'3 X 7'6" Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Recycled Polyester construction is complemented by Concrete Lapis tones for a polished look.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Concrete Lapis&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16191,7 +16191,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -16245,10 +16245,10 @@
       <c r="G109" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Recycled Polyester and Abstract Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Abstract Multi&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16335,7 +16335,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -16389,10 +16389,10 @@
       <c r="G110" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 5'3 X 7'6" Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Recycled Polyester, it is finished in Relic Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Relic Beige&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr">
@@ -16533,10 +16533,10 @@
       <c r="G111" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with WILHELM 5'3 X 7'6" Area Rug and its Contemporary character. Built as a accent rug, it pairs well with a wide range of interiors. Finished in Obelisk Gray tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Obelisk Gray&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16623,7 +16623,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -16677,10 +16677,10 @@
       <c r="G112" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 5'3 X 7'6" Area Rug brings a Contemporary look to your home with a refined, comfortable feel. As a accent rug, it is designed to complement your space. The Recycled Polyester construction is complemented by Palmette Multi tones for a polished look.&lt;br&gt;
+Elevate your space with WILHELM 5'3 X 7'6" Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Doppler Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 5'3" X 7'6"&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Palmette Multi&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 21.84 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -16965,7 +16965,7 @@
 WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Doppler Teal&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr">
@@ -17106,10 +17106,10 @@
       <c r="G115" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with WILHELM 8' X 11' Area Rug and its Contemporary character. As a accent rug, it is designed to complement your space. Finished in Spice Rose tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Spice Rose&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -17250,10 +17250,10 @@
       <c r="G116" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 8' X 11' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. This accent rug is made to fit naturally into the room. The Recycled Polyester construction is complemented by Indigo Breach tones for a polished look.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Indigo Breach&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr">
@@ -17394,10 +17394,10 @@
       <c r="G117" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with WILHELM 8' X 11' Area Rug, styled in Contemporary and designed for everyday comfort. Built as a accent rug, it pairs well with a wide range of interiors. With Recycled Polyester and Concrete Lapis tones, it blends structure and softness in one clean profile.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Concrete Lapis&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17484,7 +17484,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -17538,10 +17538,10 @@
       <c r="G118" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent rug, it is designed to complement your space. Crafted from Recycled Polyester, it is finished in Abstract Multi tones that pair easily with surrounding decor.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Abstract Multi&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17628,7 +17628,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr">
@@ -17682,10 +17682,10 @@
       <c r="G119" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with WILHELM 8' X 11' Area Rug and its Contemporary character. This accent rug is made to fit naturally into the room. Finished in Chroma Multi tones, the Recycled Polyester build balances durability with visual appeal.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Chroma Multi&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17772,7 +17772,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -17826,10 +17826,10 @@
       <c r="G120" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 8' X 11' Area Rug brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent rug, it pairs well with a wide range of interiors. The Recycled Polyester construction is complemented by Relic Beige tones for a polished look.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Relic Beige&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -17970,10 +17970,10 @@
       <c r="G121" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with WILHELM 8' X 11' Area Rug, styled in Contemporary and designed for everyday comfort. As a accent rug, it is designed to complement your space. With Recycled Polyester and Obelisk Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Obelisk Gray&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -18114,10 +18114,10 @@
       <c r="G122" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent rug is made to fit naturally into the room. Crafted from Recycled Polyester, it is finished in Palmette Multi tones that pair easily with surrounding decor.&lt;br&gt;
+WILHELM 8' X 11' Area Rug adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent rug, it pairs well with a wide range of interiors. Crafted from Recycled Polyester, it is finished in Doppler Teal tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 8' X 11'&lt;/p&gt;
 &lt;p&gt;Materials: Recycled Polyester.&lt;br&gt;
-Color: Palmette Multi&lt;br&gt;
+Color: Doppler Teal or Spice Rose or Indigo Breach or Concrete Lapis or Abstract Multi or Chroma Multi or Relic Beige or Obelisk Gray or Palmette Multi&lt;br&gt;
 Weight: 46.73 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD122" t="inlineStr">
@@ -18345,7 +18345,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -18401,8 +18401,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 ABBI Table Lamp adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Fabric, Glass, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 16"L X 9"W X 27 1/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Glass, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Glass, Metal, Others.&lt;br&gt;
+Color: Black or Chrome&lt;br&gt;
 Weight: 13.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18489,7 +18489,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
@@ -18543,10 +18543,10 @@
       <c r="G125" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ABBI Table Lamp and its Contemporary character. Built as a accent lighting, it pairs well with a wide range of interiors. Finished in Chrome tones, the Fabric, Glass, Metal, build balances durability with visual appeal.&lt;br&gt;
+ABBI Table Lamp adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Fabric, Glass, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 16"L X 9"W X 27 1/4"H&lt;/p&gt;
-&lt;p&gt;Materials: Fabric, Glass, Metal.&lt;br&gt;
-Color: Chrome&lt;br&gt;
+&lt;p&gt;Materials: Fabric, Glass, Metal, Others.&lt;br&gt;
+Color: Black or Chrome&lt;br&gt;
 Weight: 13.76 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -18633,7 +18633,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr">
@@ -18917,7 +18917,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -19060,7 +19060,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD128" t="inlineStr">
@@ -19203,7 +19203,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -19346,7 +19346,7 @@
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr">
@@ -19489,7 +19489,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr">
@@ -20272,7 +20272,7 @@
 BRIAR Table Lamp adds a Industrial touch while keeping the room feeling warm and welcoming. Built as a accent lighting, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Antique Gold tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 3 7/10"D X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Antique Gold&lt;br&gt;
+Color: Antique Gold or Stain Nickel&lt;br&gt;
 Weight: 7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20359,7 +20359,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -20413,10 +20413,10 @@
       <c r="G138" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BRIAR Table Lamp and its Industrial character. As a accent lighting, it is designed to complement your space. Finished in Stain Nickel tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+BRIAR Table Lamp adds a Industrial touch while keeping the room feeling warm and welcoming. Built as a accent lighting, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Antique Gold tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 3 7/10"D X 22"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Stain Nickel&lt;br&gt;
+Color: Antique Gold or Stain Nickel&lt;br&gt;
 Weight: 7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -20507,7 +20507,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -20648,7 +20648,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -20794,7 +20794,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -20849,10 +20849,10 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with CECELIA Floor Lamp and its Traditional character. This accent lighting is made to fit naturally into the room. Finished in Copper tones, the Crystal, Metal build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 18"L X 18"W X 62"H&lt;/p&gt;
+Product Dimensions: 18"L X 18"W X 62"H / 18"L X 18"W X 35"H&lt;/p&gt;
 &lt;p&gt;Materials: Crystal, Metal.&lt;br&gt;
 Color: Copper&lt;br&gt;
-Weight: 20 lbs&lt;/p&gt;</t>
+Weight: 20 or 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H141" s="68" t="inlineStr">
@@ -20942,7 +20942,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -20996,11 +20996,11 @@
       <c r="G142" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CECELIA Floor Lamp brings a Traditional look to your home with a refined, comfortable feel. Built as a accent lighting, it pairs well with a wide range of interiors. The Crystal, Metal construction is complemented by Copper tones for a polished look.&lt;br&gt;
-Product Dimensions: 18"L X 18"W X 35"H&lt;/p&gt;
+Make the room feel complete with CECELIA Floor Lamp and its Traditional character. This accent lighting is made to fit naturally into the room. Finished in Copper tones, the Crystal, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 18"L X 18"W X 62"H / 18"L X 18"W X 35"H&lt;/p&gt;
 &lt;p&gt;Materials: Crystal, Metal.&lt;br&gt;
 Color: Copper&lt;br&gt;
-Weight: 11 lbs&lt;/p&gt;</t>
+Weight: 20 or 11 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H142" s="68" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -21384,7 +21384,7 @@
       </c>
       <c r="AC144" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD144" t="inlineStr">
@@ -21525,7 +21525,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -21812,7 +21812,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -21953,7 +21953,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -22235,7 +22235,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr">
@@ -22376,7 +22376,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -22517,7 +22517,7 @@
       </c>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr">
@@ -22574,7 +22574,7 @@
 EDIE Table Lamp brings a Contemporary look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Metal construction is complemented by Burgundy tones for a polished look.&lt;br&gt;
 Product Dimensions: 12"DIA X 23 1/2"H (1PC/CTN)&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Burgundy&lt;br&gt;
+Color: Burgundy or Black or Pink&lt;br&gt;
 Weight: 3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22661,7 +22661,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -22715,10 +22715,10 @@
       <c r="G154" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with EDIE Table Lamp, styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+EDIE Table Lamp brings a Contemporary look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Metal construction is complemented by Burgundy tones for a polished look.&lt;br&gt;
 Product Dimensions: 12"DIA X 23 1/2"H (1PC/CTN)&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Burgundy or Black or Pink&lt;br&gt;
 Weight: 3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22805,7 +22805,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -22859,10 +22859,10 @@
       <c r="G155" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-EDIE Table Lamp adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent lighting, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Pink tones that pair easily with surrounding decor.&lt;br&gt;
+EDIE Table Lamp brings a Contemporary look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Metal construction is complemented by Burgundy tones for a polished look.&lt;br&gt;
 Product Dimensions: 12"DIA X 23 1/2"H (1PC/CTN)&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Pink&lt;br&gt;
+Color: Burgundy or Black or Pink&lt;br&gt;
 Weight: 3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -22949,7 +22949,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -23090,7 +23090,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD156" t="inlineStr">
@@ -23231,7 +23231,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD158" t="inlineStr">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD160" t="inlineStr">
@@ -23809,7 +23809,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr">
@@ -24091,7 +24091,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -24232,7 +24232,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD164" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="AC166" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD166" t="inlineStr">
@@ -24655,7 +24655,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="AC168" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD168" t="inlineStr">
@@ -24937,7 +24937,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -25078,7 +25078,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -25360,7 +25360,7 @@
       </c>
       <c r="AC172" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD172" t="inlineStr">
@@ -25420,11 +25420,11 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with HANNA Table Lamp and its Traditional character. This accent lighting is made to fit naturally into the room. Finished in Espresso tones, the Ceramic build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 27"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Espresso&lt;br&gt;
+Color: Espresso or Gray&lt;br&gt;
 Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -25573,13 +25573,13 @@
       <c r="G174" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HANNA Table Lamp brings a Traditional look to your home with a refined, comfortable feel. Built as a accent lighting, it pairs well with a wide range of interiors. The Ceramic construction is complemented by Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with HANNA Table Lamp and its Traditional character. This accent lighting is made to fit naturally into the room. Finished in Espresso tones, the Ceramic build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 27"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Espresso or Gray&lt;br&gt;
 Weight: 24 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -25959,7 +25959,7 @@
       </c>
       <c r="AC176" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD176" t="inlineStr">
@@ -26102,7 +26102,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -26245,7 +26245,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD178" t="inlineStr">
@@ -26388,7 +26388,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -26443,12 +26443,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with IVY Table Lamp and its Glam character. As a accent lighting, it is designed to complement your space. Finished in Chrome tones, the Crystal, Metal build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 17"L X 17"W X 30"H&lt;/p&gt;
+Product Dimensions: 17"L X 17"W X 30"H / 16"L X 16"W X 29 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Crystal, Metal.&lt;br&gt;
-Color: Chrome&lt;br&gt;
-Weight: 17 lbs&lt;/p&gt;</t>
+Color: Chrome or Gold or Ivory&lt;br&gt;
+Weight: 17 or 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H180" s="39" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr">
@@ -26588,11 +26588,13 @@
       <c r="G181" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-IVY Table Lamp brings a Contemporary look to your home with a refined, comfortable feel. This accent lighting is made to fit naturally into the room. The Crystal, Metal construction is complemented by Gold or Ivory tones for a polished look.&lt;br&gt;
-Product Dimensions: 16"L X 16"W X 29 1/2"H&lt;/p&gt;
+Make the room feel complete with IVY Table Lamp and its Glam character. As a accent lighting, it is designed to complement your space. Finished in Chrome tones, the Crystal, Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 17"L X 17"W X 30"H / 16"L X 16"W X 29 1/2"H&lt;/p&gt;
+&lt;p&gt;Features&lt;br&gt;
+- Glam design&lt;/p&gt;
 &lt;p&gt;Materials: Crystal, Metal.&lt;br&gt;
-Color: Gold or Ivory&lt;br&gt;
-Weight: 13 lbs&lt;/p&gt;</t>
+Color: Chrome or Gold or Ivory&lt;br&gt;
+Weight: 17 or 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H181" s="39" t="inlineStr">
@@ -26678,7 +26680,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -26819,7 +26821,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr">
@@ -26879,7 +26881,7 @@
 - Glam design&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -26966,7 +26968,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -27020,13 +27022,13 @@
       <c r="G184" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with JADA Ceiling Lamp and its Glam character. Built as a accent lighting, it pairs well with a wide range of interiors. Finished in Chrome or White tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+JADA Ceiling Lamp adds a Glam touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Metal, it is finished in Chrome or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 24"H X 16"D&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Chrome or White&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27113,7 +27115,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr">
@@ -27173,7 +27175,7 @@
 - Glam design&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27260,7 +27262,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -27314,13 +27316,13 @@
       <c r="G186" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with JADA Floor Lamp, styled in Glam and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Metal and Chrome or White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+JADA Floor Lamp brings a Glam look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Metal construction is complemented by Chrome or Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 16"DIA X 62 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Chrome or White&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 16 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27407,7 +27409,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr">
@@ -27467,7 +27469,7 @@
 - Glam design&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Chrome or Black&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 9.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27554,7 +27556,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -27608,13 +27610,13 @@
       <c r="G188" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with JADA Table Lamp and its Glam character. As a accent lighting, it is designed to complement your space. Finished in Chrome or White tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+JADA Table Lamp adds a Glam touch while keeping the room feeling warm and welcoming. Built as a accent lighting, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Chrome or Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 29 1/2"H X 16"DIA&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Chrome or White&lt;br&gt;
+Color: Chrome or Black or Chrome or White&lt;br&gt;
 Weight: 9.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -27701,7 +27703,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD188" t="inlineStr">
@@ -27842,7 +27844,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -27988,7 +27990,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr">
@@ -28045,7 +28047,7 @@
 Elevate your space with JESS Arch Lamp, styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Marble, Metal and Antique Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 18"DIA X 86"H&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Metal.&lt;br&gt;
-Color: Antique Gold&lt;br&gt;
+Color: Antique Gold or Black or Brushed Steel&lt;br&gt;
 Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28132,7 +28134,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -28186,10 +28188,10 @@
       <c r="G192" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JESS Arch Lamp adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent lighting, it pairs well with a wide range of interiors. Crafted from Marble, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with JESS Arch Lamp, styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Marble, Metal and Antique Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 18"DIA X 86"H&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Antique Gold or Black or Brushed Steel&lt;br&gt;
 Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28276,7 +28278,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -28330,10 +28332,10 @@
       <c r="G193" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with JESS Arch Lamp and its Contemporary character. As a accent lighting, it is designed to complement your space. Finished in Brushed Steel tones, the Marble, Metal build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with JESS Arch Lamp, styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Marble, Metal and Antique Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 18"DIA X 86"H&lt;/p&gt;
 &lt;p&gt;Materials: Marble, Metal.&lt;br&gt;
-Color: Brushed Steel&lt;br&gt;
+Color: Antique Gold or Black or Brushed Steel&lt;br&gt;
 Weight: 28 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -28420,7 +28422,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -28561,7 +28563,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr">
@@ -28704,7 +28706,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -28847,7 +28849,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr">
@@ -28995,7 +28997,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr">
@@ -29136,7 +29138,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr">
@@ -29277,7 +29279,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr">
@@ -29425,7 +29427,7 @@
       </c>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr">
@@ -29573,7 +29575,7 @@
       </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr">
@@ -29714,7 +29716,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr">
@@ -29855,7 +29857,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr">
@@ -29912,7 +29914,7 @@
 LUZ Table Lamp brings a Contemporary look to your home with a refined, comfortable feel. This accent lighting is made to fit naturally into the room. The Metal construction is complemented by Antique Gold tones for a polished look.&lt;br&gt;
 Product Dimensions: 12 1/2"DIA X 26"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Antique Gold&lt;br&gt;
+Color: Antique Gold or Silver&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -29999,7 +30001,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr">
@@ -30053,10 +30055,10 @@
       <c r="G205" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with LUZ Table Lamp, styled in Geometric Design and designed for everyday comfort. Built as a accent lighting, it pairs well with a wide range of interiors. With Metal and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+LUZ Table Lamp brings a Contemporary look to your home with a refined, comfortable feel. This accent lighting is made to fit naturally into the room. The Metal construction is complemented by Antique Gold tones for a polished look.&lt;br&gt;
 Product Dimensions: 12 1/2"DIA X 26"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Antique Gold or Silver&lt;br&gt;
 Weight: 12 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30143,7 +30145,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD205" t="inlineStr">
@@ -30284,7 +30286,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD206" t="inlineStr">
@@ -30341,7 +30343,7 @@
 MEG Floor Lamp adds a Transitional touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Metal, it is finished in Clear tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60 1/2"H X 5"DIA&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Clear&lt;br&gt;
+Color: Clear or Black or Chrome&lt;br&gt;
 Weight: 18 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30428,7 +30430,7 @@
       </c>
       <c r="AC207" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD207" t="inlineStr">
@@ -30482,10 +30484,10 @@
       <c r="G208" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with MEG Floor Lamp and its Transitional character. Built as a accent lighting, it pairs well with a wide range of interiors. Finished in Black or Chrome tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+MEG Floor Lamp adds a Transitional touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Metal, it is finished in Clear tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60 1/2"H X 5"DIA&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
+Color: Clear or Black or Chrome&lt;br&gt;
 Weight: 18 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30572,7 +30574,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD208" t="inlineStr">
@@ -30629,7 +30631,7 @@
 MEG Table Lamp brings a Transitional look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Metal construction is complemented by Clear tones for a polished look.&lt;br&gt;
 Product Dimensions: 27 1/2"H X 5"DIA&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Clear&lt;br&gt;
+Color: Clear or Black or Chrome&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30716,7 +30718,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD209" t="inlineStr">
@@ -30770,10 +30772,10 @@
       <c r="G210" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with MEG Table Lamp, styled in Transitional and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Metal and Black or Chrome tones, it blends structure and softness in one clean profile.&lt;br&gt;
+MEG Table Lamp brings a Transitional look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Metal construction is complemented by Clear tones for a polished look.&lt;br&gt;
 Product Dimensions: 27 1/2"H X 5"DIA&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black or Chrome&lt;br&gt;
+Color: Clear or Black or Chrome&lt;br&gt;
 Weight: 10 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -30860,7 +30862,7 @@
       </c>
       <c r="AC210" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD210" t="inlineStr">
@@ -31001,7 +31003,7 @@
       </c>
       <c r="AC211" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD211" t="inlineStr">
@@ -31142,7 +31144,7 @@
       </c>
       <c r="AC212" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD212" t="inlineStr">
@@ -31296,7 +31298,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD213" t="inlineStr">
@@ -31450,7 +31452,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD214" t="inlineStr">
@@ -31591,7 +31593,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD215" t="inlineStr">
@@ -31651,11 +31653,11 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 NIKI Table Lamp adds a Traditional touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Ceramic, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Ivory&lt;br&gt;
 Weight: 23.54 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -31746,7 +31748,7 @@
       </c>
       <c r="AC216" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD216" t="inlineStr">
@@ -31804,13 +31806,13 @@
       <c r="G217" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with NIKI Table Lamp and its Traditional character. Built as a accent lighting, it pairs well with a wide range of interiors. Finished in Ivory tones, the Ceramic build balances durability with visual appeal.&lt;br&gt;
+NIKI Table Lamp adds a Traditional touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Ceramic, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Ivory&lt;br&gt;
+Color: Black or Ivory&lt;br&gt;
 Weight: 23.54 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -31901,7 +31903,7 @@
       </c>
       <c r="AC217" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD217" t="inlineStr">
@@ -32042,7 +32044,7 @@
       </c>
       <c r="AC218" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD218" t="inlineStr">
@@ -32183,7 +32185,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -32331,7 +32333,7 @@
       </c>
       <c r="AC220" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD220" t="inlineStr">
@@ -32472,7 +32474,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -32620,7 +32622,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr">
@@ -32761,7 +32763,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -32904,7 +32906,7 @@
       </c>
       <c r="AC224" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD224" t="inlineStr">
@@ -33047,7 +33049,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -33190,7 +33192,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr">
@@ -33331,7 +33333,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -33472,7 +33474,7 @@
       </c>
       <c r="AC228" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD228" t="inlineStr">
@@ -33532,11 +33534,11 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 SCARLETT Table Lamp brings a Transitional look to your home with a refined, comfortable feel. Built as a accent lighting, it pairs well with a wide range of interiors. The Ceramic construction is complemented by Burgundy tones for a polished look.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Burgundy&lt;br&gt;
+Color: Burgundy or Black or Ivory&lt;br&gt;
 Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33627,7 +33629,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -33685,13 +33687,13 @@
       <c r="G230" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with SCARLETT Table Lamp, styled in Transitional and designed for everyday comfort. As a accent lighting, it is designed to complement your space. With Ceramic and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+SCARLETT Table Lamp brings a Transitional look to your home with a refined, comfortable feel. Built as a accent lighting, it pairs well with a wide range of interiors. The Ceramic construction is complemented by Burgundy tones for a polished look.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Burgundy or Black or Ivory&lt;br&gt;
 Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33782,7 +33784,7 @@
       </c>
       <c r="AC230" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD230" t="inlineStr">
@@ -33840,13 +33842,13 @@
       <c r="G231" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SCARLETT Table Lamp adds a Transitional touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Ceramic, it is finished in Ivory tones that pair easily with surrounding decor.&lt;br&gt;
+SCARLETT Table Lamp brings a Transitional look to your home with a refined, comfortable feel. Built as a accent lighting, it pairs well with a wide range of interiors. The Ceramic construction is complemented by Burgundy tones for a polished look.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 27"H&lt;br&gt;
-Size: (6 or CTN)&lt;/p&gt;
+Size: (6/CTN)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Padded Headboard &amp;amp; Footboard with pleated design&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
-Color: Ivory&lt;br&gt;
+Color: Burgundy or Black or Ivory&lt;br&gt;
 Weight: 22 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -33937,7 +33939,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -34078,7 +34080,7 @@
       </c>
       <c r="AC232" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD232" t="inlineStr">
@@ -34222,7 +34224,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -34368,7 +34370,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr">
@@ -34514,7 +34516,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -34660,7 +34662,7 @@
       </c>
       <c r="AC236" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD236" t="inlineStr">
@@ -34717,7 +34719,7 @@
 Elevate your space with SPRIG Table Lamp (2 or CTN), styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 15"L X 15"W X 28"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Red or White&lt;br&gt;
 Weight: 16.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -34808,7 +34810,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -34862,10 +34864,10 @@
       <c r="G238" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-SPRIG Table Lamp (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent lighting, it pairs well with a wide range of interiors. Crafted from Metal, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with SPRIG Table Lamp (2 or CTN), styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 15"L X 15"W X 28"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Black or Red or White&lt;br&gt;
 Weight: 16.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -34956,7 +34958,7 @@
       </c>
       <c r="AC238" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD238" t="inlineStr">
@@ -35010,10 +35012,10 @@
       <c r="G239" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with SPRIG Table Lamp (2 or CTN) and its Contemporary character. As a accent lighting, it is designed to complement your space. Finished in White tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with SPRIG Table Lamp (2 or CTN), styled in Contemporary and designed for everyday comfort. This accent lighting is made to fit naturally into the room. With Metal and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 15"L X 15"W X 28"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Red or White&lt;br&gt;
 Weight: 16.06 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -35104,7 +35106,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -35245,7 +35247,7 @@
       </c>
       <c r="AC240" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD240" t="inlineStr">
@@ -35386,7 +35388,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -35527,7 +35529,7 @@
       </c>
       <c r="AC242" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD242" t="inlineStr">
@@ -35668,7 +35670,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -35816,7 +35818,7 @@
       </c>
       <c r="AC244" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD244" t="inlineStr">
@@ -35957,7 +35959,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -36098,7 +36100,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -36153,9 +36155,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with ZAYA Floor Lamp and its Contemporary character. This accent lighting is made to fit naturally into the room. Finished in Stained Gold tones, the Metal build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 20"DIA X 57" (UP TO 71"H) Shade size: 20"DIA X13"H&lt;/p&gt;
+Product Dimensions: 20"DIA X 57" (UP TO 71"H)  Shade size: 20"DIA X13"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Stained Gold&lt;br&gt;
+Color: Stained Gold or Brushed Steel&lt;br&gt;
 Weight: 12.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36242,7 +36244,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -36296,10 +36298,10 @@
       <c r="G248" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZAYA Floor Lamp brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent lighting, it pairs well with a wide range of interiors. The Metal construction is complemented by Brushed Steel tones for a polished look.&lt;br&gt;
-Product Dimensions: 20"DIA X 57" (UP TO 71"H) Shade size: 20"DIA X13"H&lt;/p&gt;
+Make the room feel complete with ZAYA Floor Lamp and its Contemporary character. This accent lighting is made to fit naturally into the room. Finished in Stained Gold tones, the Metal build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 20"DIA X 57" (UP TO 71"H)  Shade size: 20"DIA X13"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Brushed Steel&lt;br&gt;
+Color: Stained Gold or Brushed Steel&lt;br&gt;
 Weight: 12.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36386,7 +36388,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -36441,9 +36443,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with ZAYA Table Lamp, styled in Contemporary and designed for everyday comfort. As a accent lighting, it is designed to complement your space. With Metal and Stained Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 15"DIA X 32"H (UP TO 37"H) shade size: 16"DIA X 10" H&lt;/p&gt;
+Product Dimensions: 15"DIA X 32"H (UP TO 37"H)  shade size: 16"DIA X 10" H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Stained Gold&lt;br&gt;
+Color: Stained Gold or Brushed Steel&lt;br&gt;
 Weight: 12.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36534,7 +36536,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -36588,10 +36590,10 @@
       <c r="G250" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZAYA Table Lamp adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent lighting is made to fit naturally into the room. Crafted from Metal, it is finished in Brushed Steel tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 15"DIA X 32"H (UP TO 37"H) shade size: 16"DIA X 10" H&lt;/p&gt;
+Elevate your space with ZAYA Table Lamp, styled in Contemporary and designed for everyday comfort. As a accent lighting, it is designed to complement your space. With Metal and Stained Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 15"DIA X 32"H (UP TO 37"H)  shade size: 16"DIA X 10" H&lt;/p&gt;
 &lt;p&gt;Materials: Metal.&lt;br&gt;
-Color: Brushed Steel&lt;br&gt;
+Color: Stained Gold or Brushed Steel&lt;br&gt;
 Weight: 12.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36682,7 +36684,7 @@
       </c>
       <c r="AC250" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD250" t="inlineStr">
@@ -36739,7 +36741,7 @@
 Make the room feel complete with ZERA Floor Lamp and its Contemporary character. Built as a accent lighting, it pairs well with a wide range of interiors. Finished in Black or Gold tones, the Fabric, Metal build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 59"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Metal.&lt;br&gt;
-Color: Black or Gold&lt;br&gt;
+Color: Black or Gold or White or Gold&lt;br&gt;
 Weight: 9.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36826,7 +36828,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -36880,10 +36882,10 @@
       <c r="G252" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ZERA Floor Lamp brings a Contemporary look to your home with a refined, comfortable feel. As a accent lighting, it is designed to complement your space. The Fabric, Metal construction is complemented by White or Gold tones for a polished look.&lt;br&gt;
+Make the room feel complete with ZERA Floor Lamp and its Contemporary character. Built as a accent lighting, it pairs well with a wide range of interiors. Finished in Black or Gold tones, the Fabric, Metal build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17"L X 17"W X 59"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Metal.&lt;br&gt;
-Color: White or Gold&lt;br&gt;
+Color: Black or Gold or White or Gold&lt;br&gt;
 Weight: 9.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -36970,7 +36972,7 @@
       </c>
       <c r="AC252" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD252" t="inlineStr">
@@ -37111,7 +37113,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -37252,7 +37254,7 @@
       </c>
       <c r="AC254" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD254" t="inlineStr">
@@ -37309,7 +37311,7 @@
 Make the room feel complete with ACASO Accent Chair and its Contemporary character. Built as a accent chair, it pairs well with a wide range of interiors. Finished in Mushroom tones, the Fabric, Foam, Rubberwood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 30.5"W X 32"D X 32.5"H (SEAT HT: 19", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Rubberwood.&lt;br&gt;
-Color: Mushroom&lt;/p&gt;</t>
+Color: Mushroom or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H255" s="54" t="inlineStr">
@@ -37393,7 +37395,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -37447,10 +37449,10 @@
       <c r="G256" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ACASO Accent Chair brings a Contemporary look to your home with a refined, comfortable feel. As a accent chair, it is designed to complement your space. The Fabric, Foam, Rubberwood construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with ACASO Accent Chair and its Contemporary character. Built as a accent chair, it pairs well with a wide range of interiors. Finished in Mushroom tones, the Fabric, Foam, Rubberwood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 30.5"W X 32"D X 32.5"H (SEAT HT: 19", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Rubberwood.&lt;br&gt;
-Color: White&lt;/p&gt;</t>
+Color: Mushroom or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H256" s="54" t="inlineStr">
@@ -37534,7 +37536,7 @@
       </c>
       <c r="AC256" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD256" t="inlineStr">
@@ -37591,7 +37593,7 @@
 Make the room feel complete with ALCOBA Accent Chair and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Mushroom tones, the Fabric, Foam, Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 25"W X 26"D X 28.5"H (SEAT HT: 18", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Wood.&lt;br&gt;
-Color: Mushroom&lt;/p&gt;</t>
+Color: Mushroom or Taupe&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H257" s="68" t="inlineStr">
@@ -37675,7 +37677,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -37729,10 +37731,10 @@
       <c r="G258" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ALCOBA Accent Chair brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent chair, it pairs well with a wide range of interiors. The Fabric, Foam, Wood construction is complemented by Taupe tones for a polished look.&lt;br&gt;
+Make the room feel complete with ALCOBA Accent Chair and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Mushroom tones, the Fabric, Foam, Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 25"W X 26"D X 28.5"H (SEAT HT: 18", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Wood.&lt;br&gt;
-Color: Taupe&lt;/p&gt;</t>
+Color: Mushroom or Taupe&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H258" s="68" t="inlineStr">
@@ -37816,7 +37818,7 @@
       </c>
       <c r="AC258" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD258" t="inlineStr">
@@ -37959,7 +37961,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -38016,7 +38018,7 @@
 Make the room feel complete with BEDALE Accent Chair and its Contemporary character. Built as a accent chair, it pairs well with a wide range of interiors. Finished in Mushroom tones, the Fabric, Wood, Foam build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 33"W X 32"D X 29"H (SEAT HT: 18.5", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Wood, Foam.&lt;br&gt;
-Color: Mushroom&lt;/p&gt;</t>
+Color: Mushroom or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H260" s="66" t="inlineStr">
@@ -38100,7 +38102,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr">
@@ -38154,10 +38156,10 @@
       <c r="G261" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BEDALE Accent Chair brings a Contemporary look to your home with a refined, comfortable feel. As a accent chair, it is designed to complement your space. The Fabric, Wood, Foam construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with BEDALE Accent Chair and its Contemporary character. Built as a accent chair, it pairs well with a wide range of interiors. Finished in Mushroom tones, the Fabric, Wood, Foam build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 33"W X 32"D X 29"H (SEAT HT: 18.5", SEAT DP: 22")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Wood, Foam.&lt;br&gt;
-Color: White&lt;/p&gt;</t>
+Color: Mushroom or White&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H261" s="66" t="inlineStr">
@@ -38241,7 +38243,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -38298,7 +38300,7 @@
 Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Chocolate Brown&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38385,7 +38387,7 @@
       </c>
       <c r="AC262" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD262" t="inlineStr">
@@ -38439,10 +38441,10 @@
       <c r="G263" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELPER Power Glider Recliner w/ Swivel brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent chair, it pairs well with a wide range of interiors. The Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood construction is complemented by Dark Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38529,7 +38531,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -38583,10 +38585,10 @@
       <c r="G264" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with BELPER Power Glider Recliner w/ Swivel, styled in Contemporary and designed for everyday comfort. As a accent chair, it is designed to complement your space. With Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood and Olive Green tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Olive Green&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38673,7 +38675,7 @@
       </c>
       <c r="AC264" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD264" t="inlineStr">
@@ -38727,10 +38729,10 @@
       <c r="G265" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELPER Power Glider Recliner w/ Swivel adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent chair is made to fit naturally into the room. Crafted from Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood, it is finished in Sky Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Sky Blue&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38817,7 +38819,7 @@
       </c>
       <c r="AC265" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD265" t="inlineStr">
@@ -38871,10 +38873,10 @@
       <c r="G266" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. Built as a accent chair, it pairs well with a wide range of interiors. Finished in Dark Teal tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Dark Teal&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -38961,7 +38963,7 @@
       </c>
       <c r="AC266" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD266" t="inlineStr">
@@ -39015,10 +39017,10 @@
       <c r="G267" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELPER Power Glider Recliner w/ Swivel brings a Contemporary look to your home with a refined, comfortable feel. As a accent chair, it is designed to complement your space. The Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood construction is complemented by Taupe tones for a polished look.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Taupe&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39105,7 +39107,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -39159,10 +39161,10 @@
       <c r="G268" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with BELPER Power Glider Recliner w/ Swivel, styled in Contemporary and designed for everyday comfort. This accent chair is made to fit naturally into the room. With Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39249,7 +39251,7 @@
       </c>
       <c r="AC268" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD268" t="inlineStr">
@@ -39303,10 +39305,10 @@
       <c r="G269" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELPER Power Glider Recliner w/ Swivel adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent chair, it pairs well with a wide range of interiors. Crafted from Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood, it is finished in Yellow tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with BELPER Power Glider Recliner w/ Swivel and its Contemporary character. This accent chair is made to fit naturally into the room. Finished in Chocolate Brown tones, the Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 39"W X 37-63"D X 41"H (SEAT HT: 19", SEAT DP: 21")&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Foam, Fiber, Engineered Wood, Eucalyptus Wood.&lt;br&gt;
-Color: Yellow&lt;br&gt;
+Color: Chocolate Brown or Dark Gray or Olive Green or Sky Blue or Dark Teal or Taupe or White or Yellow&lt;br&gt;
 Weight: 99.43 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39393,7 +39395,7 @@
       </c>
       <c r="AC269" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD269" t="inlineStr">
@@ -39452,7 +39454,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Metal, Solid Wood.&lt;br&gt;
-Color: Dark Blue&lt;br&gt;
+Color: Dark Blue or Light Brown or Dark Gray&lt;br&gt;
 Weight: 43.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39539,7 +39541,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -39593,12 +39595,12 @@
       <c r="G271" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FLORENS Swivel Chair and its Contemporary character. As a accent chair, it is designed to complement your space. Finished in Light Brown tones, the Fabric, Metal, Solid Wood build balances durability with visual appeal.&lt;br&gt;
+FLORENS Swivel Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent chair, it pairs well with a wide range of interiors. Crafted from Fabric, Metal, Solid Wood, it is finished in Dark Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 31.5"W X 33"D X 29"H(SEAT HT: 17"; SEAT DP: 29")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Metal, Solid Wood.&lt;br&gt;
-Color: Light Brown&lt;br&gt;
+Color: Dark Blue or Light Brown or Dark Gray&lt;br&gt;
 Weight: 43.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39685,7 +39687,7 @@
       </c>
       <c r="AC271" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD271" t="inlineStr">
@@ -39739,12 +39741,12 @@
       <c r="G272" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FLORENS Swivel Chair brings a Contemporary look to your home with a refined, comfortable feel. This accent chair is made to fit naturally into the room. The Fabric, Metal, Solid Wood construction is complemented by Dark Gray tones for a polished look.&lt;br&gt;
+FLORENS Swivel Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent chair, it pairs well with a wide range of interiors. Crafted from Fabric, Metal, Solid Wood, it is finished in Dark Blue tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 31.5"W X 33"D X 29"H(SEAT HT: 17"; SEAT DP: 29")&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Metal, Solid Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Dark Blue or Light Brown or Dark Gray&lt;br&gt;
 Weight: 43.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39831,7 +39833,7 @@
       </c>
       <c r="AC272" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD272" t="inlineStr">
@@ -39886,9 +39888,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 PERCE Office Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent chair, it pairs well with a wide range of interiors. Crafted from Leatherette, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: UPRIGHT: 27"W X 29 1/2 (UP TO 44) "D X 46 3/4 (UP TO 50) "H, RECLINED: 27"W X 60 1/2"D X 37"H, (SEAT HT: 20 1/2" UP TO 23 5/8", SEAT DP: 17 1/2")&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Metal.&lt;br&gt;
-Color: Black&lt;br&gt;
+Product Dimensions: UPRIGHT: 27"W X 29 1/2 (UP TO 44) "D X 46 3/4 (UP TO 50) "H, RECLINED: 27"W X 60 1/2"D X 37"H, (SEAT HT: 20 1/2" UP TO 23 5/8", SEAT DP: 17 1/2") / UPRIGHT: 27"W X 29 1/2 (UP TO 44) "D X 46 3/4 (UP TO 50) "H, RECLINED: 27"W X 60 1/2"D X 37"H (SEAT HT: 20 1/2" UP TO 23 5/8", SEAT DP: 17 1/2")&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Metal, Others.&lt;br&gt;
+Color: Black or Brown&lt;br&gt;
 Weight: 50.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -39975,7 +39977,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">
@@ -40029,10 +40031,10 @@
       <c r="G274" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with PERCE Office Chair and its Contemporary character. As a accent chair, it is designed to complement your space. Finished in Brown tones, the Leatherette, Metal, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: UPRIGHT: 27"W X 29 1/2 (UP TO 44) "D X 46 3/4 (UP TO 50) "H, RECLINED: 27"W X 60 1/2"D X 37"H (SEAT HT: 20 1/2" UP TO 23 5/8", SEAT DP: 17 1/2")&lt;/p&gt;
-&lt;p&gt;Materials: Leatherette, Metal.&lt;br&gt;
-Color: Brown&lt;br&gt;
+PERCE Office Chair adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent chair, it pairs well with a wide range of interiors. Crafted from Leatherette, Metal, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: UPRIGHT: 27"W X 29 1/2 (UP TO 44) "D X 46 3/4 (UP TO 50) "H, RECLINED: 27"W X 60 1/2"D X 37"H, (SEAT HT: 20 1/2" UP TO 23 5/8", SEAT DP: 17 1/2") / UPRIGHT: 27"W X 29 1/2 (UP TO 44) "D X 46 3/4 (UP TO 50) "H, RECLINED: 27"W X 60 1/2"D X 37"H (SEAT HT: 20 1/2" UP TO 23 5/8", SEAT DP: 17 1/2")&lt;/p&gt;
+&lt;p&gt;Materials: Leatherette, Metal, Others.&lt;br&gt;
+Color: Black or Brown&lt;br&gt;
 Weight: 50.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -40119,7 +40121,7 @@
       </c>
       <c r="AC274" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD274" t="inlineStr">
@@ -40260,7 +40262,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -40317,7 +40319,7 @@
 Elevate your space with STILLWATER Chaise, styled in Transitional and designed for everyday comfort. Built as a accent chair, it pairs well with a wide range of interiors. With Linen-like Fabric, Wood, Engineered Wood and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 61"W X 25"D X 31 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like Fabric, Wood, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Gray&lt;br&gt;
 Weight: 69.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -40404,7 +40406,7 @@
       </c>
       <c r="AC276" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD276" t="inlineStr">
@@ -40458,10 +40460,10 @@
       <c r="G277" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STILLWATER Chaise adds a Transitional touch while keeping the room feeling warm and welcoming. As a accent chair, it is designed to complement your space. Crafted from Linen-like Fabric, Wood, Engineered Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with STILLWATER Chaise, styled in Transitional and designed for everyday comfort. Built as a accent chair, it pairs well with a wide range of interiors. With Linen-like Fabric, Wood, Engineered Wood and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 61"W X 25"D X 31 1/2"H&lt;/p&gt;
 &lt;p&gt;Materials: Linen-like Fabric, Wood, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Beige or Gray&lt;br&gt;
 Weight: 69.3 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -40548,7 +40550,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -40691,7 +40693,7 @@
       </c>
       <c r="AC278" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD278" t="inlineStr">
@@ -40834,7 +40836,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -40889,9 +40891,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with ACKE Computer Desk, styled in Contemporary and designed for everyday comfort. This accent desk is made to fit naturally into the room. With Metal, Glass, Engineered Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 59 1/4"L X 23 5/8"W X 29 3/4"H (WHEN SHELF OPEN: 55 1/8"W)&lt;/p&gt;
+Product Dimensions: 59 1/4"L X 23 5/8"W X 29 3/4"H (WHEN SHELF OPEN: 55 1/8"W) / 59 1/4 - 55 1/8"L X 23 5/8"D X 29 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 141.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -40978,7 +40980,7 @@
       </c>
       <c r="AC280" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD280" t="inlineStr">
@@ -41032,10 +41034,10 @@
       <c r="G281" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-ACKE Computer Desk adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent desk, it pairs well with a wide range of interiors. Crafted from Metal, Glass, Engineered Wood, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 59 1/4 - 55 1/8"L X 23 5/8"D X 29 3/4"H&lt;/p&gt;
+Elevate your space with ACKE Computer Desk, styled in Contemporary and designed for everyday comfort. This accent desk is made to fit naturally into the room. With Metal, Glass, Engineered Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 59 1/4"L X 23 5/8"W X 29 3/4"H (WHEN SHELF OPEN: 55 1/8"W) / 59 1/4 - 55 1/8"L X 23 5/8"D X 29 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 141.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41122,7 +41124,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -41176,10 +41178,10 @@
       <c r="G282" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ACKE Computer Desk and its Contemporary character. As a accent desk, it is designed to complement your space. Finished in White tones, the Metal, Glass, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 59 1/4"L X 23 5/8"W X 29 3/4"H (WHEN SHELF OPEN: 55 1/8"W)&lt;/p&gt;
+Elevate your space with ACKE Computer Desk, styled in Contemporary and designed for everyday comfort. This accent desk is made to fit naturally into the room. With Metal, Glass, Engineered Wood and Black tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 59 1/4"L X 23 5/8"W X 29 3/4"H (WHEN SHELF OPEN: 55 1/8"W) / 59 1/4 - 55 1/8"L X 23 5/8"D X 29 3/4"H&lt;/p&gt;
 &lt;p&gt;Materials: Metal, Glass, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or Gray or White&lt;br&gt;
 Weight: 141.02 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41266,7 +41268,7 @@
       </c>
       <c r="AC282" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD282" t="inlineStr">
@@ -41408,7 +41410,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -41551,7 +41553,7 @@
       </c>
       <c r="AC284" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD284" t="inlineStr">
@@ -41692,7 +41694,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -41838,7 +41840,7 @@
       </c>
       <c r="AC286" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD286" t="inlineStr">
@@ -41897,8 +41899,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port and Power&lt;br&gt;
 Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Steel, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique Blue&lt;br&gt;
+&lt;p&gt;Materials: Steel, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Blue or Antique White or Walnut&lt;br&gt;
 Weight: 135.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -41983,7 +41985,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -42037,13 +42039,13 @@
       <c r="G288" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-FREIBURG Corner Desk adds a Transitional touch while keeping the room feeling warm and welcoming. As a accent desk, it is designed to complement your space. Crafted from Steel, Solid Wood, Wood Veneer, it is finished in Antique White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with FREIBURG Corner Desk, styled in Transitional and designed for everyday comfort. Built as a accent desk, it pairs well with a wide range of interiors. With Steel, Solid Wood, Wood Veneer, and Antique Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 56 3/4"L X 64"W X 30 1/2"H (UP TO 41 1/4"H)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port and Power&lt;br&gt;
 Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Steel, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Antique White&lt;br&gt;
+&lt;p&gt;Materials: Steel, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Blue or Antique White or Walnut&lt;br&gt;
 Weight: 135.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -42128,7 +42130,7 @@
       </c>
       <c r="AC288" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD288" t="inlineStr">
@@ -42182,13 +42184,13 @@
       <c r="G289" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with FREIBURG Corner Desk and its Transitional character. This accent desk is made to fit naturally into the room. Finished in Walnut tones, the Steel, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with FREIBURG Corner Desk, styled in Transitional and designed for everyday comfort. Built as a accent desk, it pairs well with a wide range of interiors. With Steel, Solid Wood, Wood Veneer, and Antique Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 56 3/4"L X 64"W X 30 1/2"H (UP TO 41 1/4"H)&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): USB Port and Power&lt;br&gt;
 Concealed Drawer&lt;/p&gt;
-&lt;p&gt;Materials: Steel, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Walnut&lt;br&gt;
+&lt;p&gt;Materials: Steel, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Antique Blue or Antique White or Walnut&lt;br&gt;
 Weight: 135.1 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -42273,7 +42275,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -42423,7 +42425,7 @@
       </c>
       <c r="AC290" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD290" t="inlineStr">
@@ -42566,7 +42568,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -42710,7 +42712,7 @@
       </c>
       <c r="AC292" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD292" t="inlineStr">
@@ -42851,7 +42853,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -42992,7 +42994,7 @@
       </c>
       <c r="AC294" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD294" t="inlineStr">
@@ -43135,7 +43137,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -43278,7 +43280,7 @@
       </c>
       <c r="AC296" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD296" t="inlineStr">
@@ -43420,7 +43422,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -43477,8 +43479,8 @@
 AILEEN Storage Stool brings a Contemporary look to your home with a refined, comfortable feel. As a accent stool, it is designed to complement your space. The Fabric, Stainless Steel, Engineered Wood construction is complemented by Charcoal tones for a polished look.&lt;br&gt;
 Product Dimensions: 18"W X 18"D X 18.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Charcoal&lt;br&gt;
-Weight: 18.62 lbs&lt;/p&gt;</t>
+Color: Charcoal or Beige&lt;br&gt;
+Weight: 18.62 or 19.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H298" s="32" t="inlineStr">
@@ -43564,7 +43566,7 @@
       </c>
       <c r="AC298" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD298" t="inlineStr">
@@ -43618,11 +43620,11 @@
       <c r="G299" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with AILEEN Storage Stool, styled in Contemporary and designed for everyday comfort. This accent stool is made to fit naturally into the room. With Fabric, Stainless Steel, Engineered Wood and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+AILEEN Storage Stool brings a Contemporary look to your home with a refined, comfortable feel. As a accent stool, it is designed to complement your space. The Fabric, Stainless Steel, Engineered Wood construction is complemented by Charcoal tones for a polished look.&lt;br&gt;
 Product Dimensions: 18"W X 18"D X 18.5"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 19.51 lbs&lt;/p&gt;</t>
+Color: Charcoal or Beige&lt;br&gt;
+Weight: 18.62 or 19.51 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H299" s="32" t="inlineStr">
@@ -43708,7 +43710,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -43765,8 +43767,8 @@
 Make the room feel complete with CYNTHIA Stool and its Contemporary character. As a accent stool, it is designed to complement your space. Finished in Brown tones, the Fabric, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
-Weight: 12.78 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 12.78 or 12.67 or 12.89 or 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H300" s="39" t="inlineStr">
@@ -43852,7 +43854,7 @@
       </c>
       <c r="AC300" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD300" t="inlineStr">
@@ -43906,11 +43908,11 @@
       <c r="G301" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CYNTHIA Stool brings a Contemporary look to your home with a refined, comfortable feel. This accent stool is made to fit naturally into the room. The Fabric, Engineered Wood construction is complemented by Green tones for a polished look.&lt;br&gt;
+Make the room feel complete with CYNTHIA Stool and its Contemporary character. As a accent stool, it is designed to complement your space. Finished in Brown tones, the Fabric, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Green&lt;br&gt;
-Weight: 12.67 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 12.78 or 12.67 or 12.89 or 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H301" s="39" t="inlineStr">
@@ -43996,7 +43998,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -44050,11 +44052,11 @@
       <c r="G302" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CYNTHIA Stool, styled in Contemporary and designed for everyday comfort. Built as a accent stool, it pairs well with a wide range of interiors. With Fabric, Engineered Wood and Saddle Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with CYNTHIA Stool and its Contemporary character. As a accent stool, it is designed to complement your space. Finished in Brown tones, the Fabric, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Saddle Brown&lt;br&gt;
-Weight: 12.89 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 12.78 or 12.67 or 12.89 or 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H302" s="39" t="inlineStr">
@@ -44140,7 +44142,7 @@
       </c>
       <c r="AC302" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD302" t="inlineStr">
@@ -44194,11 +44196,11 @@
       <c r="G303" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CYNTHIA Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent stool, it is designed to complement your space. Crafted from Fabric, Engineered Wood, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with CYNTHIA Stool and its Contemporary character. As a accent stool, it is designed to complement your space. Finished in Brown tones, the Fabric, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 13 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 12.78 or 12.67 or 12.89 or 13 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H303" s="39" t="inlineStr">
@@ -44284,7 +44286,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -44343,7 +44345,7 @@
 &lt;p&gt;Features&lt;br&gt;
 - Upholstered in velvet-like fabric&lt;/p&gt;
 &lt;p&gt;Materials: Velvet, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 11.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -44430,7 +44432,7 @@
       </c>
       <c r="AC304" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD304" t="inlineStr">
@@ -44484,12 +44486,12 @@
       <c r="G305" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with DOROTHEA Stool, styled in Contemporary and designed for everyday comfort. This accent stool is made to fit naturally into the room. With Velvet, Stainless Steel, Engineered Wood and White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+DOROTHEA Stool brings a Contemporary look to your home with a refined, comfortable feel. As a accent stool, it is designed to complement your space. The Velvet, Stainless Steel, Engineered Wood construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 15"W X 15"D X 17.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Upholstered in velvet-like fabric&lt;/p&gt;
 &lt;p&gt;Materials: Velvet, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
+Color: Black or White&lt;br&gt;
 Weight: 11.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -44576,7 +44578,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -44635,8 +44637,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Upholstered in velvet-like fabric&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Black&lt;br&gt;
-Weight: 11.9 lbs&lt;/p&gt;</t>
+Color: Black or White&lt;br&gt;
+Weight: 11.9 or 11.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H306" s="64" t="inlineStr">
@@ -44722,7 +44724,7 @@
       </c>
       <c r="AC306" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD306" t="inlineStr">
@@ -44776,13 +44778,13 @@
       <c r="G307" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with DOTTIE Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in White tones, the Fabric, Stainless Steel, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+DOTTIE Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent stool is made to fit naturally into the room. Crafted from Fabric, Stainless Steel, Engineered Wood, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 15"W X 15"D X 18"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Upholstered in velvet-like fabric&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 11.79 lbs&lt;/p&gt;</t>
+Color: Black or White&lt;br&gt;
+Weight: 11.9 or 11.79 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H307" s="64" t="inlineStr">
@@ -44868,7 +44870,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -44927,8 +44929,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Teddy-like Fabric, Solid Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
-Weight: 14.77 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 14.77 or 14.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H308" s="66" t="inlineStr">
@@ -45014,7 +45016,7 @@
       </c>
       <c r="AC308" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD308" t="inlineStr">
@@ -45068,13 +45070,13 @@
       <c r="G309" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JANETTA Stool brings a Contemporary look to your home with a refined, comfortable feel. As a accent stool, it is designed to complement your space. The Teddy-like Fabric, Solid Wood construction is complemented by Green tones for a polished look.&lt;br&gt;
+Make the room feel complete with JANETTA Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Brown tones, the Teddy-like Fabric, Solid Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 18"W X 18"D X 19.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Teddy-like Fabric, Solid Wood.&lt;br&gt;
-Color: Green&lt;br&gt;
-Weight: 14.77 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 14.77 or 14.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H309" s="66" t="inlineStr">
@@ -45160,7 +45162,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD309" t="inlineStr">
@@ -45214,13 +45216,13 @@
       <c r="G310" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with JANETTA Stool, styled in Contemporary and designed for everyday comfort. This accent stool is made to fit naturally into the room. With Teddy-like Fabric, Solid Wood and Saddle Brown tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with JANETTA Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Brown tones, the Teddy-like Fabric, Solid Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 18"W X 18"D X 19.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Teddy-like Fabric, Solid Wood.&lt;br&gt;
-Color: Saddle Brown&lt;br&gt;
-Weight: 14.88 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 14.77 or 14.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H310" s="66" t="inlineStr">
@@ -45306,7 +45308,7 @@
       </c>
       <c r="AC310" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD310" t="inlineStr">
@@ -45360,13 +45362,13 @@
       <c r="G311" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JANETTA Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent stool, it pairs well with a wide range of interiors. Crafted from Teddy-like Fabric, Solid Wood, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Make the room feel complete with JANETTA Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Brown tones, the Teddy-like Fabric, Solid Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 18"W X 18"D X 19.5"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Teddy-like Fabric, Solid Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 14.77 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 14.77 or 14.88 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H311" s="66" t="inlineStr">
@@ -45452,7 +45454,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD311" t="inlineStr">
@@ -45509,8 +45511,8 @@
 Make the room feel complete with KRYSTEN Storage Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Green tones, the Chenille Fabric, Stainless Steel, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 15"W X 15"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Chenille Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Green&lt;br&gt;
-Weight: 15.43 lbs&lt;/p&gt;</t>
+Color: Green or Silver Gray or Beige&lt;br&gt;
+Weight: 15.43 or 15.65 or 14.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H312" s="36" t="inlineStr">
@@ -45596,7 +45598,7 @@
       </c>
       <c r="AC312" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD312" t="inlineStr">
@@ -45650,11 +45652,11 @@
       <c r="G313" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KRYSTEN Storage Stool brings a Contemporary look to your home with a refined, comfortable feel. As a accent stool, it is designed to complement your space. The Chenille Fabric, Stainless Steel, Engineered Wood construction is complemented by Silver Gray tones for a polished look.&lt;br&gt;
+Make the room feel complete with KRYSTEN Storage Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Green tones, the Chenille Fabric, Stainless Steel, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 15"W X 15"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Chenille Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Silver Gray&lt;br&gt;
-Weight: 15.65 lbs&lt;/p&gt;</t>
+Color: Green or Silver Gray or Beige&lt;br&gt;
+Weight: 15.43 or 15.65 or 14.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H313" s="36" t="inlineStr">
@@ -45740,7 +45742,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD313" t="inlineStr">
@@ -45794,11 +45796,11 @@
       <c r="G314" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with KRYSTEN Storage Stool, styled in Contemporary and designed for everyday comfort. This accent stool is made to fit naturally into the room. With Chenille Fabric, Stainless Steel, Engineered Wood and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with KRYSTEN Storage Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Green tones, the Chenille Fabric, Stainless Steel, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 15"W X 15"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Chenille Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 14.21 lbs&lt;/p&gt;</t>
+Color: Green or Silver Gray or Beige&lt;br&gt;
+Weight: 15.43 or 15.65 or 14.21 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H314" s="36" t="inlineStr">
@@ -45884,7 +45886,7 @@
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD314" t="inlineStr">
@@ -45941,8 +45943,8 @@
 THISBE Stool brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent stool, it pairs well with a wide range of interiors. The Fabric, Engineered Wood construction is complemented by Brown tones for a polished look.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Brown&lt;br&gt;
-Weight: 13.99 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 13.99 or 13.55 or 13.88 or 13.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H315" s="42" t="inlineStr">
@@ -46028,7 +46030,7 @@
       </c>
       <c r="AC315" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD315" t="inlineStr">
@@ -46082,11 +46084,11 @@
       <c r="G316" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with THISBE Stool, styled in Contemporary and designed for everyday comfort. As a accent stool, it is designed to complement your space. With Fabric, Engineered Wood and Green tones, it blends structure and softness in one clean profile.&lt;br&gt;
+THISBE Stool brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent stool, it pairs well with a wide range of interiors. The Fabric, Engineered Wood construction is complemented by Brown tones for a polished look.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Green&lt;br&gt;
-Weight: 13.55 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 13.99 or 13.55 or 13.88 or 13.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H316" s="42" t="inlineStr">
@@ -46172,7 +46174,7 @@
       </c>
       <c r="AC316" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD316" t="inlineStr">
@@ -46226,11 +46228,11 @@
       <c r="G317" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-THISBE Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent stool is made to fit naturally into the room. Crafted from Fabric, Engineered Wood, it is finished in Saddle Brown tones that pair easily with surrounding decor.&lt;br&gt;
+THISBE Stool brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent stool, it pairs well with a wide range of interiors. The Fabric, Engineered Wood construction is complemented by Brown tones for a polished look.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Saddle Brown&lt;br&gt;
-Weight: 13.88 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 13.99 or 13.55 or 13.88 or 13.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H317" s="42" t="inlineStr">
@@ -46316,7 +46318,7 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD317" t="inlineStr">
@@ -46370,11 +46372,11 @@
       <c r="G318" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with THISBE Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Beige tones, the Fabric, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+THISBE Stool brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent stool, it pairs well with a wide range of interiors. The Fabric, Engineered Wood construction is complemented by Brown tones for a polished look.&lt;br&gt;
 Product Dimensions: 17.5"W X 17.5"D X 19"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 13.77 lbs&lt;/p&gt;</t>
+Color: Brown or Green or Saddle Brown or Beige&lt;br&gt;
+Weight: 13.99 or 13.55 or 13.88 or 13.77 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H318" s="42" t="inlineStr">
@@ -46460,7 +46462,7 @@
       </c>
       <c r="AC318" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD318" t="inlineStr">
@@ -46517,8 +46519,8 @@
 YOLANDA Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent stool is made to fit naturally into the room. Crafted from Fabric, Stainless Steel, Engineered Wood, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 16"W X 16"D X 18"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
-Weight: 9.47 lbs&lt;/p&gt;</t>
+Color: Dark Gray or Green or Gray or Beige&lt;br&gt;
+Weight: 9.47 or 9.59 or 9.7 or 9.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H319" s="57" t="inlineStr">
@@ -46604,7 +46606,7 @@
       </c>
       <c r="AC319" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD319" t="inlineStr">
@@ -46658,11 +46660,11 @@
       <c r="G320" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with YOLANDA Stool and its Contemporary character. Built as a accent stool, it pairs well with a wide range of interiors. Finished in Green tones, the Fabric, Stainless Steel, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+YOLANDA Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent stool is made to fit naturally into the room. Crafted from Fabric, Stainless Steel, Engineered Wood, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 16"W X 16"D X 18"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Green&lt;br&gt;
-Weight: 9.59 lbs&lt;/p&gt;</t>
+Color: Dark Gray or Green or Gray or Beige&lt;br&gt;
+Weight: 9.47 or 9.59 or 9.7 or 9.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H320" s="57" t="inlineStr">
@@ -46748,7 +46750,7 @@
       </c>
       <c r="AC320" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD320" t="inlineStr">
@@ -46802,11 +46804,11 @@
       <c r="G321" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-YOLANDA Stool brings a Contemporary look to your home with a refined, comfortable feel. As a accent stool, it is designed to complement your space. The Fabric, Stainless Steel, Engineered Wood construction is complemented by Gray tones for a polished look.&lt;br&gt;
+YOLANDA Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent stool is made to fit naturally into the room. Crafted from Fabric, Stainless Steel, Engineered Wood, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 16"W X 16"D X 18"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 9.7 lbs&lt;/p&gt;</t>
+Color: Dark Gray or Green or Gray or Beige&lt;br&gt;
+Weight: 9.47 or 9.59 or 9.7 or 9.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H321" s="57" t="inlineStr">
@@ -46892,7 +46894,7 @@
       </c>
       <c r="AC321" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD321" t="inlineStr">
@@ -46946,11 +46948,11 @@
       <c r="G322" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with YOLANDA Stool, styled in Contemporary and designed for everyday comfort. This accent stool is made to fit naturally into the room. With Fabric, Stainless Steel, Engineered Wood and Beige tones, it blends structure and softness in one clean profile.&lt;br&gt;
+YOLANDA Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent stool is made to fit naturally into the room. Crafted from Fabric, Stainless Steel, Engineered Wood, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 16"W X 16"D X 18"H&lt;/p&gt;
 &lt;p&gt;Materials: Fabric, Stainless Steel, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 9.58 lbs&lt;/p&gt;</t>
+Color: Dark Gray or Green or Gray or Beige&lt;br&gt;
+Weight: 9.47 or 9.59 or 9.7 or 9.58 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H322" s="57" t="inlineStr">
@@ -47036,7 +47038,7 @@
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD322" t="inlineStr">
@@ -47182,7 +47184,7 @@
       </c>
       <c r="AC323" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD323" t="inlineStr">
@@ -47328,7 +47330,7 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD324" t="inlineStr">
@@ -47474,7 +47476,7 @@
       </c>
       <c r="AC325" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD325" t="inlineStr">
@@ -47531,7 +47533,7 @@
 BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Blue or Purple or Red or Silver or Multi&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -47622,7 +47624,7 @@
       </c>
       <c r="AC326" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD326" t="inlineStr">
@@ -47676,10 +47678,10 @@
       <c r="G327" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BELLE 20" X 20" Pillow (2 or CTN) and its Contemporary character. As a accent pillow, it is designed to complement your space. Finished in Blue tones, the 100% Polyester Velvet build balances durability with visual appeal.&lt;br&gt;
+BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Beige or Blue or Purple or Red or Silver or Multi&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -47770,7 +47772,7 @@
       </c>
       <c r="AC327" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD327" t="inlineStr">
@@ -47824,10 +47826,10 @@
       <c r="G328" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELLE 20" X 20" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. This accent pillow is made to fit naturally into the room. The 100% Polyester Velvet construction is complemented by Purple tones for a polished look.&lt;br&gt;
+BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Purple&lt;br&gt;
+Color: Beige or Blue or Purple or Red or Silver or Multi&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -47918,7 +47920,7 @@
       </c>
       <c r="AC328" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD328" t="inlineStr">
@@ -47972,10 +47974,10 @@
       <c r="G329" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with BELLE 20" X 20" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. Built as a accent pillow, it pairs well with a wide range of interiors. With 100% Polyester Velvet and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Beige or Blue or Purple or Red or Silver or Multi&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -48066,7 +48068,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD329" t="inlineStr">
@@ -48120,10 +48122,10 @@
       <c r="G330" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent pillow, it is designed to complement your space. Crafted from 100% Polyester Velvet, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
+BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Beige or Blue or Purple or Red or Silver or Multi&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -48214,7 +48216,7 @@
       </c>
       <c r="AC330" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD330" t="inlineStr">
@@ -48268,10 +48270,10 @@
       <c r="G331" s="57" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with BELLE 20" X 20" Pillow (2 or CTN) and its Contemporary character. This accent pillow is made to fit naturally into the room. Finished in Multi tones, the 100% Polyester Velvet build balances durability with visual appeal.&lt;br&gt;
+BELLE 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Multi&lt;br&gt;
+Color: Beige or Blue or Purple or Red or Silver or Multi&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -48362,7 +48364,7 @@
       </c>
       <c r="AC331" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD331" t="inlineStr">
@@ -48508,7 +48510,7 @@
       </c>
       <c r="AC332" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD332" t="inlineStr">
@@ -48654,7 +48656,7 @@
       </c>
       <c r="AC333" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD333" t="inlineStr">
@@ -48801,7 +48803,7 @@
       </c>
       <c r="AC334" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD334" t="inlineStr">
@@ -48947,7 +48949,7 @@
       </c>
       <c r="AC335" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD335" t="inlineStr">
@@ -49002,9 +49004,9 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 20" X 20"&lt;/p&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49091,7 +49093,7 @@
       </c>
       <c r="AC336" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD336" t="inlineStr">
@@ -49145,10 +49147,10 @@
       <c r="G337" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CAPARICA 20" X 20" Pillow and its Contemporary character. Built as a accent pillow, it pairs well with a wide range of interiors. Finished in Charcoal tones, the 100% Polyester build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 20" X 20"&lt;/p&gt;
+CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Charcoal&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49235,7 +49237,7 @@
       </c>
       <c r="AC337" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD337" t="inlineStr">
@@ -49289,10 +49291,10 @@
       <c r="G338" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA 20" X 20" Pillow brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The 100% Polyester construction is complemented by Blush tones for a polished look.&lt;br&gt;
-Product Dimensions: 20" X 20"&lt;/p&gt;
+CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Blush&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49379,7 +49381,7 @@
       </c>
       <c r="AC338" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD338" t="inlineStr">
@@ -49433,10 +49435,10 @@
       <c r="G339" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CAPARICA 20" X 20" Pillow, styled in Contemporary and designed for everyday comfort. This accent pillow is made to fit naturally into the room. With 100% Polyester and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 20" X 20"&lt;/p&gt;
+CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49523,7 +49525,7 @@
       </c>
       <c r="AC339" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD339" t="inlineStr">
@@ -49577,10 +49579,10 @@
       <c r="G340" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester, it is finished in Off-White tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 20" X 20"&lt;/p&gt;
+CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Off-White&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49671,7 +49673,7 @@
       </c>
       <c r="AC340" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD340" t="inlineStr">
@@ -49725,10 +49727,10 @@
       <c r="G341" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CAPARICA 20" X 20" Pillow and its Contemporary character. As a accent pillow, it is designed to complement your space. Finished in Gold tones, the 100% Polyester build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 20" X 20" X 3"&lt;/p&gt;
+CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Gold&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49815,7 +49817,7 @@
       </c>
       <c r="AC341" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD341" t="inlineStr">
@@ -49869,10 +49871,10 @@
       <c r="G342" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA 20" X 20" Pillow brings a Contemporary look to your home with a refined, comfortable feel. This accent pillow is made to fit naturally into the room. The 100% Polyester construction is complemented by Teal tones for a polished look.&lt;br&gt;
-Product Dimensions: 20" X 20" X 3"&lt;/p&gt;
+CAPARICA 20" X 20" Pillow adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester, it is finished in Black tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 20" X 20" / 20" X 20" X 3"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Teal&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White or Gold or Teal&lt;br&gt;
 Weight: 2 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -49959,7 +49961,7 @@
       </c>
       <c r="AC342" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD342" t="inlineStr">
@@ -50016,7 +50018,7 @@
 CAPARICA Throw brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The 100% Polyester construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Black&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50103,7 +50105,7 @@
       </c>
       <c r="AC343" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD343" t="inlineStr">
@@ -50157,10 +50159,10 @@
       <c r="G344" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with CAPARICA Throw, styled in Contemporary and designed for everyday comfort. This accent pillow is made to fit naturally into the room. With 100% Polyester and Charcoal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+CAPARICA Throw brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The 100% Polyester construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Charcoal&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50247,7 +50249,7 @@
       </c>
       <c r="AC344" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD344" t="inlineStr">
@@ -50301,10 +50303,10 @@
       <c r="G345" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA Throw adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester, it is finished in Blush tones that pair easily with surrounding decor.&lt;br&gt;
+CAPARICA Throw brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The 100% Polyester construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Blush&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50391,7 +50393,7 @@
       </c>
       <c r="AC345" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD345" t="inlineStr">
@@ -50445,10 +50447,10 @@
       <c r="G346" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with CAPARICA Throw and its Contemporary character. As a accent pillow, it is designed to complement your space. Finished in Silver tones, the 100% Polyester build balances durability with visual appeal.&lt;br&gt;
+CAPARICA Throw brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The 100% Polyester construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50535,7 +50537,7 @@
       </c>
       <c r="AC346" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD346" t="inlineStr">
@@ -50589,10 +50591,10 @@
       <c r="G347" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA Throw brings a Contemporary look to your home with a refined, comfortable feel. This accent pillow is made to fit naturally into the room. The 100% Polyester construction is complemented by Off-White tones for a polished look.&lt;br&gt;
+CAPARICA Throw brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The 100% Polyester construction is complemented by Black tones for a polished look.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Off-White&lt;br&gt;
+Color: Black or Charcoal or Blush or Silver or Off-White&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -50683,7 +50685,7 @@
       </c>
       <c r="AC347" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD347" t="inlineStr">
@@ -50829,7 +50831,7 @@
       </c>
       <c r="AC348" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD348" t="inlineStr">
@@ -50975,7 +50977,7 @@
       </c>
       <c r="AC349" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD349" t="inlineStr">
@@ -51121,7 +51123,7 @@
       </c>
       <c r="AC350" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD350" t="inlineStr">
@@ -51262,7 +51264,7 @@
       </c>
       <c r="AC351" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD351" t="inlineStr">
@@ -51408,7 +51410,7 @@
       </c>
       <c r="AC352" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD352" t="inlineStr">
@@ -51554,7 +51556,7 @@
       </c>
       <c r="AC353" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD353" t="inlineStr">
@@ -51700,7 +51702,7 @@
       </c>
       <c r="AC354" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD354" t="inlineStr">
@@ -51846,7 +51848,7 @@
       </c>
       <c r="AC355" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD355" t="inlineStr">
@@ -51992,7 +51994,7 @@
       </c>
       <c r="AC356" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD356" t="inlineStr">
@@ -52138,7 +52140,7 @@
       </c>
       <c r="AC357" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD357" t="inlineStr">
@@ -52284,7 +52286,7 @@
       </c>
       <c r="AC358" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD358" t="inlineStr">
@@ -52430,7 +52432,7 @@
       </c>
       <c r="AC359" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD359" t="inlineStr">
@@ -52577,7 +52579,7 @@
       </c>
       <c r="AC360" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD360" t="inlineStr">
@@ -52723,7 +52725,7 @@
       </c>
       <c r="AC361" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD361" t="inlineStr">
@@ -52869,7 +52871,7 @@
       </c>
       <c r="AC362" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD362" t="inlineStr">
@@ -53015,7 +53017,7 @@
       </c>
       <c r="AC363" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD363" t="inlineStr">
@@ -53161,7 +53163,7 @@
       </c>
       <c r="AC364" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD364" t="inlineStr">
@@ -53307,7 +53309,7 @@
       </c>
       <c r="AC365" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD365" t="inlineStr">
@@ -53453,7 +53455,7 @@
       </c>
       <c r="AC366" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD366" t="inlineStr">
@@ -53599,7 +53601,7 @@
       </c>
       <c r="AC367" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD367" t="inlineStr">
@@ -53746,7 +53748,7 @@
       </c>
       <c r="AC368" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD368" t="inlineStr">
@@ -53802,8 +53804,8 @@
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with JORJA 20" X 20" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With 80% Polyester, 20% Linen and Beige or Purple tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
-&lt;p&gt;Materials: 80% Polyester, 20% Linen.&lt;br&gt;
-Color: Beige or Purple&lt;br&gt;
+&lt;p&gt;Materials: 80% Polyester, 20% Linen or 100% Cotton.&lt;br&gt;
+Color: Beige or Purple or Purple&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -53894,7 +53896,7 @@
       </c>
       <c r="AC369" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD369" t="inlineStr">
@@ -53948,10 +53950,10 @@
       <c r="G370" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JORJA 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Cotton, it is finished in Purple tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with JORJA 20" X 20" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With 80% Polyester, 20% Linen and Beige or Purple tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
-&lt;p&gt;Materials: 100% Cotton.&lt;br&gt;
-Color: Purple&lt;br&gt;
+&lt;p&gt;Materials: 80% Polyester, 20% Linen or 100% Cotton.&lt;br&gt;
+Color: Beige or Purple or Purple&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -54042,7 +54044,7 @@
       </c>
       <c r="AC370" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD370" t="inlineStr">
@@ -54188,7 +54190,7 @@
       </c>
       <c r="AC371" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD371" t="inlineStr">
@@ -54334,7 +54336,7 @@
       </c>
       <c r="AC372" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD372" t="inlineStr">
@@ -54391,7 +54393,7 @@
 KARI 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent pillow, it is designed to complement your space. Crafted from Linen, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Dark Gray&lt;br&gt;
+Color: Dark Gray or Silver or Orange or Teal&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -54482,7 +54484,7 @@
       </c>
       <c r="AC373" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD373" t="inlineStr">
@@ -54536,10 +54538,10 @@
       <c r="G374" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with KARI 20" X 20" Pillow (2 or CTN) and its Contemporary character. This accent pillow is made to fit naturally into the room. Finished in Silver tones, the Linen build balances durability with visual appeal.&lt;br&gt;
+KARI 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent pillow, it is designed to complement your space. Crafted from Linen, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Dark Gray or Silver or Orange or Teal&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -54630,7 +54632,7 @@
       </c>
       <c r="AC374" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD374" t="inlineStr">
@@ -54684,10 +54686,10 @@
       <c r="G375" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-KARI 20" X 20" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent pillow, it pairs well with a wide range of interiors. The Linen construction is complemented by Orange tones for a polished look.&lt;br&gt;
+KARI 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent pillow, it is designed to complement your space. Crafted from Linen, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Orange&lt;br&gt;
+Color: Dark Gray or Silver or Orange or Teal&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -54778,7 +54780,7 @@
       </c>
       <c r="AC375" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD375" t="inlineStr">
@@ -54832,10 +54834,10 @@
       <c r="G376" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with KARI 20" X 20" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With Linen and Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
+KARI 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent pillow, it is designed to complement your space. Crafted from Linen, it is finished in Dark Gray tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Teal&lt;br&gt;
+Color: Dark Gray or Silver or Orange or Teal&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -54926,7 +54928,7 @@
       </c>
       <c r="AC376" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD376" t="inlineStr">
@@ -55072,7 +55074,7 @@
       </c>
       <c r="AC377" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD377" t="inlineStr">
@@ -55218,7 +55220,7 @@
       </c>
       <c r="AC378" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD378" t="inlineStr">
@@ -55364,7 +55366,7 @@
       </c>
       <c r="AC379" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD379" t="inlineStr">
@@ -55510,7 +55512,7 @@
       </c>
       <c r="AC380" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD380" t="inlineStr">
@@ -55656,7 +55658,7 @@
       </c>
       <c r="AC381" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD381" t="inlineStr">
@@ -55802,7 +55804,7 @@
       </c>
       <c r="AC382" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD382" t="inlineStr">
@@ -55948,7 +55950,7 @@
       </c>
       <c r="AC383" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD383" t="inlineStr">
@@ -56005,7 +56007,7 @@
 LEYLA 20" X 20" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. This accent pillow is made to fit naturally into the room. The Jacquard Fabric construction is complemented by Silver tones for a polished look.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Jacquard Fabric.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Silver or Green&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -56096,7 +56098,7 @@
       </c>
       <c r="AC384" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD384" t="inlineStr">
@@ -56150,10 +56152,10 @@
       <c r="G385" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with LEYLA 20" X 20" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. Built as a accent pillow, it pairs well with a wide range of interiors. With Jacquard Fabric and Green tones, it blends structure and softness in one clean profile.&lt;br&gt;
+LEYLA 20" X 20" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. This accent pillow is made to fit naturally into the room. The Jacquard Fabric construction is complemented by Silver tones for a polished look.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Jacquard Fabric.&lt;br&gt;
-Color: Green&lt;br&gt;
+Color: Silver or Green&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -56244,7 +56246,7 @@
       </c>
       <c r="AC385" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD385" t="inlineStr">
@@ -56390,7 +56392,7 @@
       </c>
       <c r="AC386" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD386" t="inlineStr">
@@ -56538,7 +56540,7 @@
       </c>
       <c r="AC387" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD387" t="inlineStr">
@@ -56592,7 +56594,7 @@
       <c r="G388" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with LINA 20" X 20" Pillow (2 or CTN) and its Transitional character. This accent pillow is made to fit naturally into the room. Finished in Ivory or Pink tones, the 100% Polyester Velvet build balances durability with visual appeal.&lt;br&gt;
+LINA 20" X 20" Pillow (2 or CTN) adds a Transitional touch while keeping the room feeling warm and welcoming. As a accent pillow, it is designed to complement your space. Crafted from 100% Polyester Velvet, it is finished in Ivory or Pink tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
 Color: Ivory or Pink&lt;br&gt;
@@ -56686,7 +56688,7 @@
       </c>
       <c r="AC388" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD388" t="inlineStr">
@@ -56832,7 +56834,7 @@
       </c>
       <c r="AC389" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD389" t="inlineStr">
@@ -56978,7 +56980,7 @@
       </c>
       <c r="AC390" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD390" t="inlineStr">
@@ -57035,7 +57037,7 @@
 Elevate your space with LORRIE 20" X 20" Pillow (2 or CTN), styled in Novelty and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With 100% Polyester Velvet and White or Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: White or Teal&lt;br&gt;
+Color: White or Teal or White or Blue&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -57126,7 +57128,7 @@
       </c>
       <c r="AC391" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD391" t="inlineStr">
@@ -57180,10 +57182,10 @@
       <c r="G392" s="39" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LORRIE 20" X 20" Pillow (2 or CTN) adds a Novelty touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from 100% Polyester Velvet, it is finished in White or Blue tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with LORRIE 20" X 20" Pillow (2 or CTN), styled in Novelty and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With 100% Polyester Velvet and White or Teal tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: White or Blue&lt;br&gt;
+Color: White or Teal or White or Blue&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -57274,7 +57276,7 @@
       </c>
       <c r="AC392" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD392" t="inlineStr">
@@ -57420,7 +57422,7 @@
       </c>
       <c r="AC393" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD393" t="inlineStr">
@@ -57566,7 +57568,7 @@
       </c>
       <c r="AC394" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD394" t="inlineStr">
@@ -57712,7 +57714,7 @@
       </c>
       <c r="AC395" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD395" t="inlineStr">
@@ -57858,7 +57860,7 @@
       </c>
       <c r="AC396" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD396" t="inlineStr">
@@ -58004,7 +58006,7 @@
       </c>
       <c r="AC397" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD397" t="inlineStr">
@@ -58061,7 +58063,7 @@
 Elevate your space with MALIA 17" X 17" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With Polyester and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 18" X 18"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Yellow&lt;br&gt;
 Weight: 4.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -58152,7 +58154,7 @@
       </c>
       <c r="AC398" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD398" t="inlineStr">
@@ -58206,10 +58208,10 @@
       <c r="G399" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MALIA 17" X 17" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from Polyester, it is finished in Red tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with MALIA 17" X 17" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With Polyester and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 18" X 18"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Yellow&lt;br&gt;
 Weight: 4.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -58300,7 +58302,7 @@
       </c>
       <c r="AC399" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD399" t="inlineStr">
@@ -58354,10 +58356,10 @@
       <c r="G400" s="48" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with MALIA 17" X 17" Pillow (2 or CTN) and its Contemporary character. Built as a accent pillow, it pairs well with a wide range of interiors. Finished in Yellow tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
+Elevate your space with MALIA 17" X 17" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With Polyester and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 18" X 18"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Yellow&lt;br&gt;
+Color: Blue or Red or Yellow&lt;br&gt;
 Weight: 4.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -58448,7 +58450,7 @@
       </c>
       <c r="AC400" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD400" t="inlineStr">
@@ -58505,7 +58507,7 @@
 MALIA 21" X 21" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The Polyester construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 22" X 22"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Red or Yellow&lt;br&gt;
 Weight: 7.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -58596,7 +58598,7 @@
       </c>
       <c r="AC401" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD401" t="inlineStr">
@@ -58650,10 +58652,10 @@
       <c r="G402" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with MALIA 21" X 21" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. This accent pillow is made to fit naturally into the room. With Polyester and Red tones, it blends structure and softness in one clean profile.&lt;br&gt;
+MALIA 21" X 21" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The Polyester construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 22" X 22"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Red&lt;br&gt;
+Color: Blue or Red or Yellow&lt;br&gt;
 Weight: 7.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -58744,7 +58746,7 @@
       </c>
       <c r="AC402" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD402" t="inlineStr">
@@ -58798,10 +58800,10 @@
       <c r="G403" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-MALIA 21" X 21" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from Polyester, it is finished in Yellow tones that pair easily with surrounding decor.&lt;br&gt;
+MALIA 21" X 21" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The Polyester construction is complemented by Blue tones for a polished look.&lt;br&gt;
 Product Dimensions: 22" X 22"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Yellow&lt;br&gt;
+Color: Blue or Red or Yellow&lt;br&gt;
 Weight: 7.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -58892,7 +58894,7 @@
       </c>
       <c r="AC403" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD403" t="inlineStr">
@@ -59039,7 +59041,7 @@
       </c>
       <c r="AC404" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD404" t="inlineStr">
@@ -59185,7 +59187,7 @@
       </c>
       <c r="AC405" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD405" t="inlineStr">
@@ -59331,7 +59333,7 @@
       </c>
       <c r="AC406" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD406" t="inlineStr">
@@ -59477,7 +59479,7 @@
       </c>
       <c r="AC407" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD407" t="inlineStr">
@@ -59623,7 +59625,7 @@
       </c>
       <c r="AC408" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD408" t="inlineStr">
@@ -59764,7 +59766,7 @@
       </c>
       <c r="AC409" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD409" t="inlineStr">
@@ -59910,7 +59912,7 @@
       </c>
       <c r="AC410" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD410" t="inlineStr">
@@ -59967,7 +59969,7 @@
 Make the room feel complete with RICKI 17" X 17" Pillow (2 or CTN) and its Contemporary character. This accent pillow is made to fit naturally into the room. Finished in Blue tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 18" X 18"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Brown&lt;br&gt;
 Weight: 4.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60058,7 +60060,7 @@
       </c>
       <c r="AC411" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD411" t="inlineStr">
@@ -60112,10 +60114,10 @@
       <c r="G412" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RICKI 17" X 17" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. Built as a accent pillow, it pairs well with a wide range of interiors. The Polyester construction is complemented by Brown tones for a polished look.&lt;br&gt;
+Make the room feel complete with RICKI 17" X 17" Pillow (2 or CTN) and its Contemporary character. This accent pillow is made to fit naturally into the room. Finished in Blue tones, the Polyester build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 18" X 18"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Brown&lt;br&gt;
+Color: Blue or Brown&lt;br&gt;
 Weight: 4.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60206,7 +60208,7 @@
       </c>
       <c r="AC412" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD412" t="inlineStr">
@@ -60263,7 +60265,7 @@
 Elevate your space with RICKI 21" X 21" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With Polyester and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 22" X 22"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Blue&lt;br&gt;
+Color: Blue or Brown&lt;br&gt;
 Weight: 7.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60354,7 +60356,7 @@
       </c>
       <c r="AC413" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD413" t="inlineStr">
@@ -60408,10 +60410,10 @@
       <c r="G414" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RICKI 21" X 21" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from Polyester, it is finished in Brown tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with RICKI 21" X 21" Pillow (2 or CTN), styled in Contemporary and designed for everyday comfort. As a accent pillow, it is designed to complement your space. With Polyester and Blue tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 22" X 22"&lt;/p&gt;
 &lt;p&gt;Materials: Polyester.&lt;br&gt;
-Color: Brown&lt;br&gt;
+Color: Blue or Brown&lt;br&gt;
 Weight: 7.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60502,7 +60504,7 @@
       </c>
       <c r="AC414" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD414" t="inlineStr">
@@ -60559,7 +60561,7 @@
 RINA 20" X 20" Pillow (2 or CTN) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Light Pink tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Light Pink&lt;br&gt;
+Color: Light Pink or Beige or Purple&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60650,7 +60652,7 @@
       </c>
       <c r="AC415" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD415" t="inlineStr">
@@ -60704,10 +60706,10 @@
       <c r="G416" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with RINA 20" X 20" Pillow (2 or CTN) and its Transitional character. As a accent pillow, it is designed to complement your space. Finished in Beige tones, the 100% Polyester Velvet build balances durability with visual appeal.&lt;br&gt;
+RINA 20" X 20" Pillow (2 or CTN) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Light Pink tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Light Pink or Beige or Purple&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60798,7 +60800,7 @@
       </c>
       <c r="AC416" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD416" t="inlineStr">
@@ -60852,10 +60854,10 @@
       <c r="G417" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-RINA 20" X 20" Pillow (2 or CTN) brings a Transitional look to your home with a refined, comfortable feel. This accent pillow is made to fit naturally into the room. The 100% Polyester Velvet construction is complemented by Purple tones for a polished look.&lt;br&gt;
+RINA 20" X 20" Pillow (2 or CTN) adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a accent pillow, it pairs well with a wide range of interiors. Crafted from 100% Polyester Velvet, it is finished in Light Pink tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester Velvet.&lt;br&gt;
-Color: Purple&lt;br&gt;
+Color: Light Pink or Beige or Purple&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -60946,7 +60948,7 @@
       </c>
       <c r="AC417" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD417" t="inlineStr">
@@ -61092,7 +61094,7 @@
       </c>
       <c r="AC418" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD418" t="inlineStr">
@@ -61238,7 +61240,7 @@
       </c>
       <c r="AC419" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD419" t="inlineStr">
@@ -61384,7 +61386,7 @@
       </c>
       <c r="AC420" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD420" t="inlineStr">
@@ -61530,7 +61532,7 @@
       </c>
       <c r="AC421" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD421" t="inlineStr">
@@ -61671,7 +61673,7 @@
       </c>
       <c r="AC422" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD422" t="inlineStr">
@@ -61812,7 +61814,7 @@
       </c>
       <c r="AC423" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD423" t="inlineStr">
@@ -61958,7 +61960,7 @@
       </c>
       <c r="AC424" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD424" t="inlineStr">
@@ -62104,7 +62106,7 @@
       </c>
       <c r="AC425" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD425" t="inlineStr">
@@ -62250,7 +62252,7 @@
       </c>
       <c r="AC426" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD426" t="inlineStr">
@@ -62396,7 +62398,7 @@
       </c>
       <c r="AC427" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD427" t="inlineStr">
@@ -62542,7 +62544,7 @@
       </c>
       <c r="AC428" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD428" t="inlineStr">
@@ -62683,7 +62685,7 @@
       </c>
       <c r="AC429" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD429" t="inlineStr">
@@ -62740,7 +62742,7 @@
 TRUDY 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from Linen, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Beige&lt;br&gt;
+Color: Beige or Gray or Silver&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -62831,7 +62833,7 @@
       </c>
       <c r="AC430" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD430" t="inlineStr">
@@ -62885,10 +62887,10 @@
       <c r="G431" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with TRUDY 20" X 20" Pillow (2 or CTN) and its Contemporary character. Built as a accent pillow, it pairs well with a wide range of interiors. Finished in Gray tones, the Linen build balances durability with visual appeal.&lt;br&gt;
+TRUDY 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from Linen, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Gray&lt;br&gt;
+Color: Beige or Gray or Silver&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -62979,7 +62981,7 @@
       </c>
       <c r="AC431" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD431" t="inlineStr">
@@ -63033,10 +63035,10 @@
       <c r="G432" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TRUDY 20" X 20" Pillow (2 or CTN) brings a Contemporary look to your home with a refined, comfortable feel. As a accent pillow, it is designed to complement your space. The Linen construction is complemented by Silver tones for a polished look.&lt;br&gt;
+TRUDY 20" X 20" Pillow (2 or CTN) adds a Contemporary touch while keeping the room feeling warm and welcoming. This accent pillow is made to fit naturally into the room. Crafted from Linen, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 20" X 20"&lt;/p&gt;
 &lt;p&gt;Materials: Linen.&lt;br&gt;
-Color: Silver&lt;br&gt;
+Color: Beige or Gray or Silver&lt;br&gt;
 Weight: 5 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -63127,7 +63129,7 @@
       </c>
       <c r="AC432" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD432" t="inlineStr">
@@ -63268,7 +63270,7 @@
       </c>
       <c r="AC433" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD433" t="inlineStr">
@@ -63408,7 +63410,7 @@
       </c>
       <c r="AC434" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD434" t="inlineStr">
@@ -63544,7 +63546,7 @@
       </c>
       <c r="AC435" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD435" t="inlineStr">
@@ -63602,8 +63604,8 @@
 Product Dimensions: 47 1/4"L X 18"W X 60 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Silver&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Silver or White&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -63690,7 +63692,7 @@
       </c>
       <c r="AC436" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD436" t="inlineStr">
@@ -63744,12 +63746,12 @@
       <c r="G437" s="64" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with ATHY Vanity w/ Stool and its Transitional character. This accent vanity is made to fit naturally into the room. Finished in White tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+ATHY Vanity w/ Stool adds a Transitional touch while keeping the room feeling warm and welcoming. As a accent vanity, it is designed to complement your space. Crafted from Mirror, Solid Wood, Wood Veneer, it is finished in Silver tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 60 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Silver or White&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -63836,7 +63838,7 @@
       </c>
       <c r="AC437" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD437" t="inlineStr">
@@ -63980,7 +63982,7 @@
       </c>
       <c r="AC438" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD438" t="inlineStr">
@@ -64119,7 +64121,7 @@
       </c>
       <c r="AC439" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD439" t="inlineStr">
@@ -64263,7 +64265,7 @@
       </c>
       <c r="AC440" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD440" t="inlineStr">
@@ -64402,7 +64404,7 @@
       </c>
       <c r="AC441" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD441" t="inlineStr">
@@ -64460,8 +64462,8 @@
 Product Dimensions: 42"L X 21 1/2"W X 29 7/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Silver&lt;br&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Silver or White&lt;br&gt;
 Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -64548,7 +64550,7 @@
       </c>
       <c r="AC442" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD442" t="inlineStr">
@@ -64602,13 +64604,12 @@
       <c r="G443" s="51" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-JOYCE Vanity w/ Stool brings a Transitional look to your home with a refined, comfortable feel. Built as a accent vanity, it pairs well with a wide range of interiors. The Solid Wood, Wood Veneer, construction is complemented by White tones for a polished look.&lt;br&gt;
+Make the room feel complete with JOYCE Vanity w/ Stool and its Transitional character. This accent vanity is made to fit naturally into the room. Finished in Silver tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 42"L X 21 1/2"W X 29 7/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
-- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;br&gt;
-Felt-Lined Top Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+- Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Silver or White&lt;br&gt;
 Weight: 125.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -64695,7 +64696,7 @@
       </c>
       <c r="AC443" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD443" t="inlineStr">
@@ -64752,7 +64753,7 @@
 LISMORE Vanity w/ Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent vanity, it is designed to complement your space. Crafted from Glass, Metal, it is finished in Champagne tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 42"L X 18 3/4"W X 50"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
-Color: Champagne&lt;br&gt;
+Color: Champagne or Chrome&lt;br&gt;
 Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -64839,7 +64840,7 @@
       </c>
       <c r="AC444" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD444" t="inlineStr">
@@ -64893,10 +64894,10 @@
       <c r="G445" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with LISMORE Vanity w/ Stool and its Contemporary character. This accent vanity is made to fit naturally into the room. Finished in Chrome tones, the Glass, Metal build balances durability with visual appeal.&lt;br&gt;
+LISMORE Vanity w/ Stool adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent vanity, it is designed to complement your space. Crafted from Glass, Metal, it is finished in Champagne tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 42"L X 18 3/4"W X 50"H&lt;/p&gt;
 &lt;p&gt;Materials: Glass, Metal.&lt;br&gt;
-Color: Chrome&lt;br&gt;
+Color: Champagne or Chrome&lt;br&gt;
 Weight: 73.7 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -64983,7 +64984,7 @@
       </c>
       <c r="AC445" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD445" t="inlineStr">
@@ -65122,7 +65123,7 @@
       </c>
       <c r="AC446" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD446" t="inlineStr">
@@ -65261,7 +65262,7 @@
       </c>
       <c r="AC447" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD447" t="inlineStr">
@@ -65403,7 +65404,7 @@
       </c>
       <c r="AC448" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD448" t="inlineStr">
@@ -65544,7 +65545,7 @@
       </c>
       <c r="AC449" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD449" t="inlineStr">
@@ -65603,8 +65604,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Obsidian Gray&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Luminous White&lt;br&gt;
 Weight: 173.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -65693,7 +65694,7 @@
       </c>
       <c r="AC450" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD450" t="inlineStr">
@@ -65747,13 +65748,13 @@
       <c r="G451" s="59" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-STEPHANIE Vanity Set adds a Glam touch while keeping the room feeling warm and welcoming. This accent vanity is made to fit naturally into the room. Crafted from Mirror, Solid Wood, Wood Veneer, it is finished in Luminous White tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with STEPHANIE Vanity Set, styled in Glam and designed for everyday comfort. As a accent vanity, it is designed to complement your space. With Mirror, Solid Wood, Wood Veneer, and Obsidian Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 60"L X 20"W X 59 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Luminous White&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Luminous White&lt;br&gt;
 Weight: 173.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -65842,7 +65843,7 @@
       </c>
       <c r="AC451" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD451" t="inlineStr">
@@ -65982,7 +65983,7 @@
       </c>
       <c r="AC452" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD452" t="inlineStr">
@@ -66041,8 +66042,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Obsidian Gray&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Tiffany Blush or Luminous White&lt;br&gt;
 Weight: 217.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -66127,7 +66128,7 @@
       </c>
       <c r="AC453" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD453" t="inlineStr">
@@ -66181,13 +66182,13 @@
       <c r="G454" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TRACIE Vanity Set brings a Glam look to your home with a refined, comfortable feel. As a accent vanity, it is designed to complement your space. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Tiffany Blush tones for a polished look.&lt;br&gt;
+Make the room feel complete with TRACIE Vanity Set and its Glam character. Built as a accent vanity, it pairs well with a wide range of interiors. Finished in Obsidian Gray tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 74 3/8"L X 31 7/8"W X 60 5/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Tiffany Blush&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Tiffany Blush or Luminous White&lt;br&gt;
 Weight: 217.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -66272,7 +66273,7 @@
       </c>
       <c r="AC454" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD454" t="inlineStr">
@@ -66326,13 +66327,13 @@
       <c r="G455" s="36" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with TRACIE Vanity Set, styled in Glam and designed for everyday comfort. This accent vanity is made to fit naturally into the room. With Mirror, Solid Wood, Wood Veneer, and Luminous White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Make the room feel complete with TRACIE Vanity Set and its Glam character. Built as a accent vanity, it pairs well with a wide range of interiors. Finished in Obsidian Gray tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
 Product Dimensions: 74 3/8"L X 31 7/8"W X 60 5/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Luminous White&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Tiffany Blush or Luminous White&lt;br&gt;
 Weight: 217.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -66417,7 +66418,7 @@
       </c>
       <c r="AC455" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD455" t="inlineStr">
@@ -66475,8 +66476,8 @@
 Product Dimensions: 47 1/4"L X 18"W X 60 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Rose Gold&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rose Gold or Silver or White&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -66567,7 +66568,7 @@
       </c>
       <c r="AC456" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD456" t="inlineStr">
@@ -66621,12 +66622,12 @@
       <c r="G457" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with TRACY Vanity w/ Stool, styled in Transitional and designed for everyday comfort. As a accent vanity, it is designed to complement your space. With Mirror, Solid Wood, Wood Veneer, and Silver tones, it blends structure and softness in one clean profile.&lt;br&gt;
+TRACY Vanity w/ Stool brings a Transitional look to your home with a refined, comfortable feel. Built as a accent vanity, it pairs well with a wide range of interiors. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 60 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Silver&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rose Gold or Silver or White&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -66713,7 +66714,7 @@
       </c>
       <c r="AC457" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD457" t="inlineStr">
@@ -66767,12 +66768,12 @@
       <c r="G458" s="54" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TRACY Vanity w/ Stool adds a Transitional touch while keeping the room feeling warm and welcoming. This accent vanity is made to fit naturally into the room. Crafted from Mirror, Solid Wood, Wood Veneer, it is finished in White tones that pair easily with surrounding decor.&lt;br&gt;
+TRACY Vanity w/ Stool brings a Transitional look to your home with a refined, comfortable feel. Built as a accent vanity, it pairs well with a wide range of interiors. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Rose Gold tones for a polished look.&lt;br&gt;
 Product Dimensions: 47 1/4"L X 18"W X 60 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: White&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Rose Gold or Silver or White&lt;br&gt;
 Weight: 160.6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -66859,7 +66860,7 @@
       </c>
       <c r="AC458" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD458" t="inlineStr">
@@ -66914,13 +66915,13 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Make the room feel complete with VALENTINA Vanity Set and its Glam character. As a accent vanity, it is designed to complement your space. Finished in Obsidian Gray tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 59 7/8"L X 20 7/8"W X 30 1/4"H&lt;/p&gt;
+Product Dimensions: 59 7/8"L X 20 7/8"W X 30 1/4"H / 59 7/8"L X 20"W X 59"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Obsidian Gray&lt;br&gt;
-Weight: 250.23 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Luminous White&lt;br&gt;
+Weight: 250.23 or 240.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H459" s="32" t="inlineStr">
@@ -67008,7 +67009,7 @@
       </c>
       <c r="AC459" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD459" t="inlineStr">
@@ -67062,14 +67063,14 @@
       <c r="G460" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-VALENTINA Vanity Set brings a Glam look to your home with a refined, comfortable feel. This accent vanity is made to fit naturally into the room. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Luminous White tones for a polished look.&lt;br&gt;
-Product Dimensions: 59 7/8"L X 20"W X 59"H&lt;/p&gt;
+Make the room feel complete with VALENTINA Vanity Set and its Glam character. As a accent vanity, it is designed to complement your space. Finished in Obsidian Gray tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+Product Dimensions: 59 7/8"L X 20 7/8"W X 30 1/4"H / 59 7/8"L X 20"W X 59"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Luminous White&lt;br&gt;
-Weight: 240.9 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Luminous White&lt;br&gt;
+Weight: 250.23 or 240.9 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H460" s="32" t="inlineStr">
@@ -67157,7 +67158,7 @@
       </c>
       <c r="AC460" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD460" t="inlineStr">
@@ -67297,7 +67298,7 @@
       </c>
       <c r="AC461" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD461" t="inlineStr">
@@ -67356,9 +67357,9 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Obsidian Gray&lt;br&gt;
-Weight: 226.6 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Luminous White&lt;br&gt;
+Weight: 226.6 or 225.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H462" s="45" t="inlineStr">
@@ -67446,7 +67447,7 @@
       </c>
       <c r="AC462" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD462" t="inlineStr">
@@ -67500,14 +67501,14 @@
       <c r="G463" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with VICKIE Vanity Set, styled in Glam and designed for everyday comfort. This accent vanity is made to fit naturally into the room. With Mirror, Solid Wood, Wood Veneer, and Luminous White tones, it blends structure and softness in one clean profile.&lt;br&gt;
+VICKIE Vanity Set brings a Glam look to your home with a refined, comfortable feel. As a accent vanity, it is designed to complement your space. The Mirror, Solid Wood, Wood Veneer, construction is complemented by Obsidian Gray tones for a polished look.&lt;br&gt;
 Product Dimensions: 60"L X 20"W X 58 3/8"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Luminous White&lt;br&gt;
-Weight: 225.5 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Obsidian Gray or Luminous White&lt;br&gt;
+Weight: 226.6 or 225.5 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H463" s="45" t="inlineStr">
@@ -67595,7 +67596,7 @@
       </c>
       <c r="AC463" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD463" t="inlineStr">
@@ -67654,8 +67655,8 @@
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Tiffany Blush&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Tiffany Blush or Luminous White&lt;br&gt;
 Weight: 206.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -67744,7 +67745,7 @@
       </c>
       <c r="AC464" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD464" t="inlineStr">
@@ -67798,13 +67799,13 @@
       <c r="G465" s="66" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with YASMINE Vanity Set and its Glam character. As a accent vanity, it is designed to complement your space. Finished in Luminous White tones, the Mirror, Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+YASMINE Vanity Set adds a Glam touch while keeping the room feeling warm and welcoming. Built as a accent vanity, it pairs well with a wide range of interiors. Crafted from Mirror, Solid Wood, Wood Veneer, it is finished in Tiffany Blush tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 60 1/4"L X 20"W X 36 1/4"H, MIRROR: 31 1/2"DIA X 1 5/8"D"&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Glam design&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Storage Drawers&lt;/p&gt;
-&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Luminous White&lt;br&gt;
+&lt;p&gt;Materials: Mirror, Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Tiffany Blush or Luminous White&lt;br&gt;
 Weight: 206.8 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -67893,7 +67894,7 @@
       </c>
       <c r="AC465" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD465" t="inlineStr">
@@ -68034,7 +68035,7 @@
       </c>
       <c r="AC466" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD466" t="inlineStr">
@@ -68091,7 +68092,7 @@
 Elevate your space with CAPARICA Throw Blanket, styled in Contemporary and designed for everyday comfort. Built as a accent blanket, it pairs well with a wide range of interiors. With 100% Polyester and Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Gold&lt;br&gt;
+Color: Gold or Teal&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -68178,7 +68179,7 @@
       </c>
       <c r="AC467" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD467" t="inlineStr">
@@ -68232,10 +68233,10 @@
       <c r="G468" s="32" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-CAPARICA Throw Blanket adds a Contemporary touch while keeping the room feeling warm and welcoming. As a accent blanket, it is designed to complement your space. Crafted from 100% Polyester, it is finished in Teal tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with CAPARICA Throw Blanket, styled in Contemporary and designed for everyday comfort. Built as a accent blanket, it pairs well with a wide range of interiors. With 100% Polyester and Gold tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 50" X 60"&lt;/p&gt;
 &lt;p&gt;Materials: 100% Polyester.&lt;br&gt;
-Color: Teal&lt;br&gt;
+Color: Gold or Teal&lt;br&gt;
 Weight: 6 lbs&lt;/p&gt;</t>
         </is>
       </c>
@@ -68322,7 +68323,7 @@
       </c>
       <c r="AC468" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD468" t="inlineStr">
@@ -68465,7 +68466,7 @@
       </c>
       <c r="AC469" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD469" t="inlineStr">
@@ -68523,9 +68524,9 @@
 Product Dimensions: 30"W X 15"D X 34 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Oak&lt;br&gt;
-Weight: 79.2 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Espresso&lt;br&gt;
+Weight: 79.2 or 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H470" s="45" t="inlineStr">
@@ -68615,7 +68616,7 @@
       </c>
       <c r="AC470" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD470" t="inlineStr">
@@ -68669,13 +68670,13 @@
       <c r="G471" s="45" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with DELLA Shoe Cabinet and its Transitional character. Built as a accent shelf, it pairs well with a wide range of interiors. Finished in Espresso tones, the Solid Wood, Wood Veneer, build balances durability with visual appeal.&lt;br&gt;
+DELLA Shoe Cabinet adds a Transitional touch while keeping the room feeling warm and welcoming. This accent shelf is made to fit naturally into the room. Crafted from Solid Wood, Wood Veneer, it is finished in Oak tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 30"W X 15"D X 34 1/2"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Espresso&lt;br&gt;
-Weight: 70.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Oak or Espresso&lt;br&gt;
+Weight: 79.2 or 70.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H471" s="45" t="inlineStr">
@@ -68761,7 +68762,7 @@
       </c>
       <c r="AC471" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD471" t="inlineStr">
@@ -68904,7 +68905,7 @@
       </c>
       <c r="AC472" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD472" t="inlineStr">
@@ -69041,7 +69042,7 @@
       </c>
       <c r="AC473" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD473" t="inlineStr">
@@ -69184,7 +69185,7 @@
       </c>
       <c r="AC474" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD474" t="inlineStr">
@@ -69328,7 +69329,7 @@
       </c>
       <c r="AC475" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD475" t="inlineStr">
@@ -69471,7 +69472,7 @@
       </c>
       <c r="AC476" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD476" t="inlineStr">
@@ -69614,7 +69615,7 @@
       </c>
       <c r="AC477" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD477" t="inlineStr">
@@ -69755,7 +69756,7 @@
       </c>
       <c r="AC478" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD478" t="inlineStr">
@@ -69813,9 +69814,9 @@
 Product Dimensions: 12"W X 24"D X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-in USB Outlet&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Cherry&lt;br&gt;
-Weight: 45.1 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Gray&lt;br&gt;
+Weight: 45.1 or 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H479" s="25" t="inlineStr">
@@ -69901,7 +69902,7 @@
       </c>
       <c r="AC479" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD479" t="inlineStr">
@@ -69955,13 +69956,13 @@
       <c r="G480" s="25" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-LILITH I Side Table w/ USB adds a Transitional touch while keeping the room feeling warm and welcoming. Built as a accent side table, it pairs well with a wide range of interiors. Crafted from Solid Wood, Wood Veneer, it is finished in Gray tones that pair easily with surrounding decor.&lt;br&gt;
+Elevate your space with LILITH I Side Table w/ USB, styled in Transitional and designed for everyday comfort. This accent side table is made to fit naturally into the room. With Solid Wood, Wood Veneer, and Cherry tones, it blends structure and softness in one clean profile.&lt;br&gt;
 Product Dimensions: 12"W X 24"D X 24"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer Bonus storage &amp;amp; convenience features (from matching set pieces): Built-in USB Outlet&lt;/p&gt;
-&lt;p&gt;Materials: Solid Wood, Wood Veneer.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 48.4 lbs&lt;/p&gt;</t>
+&lt;p&gt;Materials: Solid Wood, Wood Veneer, Others.&lt;br&gt;
+Color: Cherry or Gray&lt;br&gt;
+Weight: 45.1 or 48.4 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H480" s="25" t="inlineStr">
@@ -70047,7 +70048,7 @@
       </c>
       <c r="AC480" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD480" t="inlineStr">
@@ -70190,7 +70191,7 @@
       </c>
       <c r="AC481" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD481" t="inlineStr">
@@ -70331,7 +70332,7 @@
       </c>
       <c r="AC482" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD482" t="inlineStr">
@@ -70472,7 +70473,7 @@
       </c>
       <c r="AC483" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD483" t="inlineStr">
@@ -70613,7 +70614,7 @@
       </c>
       <c r="AC484" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD484" t="inlineStr">
@@ -70754,7 +70755,7 @@
       </c>
       <c r="AC485" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD485" t="inlineStr">
@@ -70895,7 +70896,7 @@
       </c>
       <c r="AC486" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD486" t="inlineStr">
@@ -71036,7 +71037,7 @@
       </c>
       <c r="AC487" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD487" t="inlineStr">
@@ -71177,7 +71178,7 @@
       </c>
       <c r="AC488" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD488" t="inlineStr">
@@ -71318,7 +71319,7 @@
       </c>
       <c r="AC489" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD489" t="inlineStr">
@@ -71375,8 +71376,8 @@
 GRAINNE Storage Bench adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent bench, it pairs well with a wide range of interiors. Crafted from Corduroy, Engineered Wood, it is finished in Green tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 50.5"W X 17.5"D X 18"H&lt;/p&gt;
 &lt;p&gt;Materials: Corduroy, Engineered Wood.&lt;br&gt;
-Color: Green&lt;br&gt;
-Weight: 38.02 lbs&lt;/p&gt;</t>
+Color: Green or White&lt;br&gt;
+Weight: 38.02 or 38.69 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H490" s="42" t="inlineStr">
@@ -71462,7 +71463,7 @@
       </c>
       <c r="AC490" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD490" t="inlineStr">
@@ -71516,11 +71517,11 @@
       <c r="G491" s="42" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with GRAINNE Storage Bench and its Contemporary character. As a accent bench, it is designed to complement your space. Finished in White tones, the Corduroy, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
+GRAINNE Storage Bench adds a Contemporary touch while keeping the room feeling warm and welcoming. Built as a accent bench, it pairs well with a wide range of interiors. Crafted from Corduroy, Engineered Wood, it is finished in Green tones that pair easily with surrounding decor.&lt;br&gt;
 Product Dimensions: 50.5"W X 17.5"D X 18"H&lt;/p&gt;
 &lt;p&gt;Materials: Corduroy, Engineered Wood.&lt;br&gt;
-Color: White&lt;br&gt;
-Weight: 38.69 lbs&lt;/p&gt;</t>
+Color: Green or White&lt;br&gt;
+Weight: 38.02 or 38.69 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H491" s="42" t="inlineStr">
@@ -71606,7 +71607,7 @@
       </c>
       <c r="AC491" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD491" t="inlineStr">
@@ -71747,7 +71748,7 @@
       </c>
       <c r="AC492" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD492" t="inlineStr">
@@ -71890,7 +71891,7 @@
       </c>
       <c r="AC493" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD493" t="inlineStr">
@@ -71945,12 +71946,12 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 TAYAH Bench adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a accent bench, it pairs well with a wide range of interiors. Crafted from Linen, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 54"L X 15 3/4"W 18 1/2"H&lt;/p&gt;
+Product Dimensions: 54"L X 15 3/4"W 18 1/2"H / 59"L X 15"W X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Linen, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 66 lbs&lt;/p&gt;</t>
+Color: Beige or Gray&lt;br&gt;
+Weight: 66 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H494" s="30" t="inlineStr">
@@ -72036,7 +72037,7 @@
       </c>
       <c r="AC494" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD494" t="inlineStr">
@@ -72090,13 +72091,13 @@
       <c r="G495" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Make the room feel complete with TAYAH Bench and its Rustic character. As a accent bench, it is designed to complement your space. Finished in Gray tones, the Linen, Solid Wood, Wood Veneer, Engineered Wood build balances durability with visual appeal.&lt;br&gt;
-Product Dimensions: 54"L X 15 3/4"W 18 1/2"H&lt;/p&gt;
+TAYAH Bench adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a accent bench, it pairs well with a wide range of interiors. Crafted from Linen, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54"L X 15 3/4"W 18 1/2"H / 59"L X 15"W X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Linen, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 66 lbs&lt;/p&gt;</t>
+Color: Beige or Gray&lt;br&gt;
+Weight: 66 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H495" s="30" t="inlineStr">
@@ -72182,7 +72183,7 @@
       </c>
       <c r="AC495" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD495" t="inlineStr">
@@ -72236,13 +72237,13 @@
       <c r="G496" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-TAYAH Bench brings a Rustic look to your home with a refined, comfortable feel. This accent bench is made to fit naturally into the room. The Linen, Solid Wood, Wood Veneer, Engineered Wood construction is complemented by Beige tones for a polished look.&lt;br&gt;
-Product Dimensions: 59"L X 15"W X 19"H&lt;/p&gt;
+TAYAH Bench adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a accent bench, it pairs well with a wide range of interiors. Crafted from Linen, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54"L X 15 3/4"W 18 1/2"H / 59"L X 15"W X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Linen, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Beige&lt;br&gt;
-Weight: 44 lbs&lt;/p&gt;</t>
+Color: Beige or Gray&lt;br&gt;
+Weight: 66 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H496" s="30" t="inlineStr">
@@ -72328,7 +72329,7 @@
       </c>
       <c r="AC496" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD496" t="inlineStr">
@@ -72382,13 +72383,13 @@
       <c r="G497" s="30" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-Elevate your space with TAYAH Bench, styled in Rustic and designed for everyday comfort. Built as a accent bench, it pairs well with a wide range of interiors. With Linen, Solid Wood, Wood Veneer, Engineered Wood and Gray tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 59"L X 15"W X 19"H&lt;/p&gt;
+TAYAH Bench adds a Rustic touch while keeping the room feeling warm and welcoming. Built as a accent bench, it pairs well with a wide range of interiors. Crafted from Linen, Solid Wood, Wood Veneer, Engineered Wood, it is finished in Beige tones that pair easily with surrounding decor.&lt;br&gt;
+Product Dimensions: 54"L X 15 3/4"W 18 1/2"H / 59"L X 15"W X 19"H&lt;/p&gt;
 &lt;p&gt;Features&lt;br&gt;
 - Made with solid wood &amp;amp; wood veneer&lt;/p&gt;
 &lt;p&gt;Materials: Linen, Solid Wood, Wood Veneer, Engineered Wood.&lt;br&gt;
-Color: Gray&lt;br&gt;
-Weight: 44 lbs&lt;/p&gt;</t>
+Color: Beige or Gray&lt;br&gt;
+Weight: 66 or 44 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H497" s="30" t="inlineStr">
@@ -72474,7 +72475,7 @@
       </c>
       <c r="AC497" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD497" t="inlineStr">
@@ -72529,10 +72530,10 @@
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
 Elevate your space with HOMILI Last Supper Plaque, styled in Traditional and designed for everyday comfort. This accent wall art is made to fit naturally into the room. With Ceramic and Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
-Product Dimensions: 29 1/4"L X 5"W X 17 1/4"H&lt;/p&gt;
+Product Dimensions: 29 1/4"L X 5"W X 17 1/4"H / 35"L X 8 1/4"W X 20"H&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
 Color: Multi&lt;br&gt;
-Weight: 19 lbs&lt;/p&gt;</t>
+Weight: 19 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H498" s="68" t="inlineStr">
@@ -72618,7 +72619,7 @@
       </c>
       <c r="AC498" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD498" t="inlineStr">
@@ -72672,11 +72673,11 @@
       <c r="G499" s="68" t="inlineStr">
         <is>
           <t>&lt;p&gt;&lt;span style="color:#1e73be;"&gt;&lt;strong&gt;FREE SHIPPING&lt;/strong&gt;&lt;/span&gt;&lt;br&gt;
-HOMILI Last Supper Plaque adds a Traditional touch while keeping the room feeling warm and welcoming. Built as a accent wall art, it pairs well with a wide range of interiors. Crafted from Ceramic, it is finished in Multi tones that pair easily with surrounding decor.&lt;br&gt;
-Product Dimensions: 35"L X 8 1/4"W X 20"H&lt;/p&gt;
+Elevate your space with HOMILI Last Supper Plaque, styled in Traditional and designed for everyday comfort. This accent wall art is made to fit naturally into the room. With Ceramic and Multi tones, it blends structure and softness in one clean profile.&lt;br&gt;
+Product Dimensions: 29 1/4"L X 5"W X 17 1/4"H / 35"L X 8 1/4"W X 20"H&lt;/p&gt;
 &lt;p&gt;Materials: Ceramic.&lt;br&gt;
 Color: Multi&lt;br&gt;
-Weight: 25 lbs&lt;/p&gt;</t>
+Weight: 19 or 25 lbs&lt;/p&gt;</t>
         </is>
       </c>
       <c r="H499" s="68" t="inlineStr">
@@ -72762,7 +72763,7 @@
       </c>
       <c r="AC499" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD499" t="inlineStr">
@@ -72910,7 +72911,7 @@
       </c>
       <c r="AC500" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD500" t="inlineStr">
@@ -73047,7 +73048,7 @@
       </c>
       <c r="AC501" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD501" t="inlineStr">
@@ -73191,7 +73192,7 @@
       </c>
       <c r="AC502" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD502" t="inlineStr">
@@ -73335,7 +73336,7 @@
       </c>
       <c r="AC503" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD503" t="inlineStr">
@@ -73476,7 +73477,7 @@
       </c>
       <c r="AC504" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD504" t="inlineStr">
@@ -73617,7 +73618,7 @@
       </c>
       <c r="AC505" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD505" t="inlineStr">
@@ -73758,7 +73759,7 @@
       </c>
       <c r="AC506" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD506" t="inlineStr">
@@ -73901,7 +73902,7 @@
       </c>
       <c r="AC507" t="inlineStr">
         <is>
-          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture</t>
+          <t>Furniture of America, Quick Ship Furniture, New Arrival, Indoor Furniture, 2026</t>
         </is>
       </c>
       <c r="AD507" t="inlineStr">

--- a/FOA Singles/Accent-Single.xlsx
+++ b/FOA Singles/Accent-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -860,12 +860,12 @@
       </c>
       <c r="H2" s="30" t="inlineStr">
         <is>
-          <t>ABBEY 4' 9" X 6' 9" Area Rug in Alphabet Multi | GOODDEGG</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I2" s="30" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J2" s="30" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="H3" s="30" t="inlineStr">
         <is>
-          <t>ABBEY 4' 9" X 6' 9" Area Rug in Alphabet Multi | GOODDEGG</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I3" s="30" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J3" s="30" t="inlineStr">
@@ -1148,12 +1148,12 @@
       </c>
       <c r="H4" s="30" t="inlineStr">
         <is>
-          <t>ABBEY 4' 9" X 6' 9" Area Rug in Sports | GOODDEGG</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I4" s="30" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J4" s="30" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="H5" s="30" t="inlineStr">
         <is>
-          <t>ABBEY 4' 9" X 6' 9" Area Rug in Solar System | GOODDEGG</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I5" s="30" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 4' 9" X 6' 9" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J5" s="30" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="H6" s="42" t="inlineStr">
         <is>
-          <t>ABBEY 5' X 8' Area Rug in Red | GOODDEGG</t>
+          <t>ABBEY 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J6" s="42" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="H7" s="42" t="inlineStr">
         <is>
-          <t>ABBEY 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>ABBEY 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J7" s="42" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="H8" s="42" t="inlineStr">
         <is>
-          <t>ABBEY 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>ABBEY 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I8" s="42" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J8" s="42" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="H9" s="42" t="inlineStr">
         <is>
-          <t>ABBEY 5' X 8' Area Rug in Us Map | GOODDEGG</t>
+          <t>ABBEY 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I9" s="42" t="inlineStr">
         <is>
-          <t>The ABBEY Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBEY 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J9" s="42" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ACANTHUS 5' X 8' Area Rug in Taupe | GOODDEGG</t>
+          <t>ACANTHUS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The ACANTHUS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACANTHUS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ACANTHUS 8' X 10' Area Rug in Taupe | GOODDEGG</t>
+          <t>ACANTHUS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The ACANTHUS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACANTHUS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="H12" s="39" t="inlineStr">
         <is>
-          <t>AMOS 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>AMOS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I12" s="39" t="inlineStr">
         <is>
-          <t>The AMOS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMOS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J12" s="39" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="H13" s="39" t="inlineStr">
         <is>
-          <t>AMOS 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>AMOS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I13" s="39" t="inlineStr">
         <is>
-          <t>The AMOS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AMOS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J13" s="39" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="H14" s="45" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 7' Area Rug in Beige | GOODDEGG</t>
+          <t>ANNMARIE 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I14" s="45" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J14" s="45" t="inlineStr">
@@ -2726,12 +2726,12 @@
       </c>
       <c r="H15" s="45" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 7' Area Rug in Navy | GOODDEGG</t>
+          <t>ANNMARIE 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I15" s="45" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J15" s="45" t="inlineStr">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="H16" s="45" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 7' Area Rug in Silver | GOODDEGG</t>
+          <t>ANNMARIE 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I16" s="45" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J16" s="45" t="inlineStr">
@@ -3014,12 +3014,12 @@
       </c>
       <c r="H17" s="45" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 7' Area Rug in White | GOODDEGG</t>
+          <t>ANNMARIE 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I17" s="45" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J17" s="45" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="H18" s="48" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 8' Area Rug in Scarlet | GOODDEGG</t>
+          <t>ANNMARIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I18" s="48" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J18" s="48" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="H19" s="48" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 8' Area Rug in Yellow | GOODDEGG</t>
+          <t>ANNMARIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I19" s="48" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J19" s="48" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="H20" s="48" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 8' Area Rug in Teal | GOODDEGG</t>
+          <t>ANNMARIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I20" s="48" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J20" s="48" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H21" s="48" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 8' Area Rug in Purple | GOODDEGG</t>
+          <t>ANNMARIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I21" s="48" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J21" s="48" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="H22" s="48" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 8' Area Rug in Blue | GOODDEGG</t>
+          <t>ANNMARIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I22" s="48" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J22" s="48" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="H23" s="48" t="inlineStr">
         <is>
-          <t>ANNMARIE 5' X 8' Area Rug in Black | GOODDEGG</t>
+          <t>ANNMARIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I23" s="48" t="inlineStr">
         <is>
-          <t>The ANNMARIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANNMARIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J23" s="48" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="H24" s="51" t="inlineStr">
         <is>
-          <t>BLITAR 5' X 7' Area Rug in Dark Gray | GOODDEGG</t>
+          <t>BLITAR 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I24" s="51" t="inlineStr">
         <is>
-          <t>The BLITAR Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BLITAR 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J24" s="51" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H25" s="51" t="inlineStr">
         <is>
-          <t>BLITAR 5' X 7' Area Rug in Brown Black | GOODDEGG</t>
+          <t>BLITAR 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I25" s="51" t="inlineStr">
         <is>
-          <t>The BLITAR Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BLITAR 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J25" s="51" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="H26" s="51" t="inlineStr">
         <is>
-          <t>BLITAR 5' X 7' Area Rug in Brown | GOODDEGG</t>
+          <t>BLITAR 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I26" s="51" t="inlineStr">
         <is>
-          <t>The BLITAR Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BLITAR 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J26" s="51" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="H27" s="42" t="inlineStr">
         <is>
-          <t>CALEDON 5' X 7' Area Rug in Gray | GOODDEGG</t>
+          <t>CALEDON 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I27" s="42" t="inlineStr">
         <is>
-          <t>The CALEDON Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CALEDON 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J27" s="42" t="inlineStr">
@@ -4598,12 +4598,12 @@
       </c>
       <c r="H28" s="42" t="inlineStr">
         <is>
-          <t>CALEDON 5' X 7' Area Rug in Gray Red | GOODDEGG</t>
+          <t>CALEDON 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I28" s="42" t="inlineStr">
         <is>
-          <t>The CALEDON Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CALEDON 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J28" s="42" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H29" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Black | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I29" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J29" s="54" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="H30" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Charcoal | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I30" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J30" s="54" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="H31" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Blush | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I31" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J31" s="54" t="inlineStr">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="H32" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Silver | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I32" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J32" s="54" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="H33" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Off-White | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I33" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J33" s="54" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="H34" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Gold | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I34" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J34" s="54" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="H35" s="54" t="inlineStr">
         <is>
-          <t>CAPARICA 5' X 7' Area Rug in Teal | GOODDEGG</t>
+          <t>CAPARICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I35" s="54" t="inlineStr">
         <is>
-          <t>The CAPARICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J35" s="54" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H36" s="57" t="inlineStr">
         <is>
-          <t>FAMALICA 5' X 7' Area Rug in Tie-Dye Beige | GOODDEGG</t>
+          <t>FAMALICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I36" s="57" t="inlineStr">
         <is>
-          <t>The FAMALICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAMALICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J36" s="57" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H37" s="57" t="inlineStr">
         <is>
-          <t>FAMALICA 5' X 7' Area Rug in Tie-Dye Gray | GOODDEGG</t>
+          <t>FAMALICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I37" s="57" t="inlineStr">
         <is>
-          <t>The FAMALICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAMALICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J37" s="57" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="H38" s="57" t="inlineStr">
         <is>
-          <t>FAMALICA 5' X 7' Area Rug in Tie-Dye Purple | GOODDEGG</t>
+          <t>FAMALICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I38" s="57" t="inlineStr">
         <is>
-          <t>The FAMALICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAMALICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J38" s="57" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="H39" s="57" t="inlineStr">
         <is>
-          <t>FAMALICA 5' X 7' Area Rug in Off-White | GOODDEGG</t>
+          <t>FAMALICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I39" s="57" t="inlineStr">
         <is>
-          <t>The FAMALICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAMALICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J39" s="57" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="H40" s="57" t="inlineStr">
         <is>
-          <t>FAMALICA 5' X 7' Area Rug in Pink | GOODDEGG</t>
+          <t>FAMALICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I40" s="57" t="inlineStr">
         <is>
-          <t>The FAMALICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAMALICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J40" s="57" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H41" s="57" t="inlineStr">
         <is>
-          <t>FAMALICA 5' X 7' Area Rug in Gray | GOODDEGG</t>
+          <t>FAMALICA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I41" s="57" t="inlineStr">
         <is>
-          <t>The FAMALICA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAMALICA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J41" s="57" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="H42" s="59" t="inlineStr">
         <is>
-          <t>FERMONT 5' X 8' Area Rug in Gray | GOODDEGG</t>
+          <t>FERMONT 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I42" s="59" t="inlineStr">
         <is>
-          <t>The FERMONT Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERMONT 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J42" s="59" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H43" s="59" t="inlineStr">
         <is>
-          <t>FERMONT 5' X 8' Area Rug in Brown Beige | GOODDEGG</t>
+          <t>FERMONT 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I43" s="59" t="inlineStr">
         <is>
-          <t>The FERMONT Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FERMONT 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J43" s="59" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Frederiction 5' X 8' Area Rug in Ivory | GOODDEGG</t>
+          <t>FREDERICTION 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>The FREDERICTION Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FREDERICTION 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H45" s="54" t="inlineStr">
         <is>
-          <t>HEPSIBA 5' X 7' Area Rug in Ogee Beige | GOODDEGG</t>
+          <t>HEPSIBA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I45" s="54" t="inlineStr">
         <is>
-          <t>The HEPSIBA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPSIBA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J45" s="54" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="H46" s="54" t="inlineStr">
         <is>
-          <t>HEPSIBA 5' X 7' Area Rug in Drop Taupe | GOODDEGG</t>
+          <t>HEPSIBA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I46" s="54" t="inlineStr">
         <is>
-          <t>The HEPSIBA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPSIBA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J46" s="54" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="H47" s="54" t="inlineStr">
         <is>
-          <t>HEPSIBA 5' X 7' Area Rug in Drop Wine | GOODDEGG</t>
+          <t>HEPSIBA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I47" s="54" t="inlineStr">
         <is>
-          <t>The HEPSIBA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPSIBA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J47" s="54" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H48" s="54" t="inlineStr">
         <is>
-          <t>HEPSIBA 5' X 7' Area Rug in Dune Sienna | GOODDEGG</t>
+          <t>HEPSIBA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I48" s="54" t="inlineStr">
         <is>
-          <t>The HEPSIBA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPSIBA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J48" s="54" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="H49" s="54" t="inlineStr">
         <is>
-          <t>HEPSIBA 5' X 7' Area Rug in Diamond Taupe | GOODDEGG</t>
+          <t>HEPSIBA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I49" s="54" t="inlineStr">
         <is>
-          <t>The HEPSIBA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HEPSIBA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J49" s="54" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="H50" s="25" t="inlineStr">
         <is>
-          <t>HOLLIE 5' X 8' Area Rug in Gold Gray | GOODDEGG</t>
+          <t>HOLLIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I50" s="25" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J50" s="25" t="inlineStr">
@@ -7911,12 +7911,12 @@
       </c>
       <c r="H51" s="25" t="inlineStr">
         <is>
-          <t>HOLLIE 5' X 8' Area Rug in Blue Gray | GOODDEGG</t>
+          <t>HOLLIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I51" s="25" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J51" s="25" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H52" s="25" t="inlineStr">
         <is>
-          <t>HOLLIE 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>HOLLIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I52" s="25" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J52" s="25" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="H53" s="25" t="inlineStr">
         <is>
-          <t>HOLLIE 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>HOLLIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I53" s="25" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J53" s="25" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="H54" s="25" t="inlineStr">
         <is>
-          <t>HOLLIE 5' X 8' Area Rug in Multi | GOODDEGG</t>
+          <t>HOLLIE 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I54" s="25" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J54" s="25" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="H55" s="32" t="inlineStr">
         <is>
-          <t>HOLLIE 8' X 10' Area Rug in Gold Gray | GOODDEGG</t>
+          <t>HOLLIE 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I55" s="32" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J55" s="32" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>HOLLIE 8' X 10' Area Rug in Blue Gray | GOODDEGG</t>
+          <t>HOLLIE 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I56" s="32" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J56" s="32" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="H57" s="32" t="inlineStr">
         <is>
-          <t>HOLLIE 8' X 10' Area Rug in Multi | GOODDEGG</t>
+          <t>HOLLIE 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I57" s="32" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J57" s="32" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="H58" s="32" t="inlineStr">
         <is>
-          <t>HOLLIE 8' X 10' Area Rug in Multi | GOODDEGG</t>
+          <t>HOLLIE 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I58" s="32" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J58" s="32" t="inlineStr">
@@ -9063,12 +9063,12 @@
       </c>
       <c r="H59" s="32" t="inlineStr">
         <is>
-          <t>HOLLIE 8' X 10' Area Rug in Multi | GOODDEGG</t>
+          <t>HOLLIE 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I59" s="32" t="inlineStr">
         <is>
-          <t>The HOLLIE Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOLLIE 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J59" s="32" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="H60" s="42" t="inlineStr">
         <is>
-          <t>KOZLU 5' X 7' Area Rug in Beige | GOODDEGG</t>
+          <t>KOZLU 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I60" s="42" t="inlineStr">
         <is>
-          <t>The KOZLU Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOZLU 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J60" s="42" t="inlineStr">
@@ -9351,12 +9351,12 @@
       </c>
       <c r="H61" s="42" t="inlineStr">
         <is>
-          <t>KOZLU 5' X 7' Area Rug in Gray Beige | GOODDEGG</t>
+          <t>KOZLU 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I61" s="42" t="inlineStr">
         <is>
-          <t>The KOZLU Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOZLU 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J61" s="42" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="H62" s="42" t="inlineStr">
         <is>
-          <t>KOZLU 5' X 7' Area Rug in Dark Gray | GOODDEGG</t>
+          <t>KOZLU 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I62" s="42" t="inlineStr">
         <is>
-          <t>The KOZLU Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KOZLU 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J62" s="42" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>LIEGE 5' X 8' Rug Pad in Pattern | GOODDEGG</t>
+          <t>LIEGE 5' X 8' Rug Pad | GOODDEGG</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>The LIEGE Rug Pad adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LIEGE 5' X 8' Rug Pad supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="H64" s="59" t="inlineStr">
         <is>
-          <t>MONTIJO 5' X 8' Area Rug in Distressed Multi | GOODDEGG</t>
+          <t>MONTIJO 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I64" s="59" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J64" s="59" t="inlineStr">
@@ -9924,12 +9924,12 @@
       </c>
       <c r="H65" s="59" t="inlineStr">
         <is>
-          <t>MONTIJO 5' X 8' Area Rug in Mediterranean Multi | GOODDEGG</t>
+          <t>MONTIJO 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I65" s="59" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J65" s="59" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H66" s="59" t="inlineStr">
         <is>
-          <t>MONTIJO 5' X 8' Area Rug in Concrete Umber | GOODDEGG</t>
+          <t>MONTIJO 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I66" s="59" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J66" s="59" t="inlineStr">
@@ -10212,12 +10212,12 @@
       </c>
       <c r="H67" s="59" t="inlineStr">
         <is>
-          <t>MONTIJO 5' X 8' Area Rug in Weave Multi | GOODDEGG</t>
+          <t>MONTIJO 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I67" s="59" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J67" s="59" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="H68" s="51" t="inlineStr">
         <is>
-          <t>MONTIJO 8' X 11' Area Rug in Distressed Multi | GOODDEGG</t>
+          <t>MONTIJO 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I68" s="51" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J68" s="51" t="inlineStr">
@@ -10500,12 +10500,12 @@
       </c>
       <c r="H69" s="51" t="inlineStr">
         <is>
-          <t>MONTIJO 8' X 11' Area Rug in Mediterranean Multi | GOODDEGG</t>
+          <t>MONTIJO 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I69" s="51" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J69" s="51" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H70" s="51" t="inlineStr">
         <is>
-          <t>MONTIJO 8' X 11' Area Rug in Concrete Umber | GOODDEGG</t>
+          <t>MONTIJO 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I70" s="51" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J70" s="51" t="inlineStr">
@@ -10788,12 +10788,12 @@
       </c>
       <c r="H71" s="51" t="inlineStr">
         <is>
-          <t>MONTIJO 8' X 11' Area Rug in Weave Multi | GOODDEGG</t>
+          <t>MONTIJO 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I71" s="51" t="inlineStr">
         <is>
-          <t>The MONTIJO Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MONTIJO 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J71" s="51" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>NEATH 8' X 10' Rug Pad in Pattern | GOODDEGG</t>
+          <t>NEATH 8' X 10' Rug Pad | GOODDEGG</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>The NEATH Rug Pad adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NEATH 8' X 10' Rug Pad supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="H73" s="42" t="inlineStr">
         <is>
-          <t>NIKSAR 5' X 7' Area Rug in Red | GOODDEGG</t>
+          <t>NIKSAR 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I73" s="42" t="inlineStr">
         <is>
-          <t>The NIKSAR Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIKSAR 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J73" s="42" t="inlineStr">
@@ -11217,12 +11217,12 @@
       </c>
       <c r="H74" s="42" t="inlineStr">
         <is>
-          <t>NIKSAR 5' X 7' Area Rug in Turquoise | GOODDEGG</t>
+          <t>NIKSAR 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I74" s="42" t="inlineStr">
         <is>
-          <t>The NIKSAR Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIKSAR 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J74" s="42" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="H75" s="42" t="inlineStr">
         <is>
-          <t>NIKSAR 5' X 7' Area Rug in Gray Purple | GOODDEGG</t>
+          <t>NIKSAR 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I75" s="42" t="inlineStr">
         <is>
-          <t>The NIKSAR Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIKSAR 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J75" s="42" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="H76" s="36" t="inlineStr">
         <is>
-          <t>PAYAS 5' X 7' Area Rug in Beige | GOODDEGG</t>
+          <t>PAYAS 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I76" s="36" t="inlineStr">
         <is>
-          <t>The PAYAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAYAS 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J76" s="36" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="H77" s="36" t="inlineStr">
         <is>
-          <t>PAYAS 5' X 7' Area Rug in Blue Multi | GOODDEGG</t>
+          <t>PAYAS 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I77" s="36" t="inlineStr">
         <is>
-          <t>The PAYAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAYAS 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J77" s="36" t="inlineStr">
@@ -11793,12 +11793,12 @@
       </c>
       <c r="H78" s="36" t="inlineStr">
         <is>
-          <t>PAYAS 5' X 7' Area Rug in Blue Multi | GOODDEGG</t>
+          <t>PAYAS 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I78" s="36" t="inlineStr">
         <is>
-          <t>The PAYAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAYAS 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J78" s="36" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="H79" s="36" t="inlineStr">
         <is>
-          <t>PAYAS 5' X 7' Area Rug in Multi | GOODDEGG</t>
+          <t>PAYAS 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I79" s="36" t="inlineStr">
         <is>
-          <t>The PAYAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAYAS 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J79" s="36" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="H80" s="36" t="inlineStr">
         <is>
-          <t>PAYAS 5' X 7' Area Rug in Multi | GOODDEGG</t>
+          <t>PAYAS 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I80" s="36" t="inlineStr">
         <is>
-          <t>The PAYAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAYAS 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J80" s="36" t="inlineStr">
@@ -12225,12 +12225,12 @@
       </c>
       <c r="H81" s="36" t="inlineStr">
         <is>
-          <t>PAYAS 5' X 7' Area Rug in Red | GOODDEGG</t>
+          <t>PAYAS 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I81" s="36" t="inlineStr">
         <is>
-          <t>The PAYAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAYAS 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J81" s="36" t="inlineStr">
@@ -12369,12 +12369,12 @@
       </c>
       <c r="H82" s="45" t="inlineStr">
         <is>
-          <t>SERANG 5' X 7' Area Rug in Gray Black | GOODDEGG</t>
+          <t>SERANG 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I82" s="45" t="inlineStr">
         <is>
-          <t>The SERANG Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SERANG 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J82" s="45" t="inlineStr">
@@ -12513,12 +12513,12 @@
       </c>
       <c r="H83" s="45" t="inlineStr">
         <is>
-          <t>SERANG 5' X 7' Area Rug in Gray Black | GOODDEGG</t>
+          <t>SERANG 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I83" s="45" t="inlineStr">
         <is>
-          <t>The SERANG Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SERANG 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J83" s="45" t="inlineStr">
@@ -12657,12 +12657,12 @@
       </c>
       <c r="H84" s="45" t="inlineStr">
         <is>
-          <t>SERANG 5' X 7' Area Rug in Gray Red | GOODDEGG</t>
+          <t>SERANG 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I84" s="45" t="inlineStr">
         <is>
-          <t>The SERANG Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SERANG 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J84" s="45" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>SHINTA 5' X 7' Area Rug in Brown Multi | GOODDEGG</t>
+          <t>SHINTA 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>The SHINTA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHINTA 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="H86" s="48" t="inlineStr">
         <is>
-          <t>SHINTA 5' X 8' Area Rug in Burgundy | GOODDEGG</t>
+          <t>SHINTA 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I86" s="48" t="inlineStr">
         <is>
-          <t>The SHINTA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHINTA 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J86" s="48" t="inlineStr">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="H87" s="48" t="inlineStr">
         <is>
-          <t>SHINTA 5' X 8' Area Rug in Red | GOODDEGG</t>
+          <t>SHINTA 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I87" s="48" t="inlineStr">
         <is>
-          <t>The SHINTA Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHINTA 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J87" s="48" t="inlineStr">
@@ -13230,12 +13230,12 @@
       </c>
       <c r="H88" s="64" t="inlineStr">
         <is>
-          <t>SIVAS 5' X 8' Area Rug in Gray Black | GOODDEGG</t>
+          <t>SIVAS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I88" s="64" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J88" s="64" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="H89" s="64" t="inlineStr">
         <is>
-          <t>SIVAS 5' X 8' Area Rug in Gray Red | GOODDEGG</t>
+          <t>SIVAS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I89" s="64" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J89" s="64" t="inlineStr">
@@ -13518,12 +13518,12 @@
       </c>
       <c r="H90" s="64" t="inlineStr">
         <is>
-          <t>SIVAS 5' X 8' Area Rug in Gray Blue | GOODDEGG</t>
+          <t>SIVAS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I90" s="64" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J90" s="64" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="H91" s="64" t="inlineStr">
         <is>
-          <t>SIVAS 5' X 8' Area Rug in Gray Black | GOODDEGG</t>
+          <t>SIVAS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I91" s="64" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J91" s="64" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="H92" s="64" t="inlineStr">
         <is>
-          <t>SIVAS 5' X 8' Area Rug in Charcoal Blue | GOODDEGG</t>
+          <t>SIVAS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I92" s="64" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J92" s="64" t="inlineStr">
@@ -13950,12 +13950,12 @@
       </c>
       <c r="H93" s="64" t="inlineStr">
         <is>
-          <t>SIVAS 5' X 8' Area Rug in Charcoal Yellow | GOODDEGG</t>
+          <t>SIVAS 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I93" s="64" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J93" s="64" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="H94" s="66" t="inlineStr">
         <is>
-          <t>SIVAS 8' X 10' Area Rug in Gray Black | GOODDEGG</t>
+          <t>SIVAS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I94" s="66" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J94" s="66" t="inlineStr">
@@ -14238,12 +14238,12 @@
       </c>
       <c r="H95" s="66" t="inlineStr">
         <is>
-          <t>SIVAS 8' X 10' Area Rug in Gray Red | GOODDEGG</t>
+          <t>SIVAS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I95" s="66" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J95" s="66" t="inlineStr">
@@ -14382,12 +14382,12 @@
       </c>
       <c r="H96" s="66" t="inlineStr">
         <is>
-          <t>SIVAS 8' X 10' Area Rug in Gray Blue | GOODDEGG</t>
+          <t>SIVAS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I96" s="66" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J96" s="66" t="inlineStr">
@@ -14526,12 +14526,12 @@
       </c>
       <c r="H97" s="66" t="inlineStr">
         <is>
-          <t>SIVAS 8' X 10' Area Rug in Gray Black | GOODDEGG</t>
+          <t>SIVAS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I97" s="66" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J97" s="66" t="inlineStr">
@@ -14670,12 +14670,12 @@
       </c>
       <c r="H98" s="66" t="inlineStr">
         <is>
-          <t>SIVAS 8' X 10' Area Rug in Charcoal Blue | GOODDEGG</t>
+          <t>SIVAS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I98" s="66" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J98" s="66" t="inlineStr">
@@ -14814,12 +14814,12 @@
       </c>
       <c r="H99" s="66" t="inlineStr">
         <is>
-          <t>SIVAS 8' X 10' Area Rug in Charcoal Yellow | GOODDEGG</t>
+          <t>SIVAS 8' X 10' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I99" s="66" t="inlineStr">
         <is>
-          <t>The SIVAS Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIVAS 8' X 10' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J99" s="66" t="inlineStr">
@@ -14958,12 +14958,12 @@
       </c>
       <c r="H100" s="68" t="inlineStr">
         <is>
-          <t>Vancouver 5' X 7' Area Rug in Gray Navy | GOODDEGG</t>
+          <t>VANCOUVER 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I100" s="68" t="inlineStr">
         <is>
-          <t>The VANCOUVER Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VANCOUVER 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J100" s="68" t="inlineStr">
@@ -15102,12 +15102,12 @@
       </c>
       <c r="H101" s="68" t="inlineStr">
         <is>
-          <t>Vancouver 5' X 7' Area Rug in Black Gray Red | GOODDEGG</t>
+          <t>VANCOUVER 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I101" s="68" t="inlineStr">
         <is>
-          <t>The VANCOUVER Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VANCOUVER 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J101" s="68" t="inlineStr">
@@ -15246,12 +15246,12 @@
       </c>
       <c r="H102" s="68" t="inlineStr">
         <is>
-          <t>Vancouver 5' X 7' Area Rug in Earth | GOODDEGG</t>
+          <t>VANCOUVER 5' X 7' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I102" s="68" t="inlineStr">
         <is>
-          <t>The VANCOUVER Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VANCOUVER 5' X 7' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J102" s="68" t="inlineStr">
@@ -15390,12 +15390,12 @@
       </c>
       <c r="H103" s="39" t="inlineStr">
         <is>
-          <t>Vancouver 5' X 8' Area Rug in Gray Beige | GOODDEGG</t>
+          <t>VANCOUVER 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I103" s="39" t="inlineStr">
         <is>
-          <t>The VANCOUVER Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VANCOUVER 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J103" s="39" t="inlineStr">
@@ -15534,12 +15534,12 @@
       </c>
       <c r="H104" s="39" t="inlineStr">
         <is>
-          <t>Vancouver 5' X 8' Area Rug in Gray | GOODDEGG</t>
+          <t>VANCOUVER 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I104" s="39" t="inlineStr">
         <is>
-          <t>The VANCOUVER Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VANCOUVER 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J104" s="39" t="inlineStr">
@@ -15678,12 +15678,12 @@
       </c>
       <c r="H105" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Doppler Teal | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I105" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J105" s="48" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="H106" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Spice Rose | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I106" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J106" s="48" t="inlineStr">
@@ -15966,12 +15966,12 @@
       </c>
       <c r="H107" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Indigo Breach | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I107" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J107" s="48" t="inlineStr">
@@ -16110,12 +16110,12 @@
       </c>
       <c r="H108" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Concrete Lapis | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I108" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J108" s="48" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="H109" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Abstract Multi | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I109" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J109" s="48" t="inlineStr">
@@ -16398,12 +16398,12 @@
       </c>
       <c r="H110" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Relic Beige | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I110" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J110" s="48" t="inlineStr">
@@ -16542,12 +16542,12 @@
       </c>
       <c r="H111" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Obelisk Gray | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I111" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J111" s="48" t="inlineStr">
@@ -16686,12 +16686,12 @@
       </c>
       <c r="H112" s="48" t="inlineStr">
         <is>
-          <t>WILHELM 5'3 X 7'6" Area Rug in Palmette Multi | GOODDEGG</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I112" s="48" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3 X 7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J112" s="48" t="inlineStr">
@@ -16829,12 +16829,12 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>WILHELM 5'3x7'6" Area Rug in Chroma Multi | GOODDEGG</t>
+          <t>WILHELM 5'3x7'6" Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>The WILHELM 3x7 Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 5'3x7'6" Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -16971,12 +16971,12 @@
       </c>
       <c r="H114" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Doppler Teal | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I114" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J114" s="64" t="inlineStr">
@@ -17115,12 +17115,12 @@
       </c>
       <c r="H115" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Spice Rose | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I115" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J115" s="64" t="inlineStr">
@@ -17259,12 +17259,12 @@
       </c>
       <c r="H116" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Indigo Breach | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I116" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J116" s="64" t="inlineStr">
@@ -17403,12 +17403,12 @@
       </c>
       <c r="H117" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Concrete Lapis | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I117" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J117" s="64" t="inlineStr">
@@ -17547,12 +17547,12 @@
       </c>
       <c r="H118" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Abstract Multi | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I118" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J118" s="64" t="inlineStr">
@@ -17691,12 +17691,12 @@
       </c>
       <c r="H119" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Chroma Multi | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I119" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J119" s="64" t="inlineStr">
@@ -17835,12 +17835,12 @@
       </c>
       <c r="H120" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Relic Beige | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I120" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J120" s="64" t="inlineStr">
@@ -17979,12 +17979,12 @@
       </c>
       <c r="H121" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Obelisk Gray | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I121" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J121" s="64" t="inlineStr">
@@ -18123,12 +18123,12 @@
       </c>
       <c r="H122" s="64" t="inlineStr">
         <is>
-          <t>WILHELM 8' X 11' Area Rug in Palmette Multi | GOODDEGG</t>
+          <t>WILHELM 8' X 11' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I122" s="64" t="inlineStr">
         <is>
-          <t>The WILHELM Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WILHELM 8' X 11' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J122" s="64" t="inlineStr">
@@ -18266,12 +18266,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>WINNIPEG 5' X 8' Area Rug in Gray Blue | GOODDEGG</t>
+          <t>WINNIPEG 5' X 8' Area Rug | GOODDEGG</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>The WINNIPEG Area Rug adds warmth and comfort underfoot. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WINNIPEG 5' X 8' Area Rug supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -18408,12 +18408,12 @@
       </c>
       <c r="H124" s="36" t="inlineStr">
         <is>
-          <t>ABBI Table Lamp in Black | GOODDEGG</t>
+          <t>ABBI Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I124" s="36" t="inlineStr">
         <is>
-          <t>The ABBI Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBI Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J124" s="36" t="inlineStr">
@@ -18552,12 +18552,12 @@
       </c>
       <c r="H125" s="36" t="inlineStr">
         <is>
-          <t>ABBI Table Lamp in Chrome | GOODDEGG</t>
+          <t>ABBI Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I125" s="36" t="inlineStr">
         <is>
-          <t>The ABBI Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ABBI Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J125" s="36" t="inlineStr">
@@ -18695,12 +18695,12 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>ALEX 27"H Table Lamp in Blue | GOODDEGG</t>
+          <t>ALEX 27"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>The ALEX H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALEX 27"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -18838,12 +18838,12 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>ALRAI 31 1 2"H Table Lamp in Clear | GOODDEGG</t>
+          <t>ALRAI 31 1/2"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>The ALRAI or H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALRAI 31 1/2"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -18981,12 +18981,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>ALRAI 63"H Floor Lamp in Clear | GOODDEGG</t>
+          <t>ALRAI 63"H Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>The ALRAI H Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALRAI 63"H Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -19124,12 +19124,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>ANA Ceiling Lamp in Gold | GOODDEGG</t>
+          <t>ANA Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>The ANA Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANA Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -19267,12 +19267,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>ANA Floor Lamp in Gold | GOODDEGG</t>
+          <t>ANA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>The ANA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -19410,12 +19410,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>ANA Table Lamp in Gold | GOODDEGG</t>
+          <t>ANA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>The ANA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -19553,12 +19553,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>ARYA Ceiling Lamp in Black Chrome | GOODDEGG</t>
+          <t>ARYA Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>The ARYA Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARYA Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -19701,12 +19701,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>ARYA Floor Lamp in Black Chrome | GOODDEGG</t>
+          <t>ARYA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>The ARYA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARYA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -19849,12 +19849,12 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>ARYA Table Lamp in Black Chrome | GOODDEGG</t>
+          <t>ARYA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>The ARYA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARYA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -19995,12 +19995,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>AYA Floor Lamp in White Silver | GOODDEGG</t>
+          <t>AYA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>The AYA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AYA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -20136,12 +20136,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>AYA Table Lamp in White Silver | GOODDEGG</t>
+          <t>AYA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>The AYA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AYA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -20278,12 +20278,12 @@
       </c>
       <c r="H137" s="30" t="inlineStr">
         <is>
-          <t>BRIAR Table Lamp in Antique Gold | GOODDEGG</t>
+          <t>BRIAR Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I137" s="30" t="inlineStr">
         <is>
-          <t>The BRIAR Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRIAR Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J137" s="30" t="inlineStr">
@@ -20422,12 +20422,12 @@
       </c>
       <c r="H138" s="30" t="inlineStr">
         <is>
-          <t>BRIAR Table Lamp in Stain Nickel | GOODDEGG</t>
+          <t>BRIAR Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I138" s="30" t="inlineStr">
         <is>
-          <t>The BRIAR Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRIAR Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J138" s="30" t="inlineStr">
@@ -20569,12 +20569,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>CAMILA 27.5"H Glass Table Lamp in Purple Blue | GOODDEGG</t>
+          <t>CAMILA 27.5"H Glass Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>The CAMILA H Glass Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAMILA 27.5"H Glass Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -20710,12 +20710,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>CECELIA Ceiling Lamp in Copper | GOODDEGG</t>
+          <t>CECELIA Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>The CECELIA Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CECELIA Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="H141" s="68" t="inlineStr">
         <is>
-          <t>CECELIA Floor Lamp in Copper | GOODDEGG</t>
+          <t>CECELIA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I141" s="68" t="inlineStr">
         <is>
-          <t>The CECELIA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CECELIA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J141" s="68" t="inlineStr">
@@ -21005,12 +21005,12 @@
       </c>
       <c r="H142" s="68" t="inlineStr">
         <is>
-          <t>CECELIA Floor Lamp in Copper | GOODDEGG</t>
+          <t>CECELIA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I142" s="68" t="inlineStr">
         <is>
-          <t>The CECELIA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CECELIA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J142" s="68" t="inlineStr">
@@ -21152,12 +21152,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>CHRISTIANA 35"H Gold Ceiling Lamp in Gold | GOODDEGG</t>
+          <t>CHRISTIANA 35"H Gold Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>The CHRISTIANA H Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CHRISTIANA 35"H Gold Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -21300,12 +21300,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>CLARIS Arch Lamp in Ivory Chrome | GOODDEGG</t>
+          <t>CLARIS Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>The CLARIS Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CLARIS Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -21446,12 +21446,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>CORA Table Lamp in Silver White | GOODDEGG</t>
+          <t>CORA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>The CORA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CORA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -21587,12 +21587,12 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>DEBORAH 24.5"H Gold Ceiling Lamp in Gold | GOODDEGG</t>
+          <t>DEBORAH 24.5"H Gold Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>The DEBORAH H Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEBORAH 24.5"H Gold Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -21733,12 +21733,12 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>DEBORAH 33"H Gold Table Lamp in Gold | GOODDEGG</t>
+          <t>DEBORAH 33"H Gold Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>The DEBORAH H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEBORAH 33"H Gold Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -21874,12 +21874,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>DEBORAH 63"H Gold Floor Lamp in Gold | GOODDEGG</t>
+          <t>DEBORAH 63"H Gold Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>The DEBORAH H Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEBORAH 63"H Gold Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -22015,12 +22015,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>DESMA Table Lamp in Champagne White | GOODDEGG</t>
+          <t>DESMA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>The DESMA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DESMA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -22156,12 +22156,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>DONNA 15"H Glass Amber Table Lamp in Amber | GOODDEGG</t>
+          <t>DONNA 15"H Glass Amber Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>The DONNA H Glass Amber Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DONNA 15"H Glass Amber Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -22297,12 +22297,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>DONNA 15"H Glass Clear Table Lamp in Clear | GOODDEGG</t>
+          <t>DONNA 15"H Glass Clear Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>The DONNA H Glass Clear Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DONNA 15"H Glass Clear Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -22438,12 +22438,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>EDIE 23.5"H Glossy White Table Lamp in White | GOODDEGG</t>
+          <t>EDIE 23.5"H Glossy White Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>The EDIE H Glossy Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDIE 23.5"H Glossy White Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -22580,12 +22580,12 @@
       </c>
       <c r="H153" s="66" t="inlineStr">
         <is>
-          <t>EDIE Table Lamp in Burgundy | GOODDEGG</t>
+          <t>EDIE Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I153" s="66" t="inlineStr">
         <is>
-          <t>The EDIE Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDIE Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J153" s="66" t="inlineStr">
@@ -22724,12 +22724,12 @@
       </c>
       <c r="H154" s="66" t="inlineStr">
         <is>
-          <t>EDIE Table Lamp in Black | GOODDEGG</t>
+          <t>EDIE Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I154" s="66" t="inlineStr">
         <is>
-          <t>The EDIE Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDIE Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J154" s="66" t="inlineStr">
@@ -22868,12 +22868,12 @@
       </c>
       <c r="H155" s="66" t="inlineStr">
         <is>
-          <t>EDIE Table Lamp in Pink | GOODDEGG</t>
+          <t>EDIE Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I155" s="66" t="inlineStr">
         <is>
-          <t>The EDIE Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EDIE Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J155" s="66" t="inlineStr">
@@ -23011,12 +23011,12 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>ELEN 28"H Olive Glass Table Lamp in Olive | GOODDEGG</t>
+          <t>ELEN 28"H Olive Glass Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>The ELEN H Olive Glass Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELEN 28"H Olive Glass Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -23152,12 +23152,12 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>ELOUISE Arch Lamp in Black Gold | GOODDEGG</t>
+          <t>ELOUISE Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>The ELOUISE Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELOUISE Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -23295,12 +23295,12 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>ELVA Floor Lamp in Silver Chrome | GOODDEGG</t>
+          <t>ELVA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>The ELVA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELVA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -23443,12 +23443,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>ELVA Table Lamp in Silver Chrome | GOODDEGG</t>
+          <t>ELVA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>The ELVA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELVA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -23589,12 +23589,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>EMI Floor Lamp in White Silver | GOODDEGG</t>
+          <t>EMI Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>The EMI Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EMI Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -23730,12 +23730,12 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>EMI Table Lamp in White Silver | GOODDEGG</t>
+          <t>EMI Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>The EMI Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EMI Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -23871,12 +23871,12 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>FAITH 20"H White Marble Gold Table Lamp in White Gold | GOODDEGG</t>
+          <t>FAITH 20"H White Marble Gold Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>The FAITH H Marble Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAITH 20"H White Marble Gold Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>FAITH 20"H White Marble Steel Table Lamp in White Silver | GOODDE</t>
+          <t>FAITH 20"H White Marble Steel Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>The FAITH H Marble Steel Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Lighting FAITH 20"H White Marble Steel Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -24153,12 +24153,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>FANNY Floor Lamp in Brown | GOODDEGG</t>
+          <t>FANNY Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>The FANNY Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FANNY Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -24294,12 +24294,12 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>FARAH 17"H Glossy White Table Lamp in White | GOODDEGG</t>
+          <t>FARAH 17"H Glossy White Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>The FARAH H Glossy Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FARAH 17"H Glossy White Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -24435,12 +24435,12 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>FARAH 17"H Matte Black Table Lamp in Black | GOODDEGG</t>
+          <t>FARAH 17"H Matte Black Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>The FARAH H Matte Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FARAH 17"H Matte Black Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -24576,12 +24576,12 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>FARAH 17"H Matte Pink Table Lamp in Pink | GOODDEGG</t>
+          <t>FARAH 17"H Matte Pink Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>The FARAH H Matte Pink Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FARAH 17"H Matte Pink Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -24717,12 +24717,12 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>FARAH 17"H Matte Teal Table Lamp in Teal | GOODDEGG</t>
+          <t>FARAH 17"H Matte Teal Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>The FARAH H Matte Teal Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FARAH 17"H Matte Teal Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
@@ -24858,12 +24858,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>FAY 30"H Table Lamp in Purple | GOODDEGG</t>
+          <t>FAY 30"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>The FAY H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAY 30"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
@@ -24999,12 +24999,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>GAEA Table Lamp in Silver White | GOODDEGG</t>
+          <t>GAEA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>The GAEA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GAEA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
@@ -25140,12 +25140,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>GAIL Table Lamp in Stain Nickel | GOODDEGG</t>
+          <t>GAIL Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>The GAIL Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GAIL Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
@@ -25281,12 +25281,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>GUADALUPE 29.5"H Golden Brown Table Lamp in Gold Brown | GOODDEGG</t>
+          <t>GUADALUPE 29.5"H Golden Brown Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>The GUADALUPE H Golden Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>Lighting GUADALUPE 29.5"H Golden Brown Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
@@ -25430,12 +25430,12 @@
       </c>
       <c r="H173" s="36" t="inlineStr">
         <is>
-          <t>HANNA Table Lamp (6 CTN) in Espresso | GOODDEGG</t>
+          <t>HANNA Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I173" s="36" t="inlineStr">
         <is>
-          <t>The HANNA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HANNA Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J173" s="36" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="H174" s="36" t="inlineStr">
         <is>
-          <t>HANNA Table Lamp (6 CTN) in Gray | GOODDEGG</t>
+          <t>HANNA Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I174" s="36" t="inlineStr">
         <is>
-          <t>The HANNA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HANNA Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J174" s="36" t="inlineStr">
@@ -25732,12 +25732,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>IRA 32.5"H Table Lamp in Silver Clear | GOODDEGG</t>
+          <t>IRA 32.5"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>The IRA H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IRA 32.5"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -25875,12 +25875,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>IRA Table Lamp in Gold | GOODDEGG</t>
+          <t>IRA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>The IRA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IRA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -26023,12 +26023,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>ISA Table Lamp in Black | GOODDEGG</t>
+          <t>ISA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>The ISA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ISA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -26166,12 +26166,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>IVY Ceiling Lamp in Chrome | GOODDEGG</t>
+          <t>IVY Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>The IVY Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IVY Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -26309,12 +26309,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>IVY Floor Lamp in Chrome | GOODDEGG</t>
+          <t>IVY Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>The IVY Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IVY Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -26453,12 +26453,12 @@
       </c>
       <c r="H180" s="39" t="inlineStr">
         <is>
-          <t>IVY Table Lamp in Chrome | GOODDEGG</t>
+          <t>IVY Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I180" s="39" t="inlineStr">
         <is>
-          <t>The IVY Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IVY Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J180" s="39" t="inlineStr">
@@ -26599,12 +26599,12 @@
       </c>
       <c r="H181" s="39" t="inlineStr">
         <is>
-          <t>IVY Table Lamp in Gold Ivory | GOODDEGG</t>
+          <t>IVY Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I181" s="39" t="inlineStr">
         <is>
-          <t>The IVY Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IVY Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J181" s="39" t="inlineStr">
@@ -26742,12 +26742,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>IYANNA Arch Lamp in Silver Beige | GOODDEGG</t>
+          <t>IYANNA Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>The IYANNA Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>IYANNA Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -26887,12 +26887,12 @@
       </c>
       <c r="H183" s="45" t="inlineStr">
         <is>
-          <t>JADA Ceiling Lamp in Chrome Black | GOODDEGG</t>
+          <t>JADA Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I183" s="45" t="inlineStr">
         <is>
-          <t>The JADA Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JADA Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J183" s="45" t="inlineStr">
@@ -27034,12 +27034,12 @@
       </c>
       <c r="H184" s="45" t="inlineStr">
         <is>
-          <t>JADA Ceiling Lamp in Chrome White | GOODDEGG</t>
+          <t>JADA Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I184" s="45" t="inlineStr">
         <is>
-          <t>The JADA Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JADA Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J184" s="45" t="inlineStr">
@@ -27181,12 +27181,12 @@
       </c>
       <c r="H185" s="48" t="inlineStr">
         <is>
-          <t>JADA Floor Lamp in Chrome Black | GOODDEGG</t>
+          <t>JADA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I185" s="48" t="inlineStr">
         <is>
-          <t>The JADA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JADA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J185" s="48" t="inlineStr">
@@ -27328,12 +27328,12 @@
       </c>
       <c r="H186" s="48" t="inlineStr">
         <is>
-          <t>JADA Floor Lamp in Chrome White | GOODDEGG</t>
+          <t>JADA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I186" s="48" t="inlineStr">
         <is>
-          <t>The JADA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JADA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J186" s="48" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="H187" s="64" t="inlineStr">
         <is>
-          <t>JADA Table Lamp in Chrome Black | GOODDEGG</t>
+          <t>JADA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I187" s="64" t="inlineStr">
         <is>
-          <t>The JADA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JADA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J187" s="64" t="inlineStr">
@@ -27622,12 +27622,12 @@
       </c>
       <c r="H188" s="64" t="inlineStr">
         <is>
-          <t>JADA Table Lamp in Chrome White | GOODDEGG</t>
+          <t>JADA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I188" s="64" t="inlineStr">
         <is>
-          <t>The JADA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JADA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J188" s="64" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>JANA 30"H Gray Glass Table Lamp in Gray | GOODDEGG</t>
+          <t>JANA 30"H Gray Glass Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>The JANA H Glass Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JANA 30"H Gray Glass Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -27906,12 +27906,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>JEN Ceiling Lamp in Clear | GOODDEGG</t>
+          <t>JEN Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>The JEN Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JEN Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -28053,12 +28053,12 @@
       </c>
       <c r="H191" s="57" t="inlineStr">
         <is>
-          <t>JESS Arch Lamp in Antique Gold | GOODDEGG</t>
+          <t>JESS Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I191" s="57" t="inlineStr">
         <is>
-          <t>The JESS Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JESS Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J191" s="57" t="inlineStr">
@@ -28197,12 +28197,12 @@
       </c>
       <c r="H192" s="57" t="inlineStr">
         <is>
-          <t>JESS Arch Lamp in Black | GOODDEGG</t>
+          <t>JESS Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I192" s="57" t="inlineStr">
         <is>
-          <t>The JESS Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JESS Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J192" s="57" t="inlineStr">
@@ -28341,12 +28341,12 @@
       </c>
       <c r="H193" s="57" t="inlineStr">
         <is>
-          <t>JESS Arch Lamp in Brushed Steel | GOODDEGG</t>
+          <t>JESS Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I193" s="57" t="inlineStr">
         <is>
-          <t>The JESS Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JESS Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J193" s="57" t="inlineStr">
@@ -28484,12 +28484,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>JESSICA 17"H Steel Table Lamp in Chrome Nickel | GOODDEGG</t>
+          <t>JESSICA 17"H Steel Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>The JESSICA H Steel Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JESSICA 17"H Steel Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -28627,12 +28627,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>JULIE 62"H Crystal Chrome Arch Lamp in Chrome | GOODDEGG</t>
+          <t>JULIE 62"H Crystal Chrome Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>The JULIE H Crystal Chrome Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JULIE 62"H Crystal Chrome Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
@@ -28770,12 +28770,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>KAITLYN 12"H Crystal Chrome Table Lamp in Chrome | GOODDEGG</t>
+          <t>KAITLYN 12"H Crystal Chrome Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>The KAITLYN H Crystal Chrome Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KAITLYN 12"H Crystal Chrome Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
@@ -28913,12 +28913,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>KIT Floor Lamp in Metal, Crystal | GOODDEGG</t>
+          <t>KIT Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>The KIT Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIT Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
@@ -29059,12 +29059,12 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>LEE 28.5"H Table Lamp in Gold Clear | GOODDEGG</t>
+          <t>LEE 28.5"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>The LEE H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEE 28.5"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
@@ -29200,12 +29200,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>LIA 13"H Table Lamp in Gold | GOODDEGG</t>
+          <t>LIA 13"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>The LIA H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LIA 13"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
@@ -29343,12 +29343,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>LILA 19"H Ceiling Lamp in Silver | GOODDEGG</t>
+          <t>LILA 19"H Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>The LILA H Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LILA 19"H Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
@@ -29491,12 +29491,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>LILA 30"H Table Lamp in Silver | GOODDEGG</t>
+          <t>LILA 30"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>The LILA H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LILA 30"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -29637,12 +29637,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>LILA Floor Lamp in Silver | GOODDEGG</t>
+          <t>LILA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>The LILA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LILA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -29778,12 +29778,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>LUNA Table Lamp (2 CTN) in Brown | GOODDEGG</t>
+          <t>LUNA Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>The LUNA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUNA Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
@@ -29920,12 +29920,12 @@
       </c>
       <c r="H204" s="45" t="inlineStr">
         <is>
-          <t>LUZ Table Lamp in Antique Gold | GOODDEGG</t>
+          <t>LUZ Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I204" s="45" t="inlineStr">
         <is>
-          <t>The LUZ Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUZ Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J204" s="45" t="inlineStr">
@@ -30064,12 +30064,12 @@
       </c>
       <c r="H205" s="45" t="inlineStr">
         <is>
-          <t>LUZ Table Lamp in Silver | GOODDEGG</t>
+          <t>LUZ Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I205" s="45" t="inlineStr">
         <is>
-          <t>The LUZ Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUZ Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J205" s="45" t="inlineStr">
@@ -30207,12 +30207,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>MEA Ceiling Lamp in Black | GOODDEGG</t>
+          <t>MEA Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>The MEA Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEA Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -30349,12 +30349,12 @@
       </c>
       <c r="H207" s="66" t="inlineStr">
         <is>
-          <t>MEG Floor Lamp in Clear | GOODDEGG</t>
+          <t>MEG Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I207" s="66" t="inlineStr">
         <is>
-          <t>The MEG Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEG Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J207" s="66" t="inlineStr">
@@ -30493,12 +30493,12 @@
       </c>
       <c r="H208" s="66" t="inlineStr">
         <is>
-          <t>MEG Floor Lamp in Black Chrome | GOODDEGG</t>
+          <t>MEG Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I208" s="66" t="inlineStr">
         <is>
-          <t>The MEG Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEG Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J208" s="66" t="inlineStr">
@@ -30637,12 +30637,12 @@
       </c>
       <c r="H209" s="57" t="inlineStr">
         <is>
-          <t>MEG Table Lamp in Clear | GOODDEGG</t>
+          <t>MEG Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I209" s="57" t="inlineStr">
         <is>
-          <t>The MEG Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEG Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J209" s="57" t="inlineStr">
@@ -30781,12 +30781,12 @@
       </c>
       <c r="H210" s="57" t="inlineStr">
         <is>
-          <t>MEG Table Lamp in Black Chrome | GOODDEGG</t>
+          <t>MEG Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I210" s="57" t="inlineStr">
         <is>
-          <t>The MEG Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEG Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J210" s="57" t="inlineStr">
@@ -30924,12 +30924,12 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>MYDA Table Lamp in Silver White | GOODDEGG</t>
+          <t>MYDA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>The MYDA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MYDA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
@@ -31065,12 +31065,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>NAYA 11"H Table Lamp (2 CTN) in Espresso Off-White | GOODDEGG</t>
+          <t>NAYA 11"H Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>The NAYA H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAYA 11"H Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
@@ -31214,12 +31214,12 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>NAYA Table Lamp Black in Chrome Black | GOODDEGG</t>
+          <t>NAYA Table Lamp, Black | GOODDEGG</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>The NAYA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAYA Table Lamp, Black Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
@@ -31368,12 +31368,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>NAYA Table Lamp White in Chrome White | GOODDEGG</t>
+          <t>NAYA Table Lamp, White | GOODDEGG</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>The NAYA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NAYA Table Lamp, White Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
@@ -31514,12 +31514,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>NENA 29"H Table Lamp in Silver | GOODDEGG</t>
+          <t>NENA 29"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>The NENA H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NENA 29"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -31663,12 +31663,12 @@
       </c>
       <c r="H216" s="30" t="inlineStr">
         <is>
-          <t>NIKI Table Lamp (6 CTN) in Black | GOODDEGG</t>
+          <t>NIKI Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I216" s="30" t="inlineStr">
         <is>
-          <t>The NIKI Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIKI Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J216" s="30" t="inlineStr">
@@ -31818,12 +31818,12 @@
       </c>
       <c r="H217" s="30" t="inlineStr">
         <is>
-          <t>NIKI Table Lamp (6 CTN) in Ivory | GOODDEGG</t>
+          <t>NIKI Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I217" s="30" t="inlineStr">
         <is>
-          <t>The NIKI Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NIKI Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J217" s="30" t="inlineStr">
@@ -31965,12 +31965,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>OONA Table Lamp (2 CTN) in White Clear | GOODDEGG</t>
+          <t>OONA Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>The OONA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OONA Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -32106,12 +32106,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>OPAL Table Lamp (2 CTN) in Silver Black | GOODDEGG</t>
+          <t>OPAL Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>The OPAL Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OPAL Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -32249,12 +32249,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>PERLA Table Lamp in Chrome | GOODDEGG</t>
+          <t>PERLA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>The PERLA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PERLA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -32395,12 +32395,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>RACHEL 15"H Glass Amber Table Lamp in Amber | GOODDEGG</t>
+          <t>RACHEL 15"H Glass Amber Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>The RACHEL H Glass Amber Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RACHEL 15"H Glass Amber Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -32538,12 +32538,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>RENA Table Lamp in Chrome | GOODDEGG</t>
+          <t>RENA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>The RENA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RENA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
@@ -32684,12 +32684,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>RENE Arch Lamp in White Chrome | GOODDEGG</t>
+          <t>RENE Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>The RENE Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RENE Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
@@ -32827,12 +32827,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>RIGEL 31 1 2"H Ceiling Lamp in Silver | GOODDEGG</t>
+          <t>RIGEL 31 1/2"H Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>The RIGEL or H Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RIGEL 31 1/2"H Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -32970,12 +32970,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>RIGEL 35"H Table Lamp in Silver | GOODDEGG</t>
+          <t>RIGEL 35"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>The RIGEL H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RIGEL 35"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
@@ -33113,12 +33113,12 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>RIGEL 63"H Floor Lamp in Silver | GOODDEGG</t>
+          <t>RIGEL 63"H Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>The RIGEL H Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RIGEL 63"H Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
@@ -33254,12 +33254,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>ROSALIE Table Lamp (2 CTN) in Antique Black | GOODDEGG</t>
+          <t>ROSALIE Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>The ROSALIE Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ROSALIE Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -33395,12 +33395,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>SAM 6"H Table Lamp in Black | GOODDEGG</t>
+          <t>SAM 6"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>The SAM H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SAM 6"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -33544,12 +33544,12 @@
       </c>
       <c r="H229" s="39" t="inlineStr">
         <is>
-          <t>SCARLETT Table Lamp (6 CTN) in Burgundy | GOODDEGG</t>
+          <t>SCARLETT Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I229" s="39" t="inlineStr">
         <is>
-          <t>The SCARLETT Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCARLETT Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J229" s="39" t="inlineStr">
@@ -33699,12 +33699,12 @@
       </c>
       <c r="H230" s="39" t="inlineStr">
         <is>
-          <t>SCARLETT Table Lamp (6 CTN) in Black | GOODDEGG</t>
+          <t>SCARLETT Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I230" s="39" t="inlineStr">
         <is>
-          <t>The SCARLETT Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCARLETT Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J230" s="39" t="inlineStr">
@@ -33854,12 +33854,12 @@
       </c>
       <c r="H231" s="39" t="inlineStr">
         <is>
-          <t>SCARLETT Table Lamp (6 CTN) in Ivory | GOODDEGG</t>
+          <t>SCARLETT Table Lamp, (6/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I231" s="39" t="inlineStr">
         <is>
-          <t>The SCARLETT Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCARLETT Table Lamp, (6/CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J231" s="39" t="inlineStr">
@@ -34001,12 +34001,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>SELMA Table Lamp (2 CTN) in Beige Gold | GOODDEGG</t>
+          <t>SELMA Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>The SELMA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SELMA Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -34145,12 +34145,12 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>SIMONE Table Lamp in White Silver | GOODDEGG</t>
+          <t>SIMONE Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>The SIMONE Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIMONE Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
@@ -34286,12 +34286,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>SOPHY Ceiling Lamp in White Chrome | GOODDEGG</t>
+          <t>SOPHY Ceiling Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>The SOPHY Ceiling Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOPHY Ceiling Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -34432,12 +34432,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>SOPHY Floor Lamp in White Chrome | GOODDEGG</t>
+          <t>SOPHY Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>The SOPHY Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOPHY Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -34578,12 +34578,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>SOPHY Table Lamp in White Chrome | GOODDEGG</t>
+          <t>SOPHY Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>The SOPHY Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SOPHY Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -34725,12 +34725,12 @@
       </c>
       <c r="H237" s="57" t="inlineStr">
         <is>
-          <t>SPRIG Table Lamp (2 CTN) in Black | GOODDEGG</t>
+          <t>SPRIG Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I237" s="57" t="inlineStr">
         <is>
-          <t>The SPRIG Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SPRIG Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J237" s="57" t="inlineStr">
@@ -34873,12 +34873,12 @@
       </c>
       <c r="H238" s="57" t="inlineStr">
         <is>
-          <t>SPRIG Table Lamp (2 CTN) in Red | GOODDEGG</t>
+          <t>SPRIG Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I238" s="57" t="inlineStr">
         <is>
-          <t>The SPRIG Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SPRIG Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J238" s="57" t="inlineStr">
@@ -35021,12 +35021,12 @@
       </c>
       <c r="H239" s="57" t="inlineStr">
         <is>
-          <t>SPRIG Table Lamp (2 CTN) in White | GOODDEGG</t>
+          <t>SPRIG Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I239" s="57" t="inlineStr">
         <is>
-          <t>The SPRIG Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SPRIG Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J239" s="57" t="inlineStr">
@@ -35168,12 +35168,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>SUZY 10"H Table Lamp (2 CTN) in Light Caramel Espresso | GOODD</t>
+          <t>SUZY 10"H Table Lamp (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>The SUZY H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SUZY 10"H Table Lamp (2 / CTN) Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
@@ -35309,12 +35309,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>TARA Table Lamp in Gold | GOODDEGG</t>
+          <t>TARA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>The TARA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TARA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
@@ -35450,12 +35450,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>TERI 13"H Table Lamp in Silver | GOODDEGG</t>
+          <t>TERI 13"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>The TERI H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TERI 13"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
@@ -35591,12 +35591,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>TERRI Table Lamp in Silver | GOODDEGG</t>
+          <t>TERRI Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>The TERRI Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TERRI Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
@@ -35734,12 +35734,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>TINA Arch Lamp in Chrome | GOODDEGG</t>
+          <t>TINA Arch Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>The TINA Arch Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TINA Arch Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
@@ -35880,12 +35880,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>URIEN Table Lamp in Black Antique Gold | GOODDEGG</t>
+          <t>URIEN Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>The URIEN Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>URIEN Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
@@ -36021,12 +36021,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>XIA Table Lamp in White | GOODDEGG</t>
+          <t>XIA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>The XIA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>XIA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -36163,12 +36163,12 @@
       </c>
       <c r="H247" s="59" t="inlineStr">
         <is>
-          <t>ZAYA Floor Lamp in Stained Gold | GOODDEGG</t>
+          <t>ZAYA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I247" s="59" t="inlineStr">
         <is>
-          <t>The ZAYA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZAYA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J247" s="59" t="inlineStr">
@@ -36307,12 +36307,12 @@
       </c>
       <c r="H248" s="59" t="inlineStr">
         <is>
-          <t>ZAYA Floor Lamp in Brushed Steel | GOODDEGG</t>
+          <t>ZAYA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I248" s="59" t="inlineStr">
         <is>
-          <t>The ZAYA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZAYA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J248" s="59" t="inlineStr">
@@ -36451,12 +36451,12 @@
       </c>
       <c r="H249" s="51" t="inlineStr">
         <is>
-          <t>ZAYA Table Lamp in Stained Gold | GOODDEGG</t>
+          <t>ZAYA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I249" s="51" t="inlineStr">
         <is>
-          <t>The ZAYA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZAYA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J249" s="51" t="inlineStr">
@@ -36599,12 +36599,12 @@
       </c>
       <c r="H250" s="51" t="inlineStr">
         <is>
-          <t>ZAYA Table Lamp in Brushed Steel | GOODDEGG</t>
+          <t>ZAYA Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I250" s="51" t="inlineStr">
         <is>
-          <t>The ZAYA Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZAYA Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J250" s="51" t="inlineStr">
@@ -36747,12 +36747,12 @@
       </c>
       <c r="H251" s="30" t="inlineStr">
         <is>
-          <t>ZERA Floor Lamp in Black Gold | GOODDEGG</t>
+          <t>ZERA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I251" s="30" t="inlineStr">
         <is>
-          <t>The ZERA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZERA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J251" s="30" t="inlineStr">
@@ -36891,12 +36891,12 @@
       </c>
       <c r="H252" s="30" t="inlineStr">
         <is>
-          <t>ZERA Floor Lamp in White Gold | GOODDEGG</t>
+          <t>ZERA Floor Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I252" s="30" t="inlineStr">
         <is>
-          <t>The ZERA Floor Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZERA Floor Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J252" s="30" t="inlineStr">
@@ -37034,12 +37034,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>ZOE 6"H Table Lamp in Black | GOODDEGG</t>
+          <t>ZOE 6"H Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>The ZOE H Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOE 6"H Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -37175,12 +37175,12 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>ZOE Table Lamp in Black | GOODDEGG</t>
+          <t>ZOE Table Lamp | GOODDEGG</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>The ZOE Table Lamp brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ZOE Table Lamp Lighting supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
@@ -37316,12 +37316,12 @@
       </c>
       <c r="H255" s="54" t="inlineStr">
         <is>
-          <t>ACASO Accent Chair in Mushroom | GOODDEGG</t>
+          <t>ACASO Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I255" s="54" t="inlineStr">
         <is>
-          <t>The ACASO Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACASO Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J255" s="54" t="inlineStr">
@@ -37457,12 +37457,12 @@
       </c>
       <c r="H256" s="54" t="inlineStr">
         <is>
-          <t>ACASO Accent Chair in White | GOODDEGG</t>
+          <t>ACASO Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I256" s="54" t="inlineStr">
         <is>
-          <t>The ACASO Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACASO Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J256" s="54" t="inlineStr">
@@ -37598,12 +37598,12 @@
       </c>
       <c r="H257" s="68" t="inlineStr">
         <is>
-          <t>ALCOBA Accent Chair in Mushroom | GOODDEGG</t>
+          <t>ALCOBA Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I257" s="68" t="inlineStr">
         <is>
-          <t>The ALCOBA Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALCOBA Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J257" s="68" t="inlineStr">
@@ -37739,12 +37739,12 @@
       </c>
       <c r="H258" s="68" t="inlineStr">
         <is>
-          <t>ALCOBA Accent Chair in Taupe | GOODDEGG</t>
+          <t>ALCOBA Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I258" s="68" t="inlineStr">
         <is>
-          <t>The ALCOBA Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALCOBA Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J258" s="68" t="inlineStr">
@@ -37882,12 +37882,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>ASSENTOFT Side Chair (2PC CTN) in Black | GOODDEGG</t>
+          <t>ASSENTOFT Side Chair (2PC / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>The ASSENTOFT Side Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ASSENTOFT Side Chair (2PC / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -38023,12 +38023,12 @@
       </c>
       <c r="H260" s="66" t="inlineStr">
         <is>
-          <t>BEDALE Accent Chair in Mushroom | GOODDEGG</t>
+          <t>BEDALE Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I260" s="66" t="inlineStr">
         <is>
-          <t>The BEDALE Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BEDALE Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J260" s="66" t="inlineStr">
@@ -38164,12 +38164,12 @@
       </c>
       <c r="H261" s="66" t="inlineStr">
         <is>
-          <t>BEDALE Accent Chair in White | GOODDEGG</t>
+          <t>BEDALE Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I261" s="66" t="inlineStr">
         <is>
-          <t>The BEDALE Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BEDALE Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J261" s="66" t="inlineStr">
@@ -38306,12 +38306,12 @@
       </c>
       <c r="H262" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Chocolate Brown | GOODDEG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I262" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J262" s="59" t="inlineStr">
@@ -38450,12 +38450,12 @@
       </c>
       <c r="H263" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Dark Gray | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I263" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J263" s="59" t="inlineStr">
@@ -38594,12 +38594,12 @@
       </c>
       <c r="H264" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Olive Green | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I264" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J264" s="59" t="inlineStr">
@@ -38738,12 +38738,12 @@
       </c>
       <c r="H265" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Sky Blue | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I265" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J265" s="59" t="inlineStr">
@@ -38882,12 +38882,12 @@
       </c>
       <c r="H266" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Dark Teal | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I266" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J266" s="59" t="inlineStr">
@@ -39026,12 +39026,12 @@
       </c>
       <c r="H267" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Taupe | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I267" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J267" s="59" t="inlineStr">
@@ -39170,12 +39170,12 @@
       </c>
       <c r="H268" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in White | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I268" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J268" s="59" t="inlineStr">
@@ -39314,12 +39314,12 @@
       </c>
       <c r="H269" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel in Yellow | GOODDEGG</t>
+          <t>BELPER Power Glider Recliner w/ Swivel | GOODDEGG</t>
         </is>
       </c>
       <c r="I269" s="59" t="inlineStr">
         <is>
-          <t>BELPER Power Glider Recliner w/ Swivel adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELPER Power Glider Recliner w/ Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J269" s="59" t="inlineStr">
@@ -39460,12 +39460,12 @@
       </c>
       <c r="H270" s="51" t="inlineStr">
         <is>
-          <t>FLORENS Swivel Chair in Dark Blue | GOODDEGG</t>
+          <t>FLORENS Swivel Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I270" s="51" t="inlineStr">
         <is>
-          <t>The FLORENS Swivel Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FLORENS Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J270" s="51" t="inlineStr">
@@ -39606,12 +39606,12 @@
       </c>
       <c r="H271" s="51" t="inlineStr">
         <is>
-          <t>FLORENS Swivel Chair in Light Brown | GOODDEGG</t>
+          <t>FLORENS Swivel Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I271" s="51" t="inlineStr">
         <is>
-          <t>The FLORENS Swivel Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FLORENS Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J271" s="51" t="inlineStr">
@@ -39752,12 +39752,12 @@
       </c>
       <c r="H272" s="51" t="inlineStr">
         <is>
-          <t>FLORENS Swivel Chair in Dark Gray | GOODDEGG</t>
+          <t>FLORENS Swivel Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I272" s="51" t="inlineStr">
         <is>
-          <t>The FLORENS Swivel Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FLORENS Swivel Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J272" s="51" t="inlineStr">
@@ -39896,12 +39896,12 @@
       </c>
       <c r="H273" s="54" t="inlineStr">
         <is>
-          <t>PERCE Office Chair in Black | GOODDEGG</t>
+          <t>PERCE Office Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I273" s="54" t="inlineStr">
         <is>
-          <t>The PERCE Office Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PERCE Office Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J273" s="54" t="inlineStr">
@@ -40040,12 +40040,12 @@
       </c>
       <c r="H274" s="54" t="inlineStr">
         <is>
-          <t>PERCE Office Chair in Brown | GOODDEGG</t>
+          <t>PERCE Office Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I274" s="54" t="inlineStr">
         <is>
-          <t>The PERCE Office Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PERCE Office Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J274" s="54" t="inlineStr">
@@ -40183,12 +40183,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>SHELIA Chair w/ Ottoman in Purple | GOODDEGG</t>
+          <t>SHELIA Chair w/ Ottoman | GOODDEGG</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>The SHELIA Chair w/ Ottoman adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHELIA Chair w/ Ottoman supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -40325,12 +40325,12 @@
       </c>
       <c r="H276" s="51" t="inlineStr">
         <is>
-          <t>STILLWATER Chaise in Beige | GOODDEGG</t>
+          <t>STILLWATER Chaise | GOODDEGG</t>
         </is>
       </c>
       <c r="I276" s="51" t="inlineStr">
         <is>
-          <t>The STILLWATER Chaise adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STILLWATER Chaise Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J276" s="51" t="inlineStr">
@@ -40469,12 +40469,12 @@
       </c>
       <c r="H277" s="51" t="inlineStr">
         <is>
-          <t>STILLWATER Chaise in Gray | GOODDEGG</t>
+          <t>STILLWATER Chaise | GOODDEGG</t>
         </is>
       </c>
       <c r="I277" s="51" t="inlineStr">
         <is>
-          <t>The STILLWATER Chaise adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STILLWATER Chaise Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J277" s="51" t="inlineStr">
@@ -40614,12 +40614,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>VAUGH Accent Chair in Rustic Brown | GOODDEGG</t>
+          <t>VAUGH Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>The VAUGH Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VAUGH Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
@@ -40757,12 +40757,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>WATERVILLE Accent Chair in Beige Dark Cherry | GOODDEGG</t>
+          <t>WATERVILLE Accent Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>The WATERVILLE Accent Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WATERVILLE Accent Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -40899,12 +40899,12 @@
       </c>
       <c r="H280" s="25" t="inlineStr">
         <is>
-          <t>ACKE Computer Desk in Black | GOODDEGG</t>
+          <t>ACKE Computer Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I280" s="25" t="inlineStr">
         <is>
-          <t>The ACKE Computer Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACKE Computer Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J280" s="25" t="inlineStr">
@@ -41043,12 +41043,12 @@
       </c>
       <c r="H281" s="25" t="inlineStr">
         <is>
-          <t>ACKE Computer Desk in Gray | GOODDEGG</t>
+          <t>ACKE Computer Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I281" s="25" t="inlineStr">
         <is>
-          <t>The ACKE Computer Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACKE Computer Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J281" s="25" t="inlineStr">
@@ -41187,12 +41187,12 @@
       </c>
       <c r="H282" s="25" t="inlineStr">
         <is>
-          <t>ACKE Computer Desk in White | GOODDEGG</t>
+          <t>ACKE Computer Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I282" s="25" t="inlineStr">
         <is>
-          <t>The ACKE Computer Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ACKE Computer Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J282" s="25" t="inlineStr">
@@ -41331,12 +41331,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>ALVIN Writing Desk in Brown Chrome | GOODDEGG</t>
+          <t>ALVIN Writing Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>The ALVIN Writing Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ALVIN Writing Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -41474,12 +41474,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>BADEN Computer Desk in Oak Black | GOODDEGG</t>
+          <t>BADEN Computer Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>The BADEN Computer Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BADEN Computer Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -41615,12 +41615,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>CORI Desk in Antique Black | GOODDEGG</t>
+          <t>CORI Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>The CORI Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CORI Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -41756,12 +41756,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Delphine Desk in Gold Black | GOODDEGG</t>
+          <t>DELPHINE Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>The DELPHINE Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DELPHINE Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -41906,12 +41906,12 @@
       </c>
       <c r="H287" s="30" t="inlineStr">
         <is>
-          <t>FREIBURG Corner Desk in Antique Blue | GOODDEGG</t>
+          <t>FREIBURG Corner Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I287" s="30" t="inlineStr">
         <is>
-          <t>The FREIBURG Corner Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FREIBURG Corner Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J287" s="30" t="inlineStr">
@@ -42051,12 +42051,12 @@
       </c>
       <c r="H288" s="30" t="inlineStr">
         <is>
-          <t>FREIBURG Corner Desk in Antique White | GOODDEGG</t>
+          <t>FREIBURG Corner Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I288" s="30" t="inlineStr">
         <is>
-          <t>The FREIBURG Corner Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FREIBURG Corner Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J288" s="30" t="inlineStr">
@@ -42196,12 +42196,12 @@
       </c>
       <c r="H289" s="30" t="inlineStr">
         <is>
-          <t>FREIBURG Corner Desk in Walnut | GOODDEGG</t>
+          <t>FREIBURG Corner Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I289" s="30" t="inlineStr">
         <is>
-          <t>The FREIBURG Corner Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FREIBURG Corner Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J289" s="30" t="inlineStr">
@@ -42346,12 +42346,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Galarga Lift top Corner Desk in Antique White | GOODDEGG</t>
+          <t>GALARGA Lift-top Corner Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>The GALARGA Lift creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GALARGA Lift-top Corner Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -42489,12 +42489,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>HALSTEIN Writing Desk in Light Walnut Gold | GOODDEGG</t>
+          <t>HALSTEIN Writing Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>The HALSTEIN Writing Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HALSTEIN Writing Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
@@ -42633,12 +42633,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>LOKE Computer Desk in White Chrome | GOODDEGG</t>
+          <t>LOKE Computer Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>The LOKE Computer Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOKE Computer Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
@@ -42774,12 +42774,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Mccredmond Desk W USB in Silver | GOODDEGG</t>
+          <t>MCCREDMOND Desk w/ USB | GOODDEGG</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>The MCCREDMOND Desk w/ USB creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MCCREDMOND Desk w/ USB supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
@@ -42915,12 +42915,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>OLGA Desk in Antique Black | GOODDEGG</t>
+          <t>OLGA Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>The OLGA Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLGA Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
@@ -43058,12 +43058,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>PORTO Corner Desk in Black | GOODDEGG</t>
+          <t>PORTO Corner Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>The PORTO Corner Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PORTO Corner Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -43201,12 +43201,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>RELIANCE Writing Desk in Antique Oak | GOODDEGG</t>
+          <t>RELIANCE Writing Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>The RELIANCE Writing Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RELIANCE Writing Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
@@ -43343,12 +43343,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>TENSED Writing Desk in Walnut Sand Black | GOODDEGG</t>
+          <t>TENSED Writing Desk | GOODDEGG</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>The TENSED Writing Desk creates a focused workspace for daily tasks. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TENSED Writing Desk supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
@@ -43485,12 +43485,12 @@
       </c>
       <c r="H298" s="32" t="inlineStr">
         <is>
-          <t>AILEEN Storage Stool in Charcoal | GOODDEGG</t>
+          <t>AILEEN Storage Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I298" s="32" t="inlineStr">
         <is>
-          <t>The AILEEN Storage Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AILEEN Storage Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J298" s="32" t="inlineStr">
@@ -43629,12 +43629,12 @@
       </c>
       <c r="H299" s="32" t="inlineStr">
         <is>
-          <t>AILEEN Storage Stool in Beige | GOODDEGG</t>
+          <t>AILEEN Storage Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I299" s="32" t="inlineStr">
         <is>
-          <t>The AILEEN Storage Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>AILEEN Storage Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J299" s="32" t="inlineStr">
@@ -43773,12 +43773,12 @@
       </c>
       <c r="H300" s="39" t="inlineStr">
         <is>
-          <t>CYNTHIA Stool in Brown | GOODDEGG</t>
+          <t>CYNTHIA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I300" s="39" t="inlineStr">
         <is>
-          <t>The CYNTHIA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYNTHIA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J300" s="39" t="inlineStr">
@@ -43917,12 +43917,12 @@
       </c>
       <c r="H301" s="39" t="inlineStr">
         <is>
-          <t>CYNTHIA Stool in Green | GOODDEGG</t>
+          <t>CYNTHIA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I301" s="39" t="inlineStr">
         <is>
-          <t>The CYNTHIA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYNTHIA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J301" s="39" t="inlineStr">
@@ -44061,12 +44061,12 @@
       </c>
       <c r="H302" s="39" t="inlineStr">
         <is>
-          <t>CYNTHIA Stool in Saddle Brown | GOODDEGG</t>
+          <t>CYNTHIA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I302" s="39" t="inlineStr">
         <is>
-          <t>The CYNTHIA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYNTHIA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J302" s="39" t="inlineStr">
@@ -44205,12 +44205,12 @@
       </c>
       <c r="H303" s="39" t="inlineStr">
         <is>
-          <t>CYNTHIA Stool in Beige | GOODDEGG</t>
+          <t>CYNTHIA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I303" s="39" t="inlineStr">
         <is>
-          <t>The CYNTHIA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CYNTHIA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J303" s="39" t="inlineStr">
@@ -44351,12 +44351,12 @@
       </c>
       <c r="H304" s="48" t="inlineStr">
         <is>
-          <t>DOROTHEA Stool in Black | GOODDEGG</t>
+          <t>DOROTHEA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I304" s="48" t="inlineStr">
         <is>
-          <t>The DOROTHEA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DOROTHEA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J304" s="48" t="inlineStr">
@@ -44497,12 +44497,12 @@
       </c>
       <c r="H305" s="48" t="inlineStr">
         <is>
-          <t>DOROTHEA Stool in White | GOODDEGG</t>
+          <t>DOROTHEA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I305" s="48" t="inlineStr">
         <is>
-          <t>The DOROTHEA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DOROTHEA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J305" s="48" t="inlineStr">
@@ -44643,12 +44643,12 @@
       </c>
       <c r="H306" s="64" t="inlineStr">
         <is>
-          <t>DOTTIE Stool in Black | GOODDEGG</t>
+          <t>DOTTIE Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I306" s="64" t="inlineStr">
         <is>
-          <t>The DOTTIE Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DOTTIE Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J306" s="64" t="inlineStr">
@@ -44789,12 +44789,12 @@
       </c>
       <c r="H307" s="64" t="inlineStr">
         <is>
-          <t>DOTTIE Stool in White | GOODDEGG</t>
+          <t>DOTTIE Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I307" s="64" t="inlineStr">
         <is>
-          <t>The DOTTIE Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DOTTIE Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J307" s="64" t="inlineStr">
@@ -44935,12 +44935,12 @@
       </c>
       <c r="H308" s="66" t="inlineStr">
         <is>
-          <t>JANETTA Stool in Brown | GOODDEGG</t>
+          <t>JANETTA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I308" s="66" t="inlineStr">
         <is>
-          <t>The JANETTA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JANETTA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J308" s="66" t="inlineStr">
@@ -45081,12 +45081,12 @@
       </c>
       <c r="H309" s="66" t="inlineStr">
         <is>
-          <t>JANETTA Stool in Green | GOODDEGG</t>
+          <t>JANETTA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I309" s="66" t="inlineStr">
         <is>
-          <t>The JANETTA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JANETTA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J309" s="66" t="inlineStr">
@@ -45227,12 +45227,12 @@
       </c>
       <c r="H310" s="66" t="inlineStr">
         <is>
-          <t>JANETTA Stool in Saddle Brown | GOODDEGG</t>
+          <t>JANETTA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I310" s="66" t="inlineStr">
         <is>
-          <t>The JANETTA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JANETTA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J310" s="66" t="inlineStr">
@@ -45373,12 +45373,12 @@
       </c>
       <c r="H311" s="66" t="inlineStr">
         <is>
-          <t>JANETTA Stool in Beige | GOODDEGG</t>
+          <t>JANETTA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I311" s="66" t="inlineStr">
         <is>
-          <t>The JANETTA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JANETTA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J311" s="66" t="inlineStr">
@@ -45517,12 +45517,12 @@
       </c>
       <c r="H312" s="36" t="inlineStr">
         <is>
-          <t>KRYSTEN Storage Stool in Green | GOODDEGG</t>
+          <t>KRYSTEN Storage Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I312" s="36" t="inlineStr">
         <is>
-          <t>The KRYSTEN Storage Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KRYSTEN Storage Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J312" s="36" t="inlineStr">
@@ -45661,12 +45661,12 @@
       </c>
       <c r="H313" s="36" t="inlineStr">
         <is>
-          <t>KRYSTEN Storage Stool in Silver Gray | GOODDEGG</t>
+          <t>KRYSTEN Storage Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I313" s="36" t="inlineStr">
         <is>
-          <t>The KRYSTEN Storage Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KRYSTEN Storage Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J313" s="36" t="inlineStr">
@@ -45805,12 +45805,12 @@
       </c>
       <c r="H314" s="36" t="inlineStr">
         <is>
-          <t>KRYSTEN Storage Stool in Beige | GOODDEGG</t>
+          <t>KRYSTEN Storage Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I314" s="36" t="inlineStr">
         <is>
-          <t>The KRYSTEN Storage Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KRYSTEN Storage Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J314" s="36" t="inlineStr">
@@ -45949,12 +45949,12 @@
       </c>
       <c r="H315" s="42" t="inlineStr">
         <is>
-          <t>THISBE Stool in Brown | GOODDEGG</t>
+          <t>THISBE Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I315" s="42" t="inlineStr">
         <is>
-          <t>The THISBE Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISBE Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J315" s="42" t="inlineStr">
@@ -46093,12 +46093,12 @@
       </c>
       <c r="H316" s="42" t="inlineStr">
         <is>
-          <t>THISBE Stool in Green | GOODDEGG</t>
+          <t>THISBE Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I316" s="42" t="inlineStr">
         <is>
-          <t>The THISBE Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISBE Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J316" s="42" t="inlineStr">
@@ -46237,12 +46237,12 @@
       </c>
       <c r="H317" s="42" t="inlineStr">
         <is>
-          <t>THISBE Stool in Saddle Brown | GOODDEGG</t>
+          <t>THISBE Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I317" s="42" t="inlineStr">
         <is>
-          <t>The THISBE Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISBE Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J317" s="42" t="inlineStr">
@@ -46381,12 +46381,12 @@
       </c>
       <c r="H318" s="42" t="inlineStr">
         <is>
-          <t>THISBE Stool in Beige | GOODDEGG</t>
+          <t>THISBE Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I318" s="42" t="inlineStr">
         <is>
-          <t>The THISBE Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>THISBE Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J318" s="42" t="inlineStr">
@@ -46525,12 +46525,12 @@
       </c>
       <c r="H319" s="57" t="inlineStr">
         <is>
-          <t>YOLANDA Stool in Dark Gray | GOODDEGG</t>
+          <t>YOLANDA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I319" s="57" t="inlineStr">
         <is>
-          <t>The YOLANDA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YOLANDA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J319" s="57" t="inlineStr">
@@ -46669,12 +46669,12 @@
       </c>
       <c r="H320" s="57" t="inlineStr">
         <is>
-          <t>YOLANDA Stool in Green | GOODDEGG</t>
+          <t>YOLANDA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I320" s="57" t="inlineStr">
         <is>
-          <t>The YOLANDA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YOLANDA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J320" s="57" t="inlineStr">
@@ -46813,12 +46813,12 @@
       </c>
       <c r="H321" s="57" t="inlineStr">
         <is>
-          <t>YOLANDA Stool in Gray | GOODDEGG</t>
+          <t>YOLANDA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I321" s="57" t="inlineStr">
         <is>
-          <t>The YOLANDA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YOLANDA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J321" s="57" t="inlineStr">
@@ -46957,12 +46957,12 @@
       </c>
       <c r="H322" s="57" t="inlineStr">
         <is>
-          <t>YOLANDA Stool in Beige | GOODDEGG</t>
+          <t>YOLANDA Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I322" s="57" t="inlineStr">
         <is>
-          <t>The YOLANDA Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YOLANDA Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J322" s="57" t="inlineStr">
@@ -47100,12 +47100,12 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>ANIKA 17" X 17" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>ANIKA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>The ANIKA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANIKA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -47246,12 +47246,12 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>ANIKA 21" X 21" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>ANIKA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>The ANIKA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ANIKA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -47392,12 +47392,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>BEA 20" X 20" Pillow (2 CTN) in Indigo | GOODDEGG</t>
+          <t>BEA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>The BEA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BEA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
@@ -47539,12 +47539,12 @@
       </c>
       <c r="H326" s="57" t="inlineStr">
         <is>
-          <t>BELLE 20" X 20" Pillow (2 CTN) in Beige | GOODDEGG</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I326" s="57" t="inlineStr">
         <is>
-          <t>The BELLE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J326" s="57" t="inlineStr">
@@ -47687,12 +47687,12 @@
       </c>
       <c r="H327" s="57" t="inlineStr">
         <is>
-          <t>BELLE 20" X 20" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I327" s="57" t="inlineStr">
         <is>
-          <t>The BELLE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J327" s="57" t="inlineStr">
@@ -47835,12 +47835,12 @@
       </c>
       <c r="H328" s="57" t="inlineStr">
         <is>
-          <t>BELLE 20" X 20" Pillow (2 CTN) in Purple | GOODDEGG</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I328" s="57" t="inlineStr">
         <is>
-          <t>The BELLE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J328" s="57" t="inlineStr">
@@ -47983,12 +47983,12 @@
       </c>
       <c r="H329" s="57" t="inlineStr">
         <is>
-          <t>BELLE 20" X 20" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I329" s="57" t="inlineStr">
         <is>
-          <t>The BELLE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J329" s="57" t="inlineStr">
@@ -48131,12 +48131,12 @@
       </c>
       <c r="H330" s="57" t="inlineStr">
         <is>
-          <t>BELLE 20" X 20" Pillow (2 CTN) in Silver | GOODDEGG</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I330" s="57" t="inlineStr">
         <is>
-          <t>The BELLE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J330" s="57" t="inlineStr">
@@ -48279,12 +48279,12 @@
       </c>
       <c r="H331" s="57" t="inlineStr">
         <is>
-          <t>BELLE 20" X 20" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I331" s="57" t="inlineStr">
         <is>
-          <t>The BELLE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BELLE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J331" s="57" t="inlineStr">
@@ -48426,12 +48426,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>BESS 20" X 20" Pillow (2 CTN) in Dark Gray | GOODDEGG</t>
+          <t>BESS 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>The BESS Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BESS 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -48572,12 +48572,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>BETH 20" X 20" Pillow (2 CTN) in Beige Indigo | GOODDEGG</t>
+          <t>BETH 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>The BETH Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BETH 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
@@ -48724,12 +48724,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>BRIA 20" X 20" Pillow Seaspray (2 CTN) in Light Teal | GOODDEGG</t>
+          <t>BRIA 20" X 20" Pillow, Seaspray (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>The BRIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRIA 20" X 20" Pillow, Seaspray (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -48865,12 +48865,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>BRIA 20" X 20" Pillow (2 CTN) in Light Beige | GOODDEGG</t>
+          <t>BRIA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>The BRIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>BRIA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
@@ -49012,12 +49012,12 @@
       </c>
       <c r="H336" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Black | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I336" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J336" s="36" t="inlineStr">
@@ -49156,12 +49156,12 @@
       </c>
       <c r="H337" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Charcoal | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I337" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J337" s="36" t="inlineStr">
@@ -49300,12 +49300,12 @@
       </c>
       <c r="H338" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Blush | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I338" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J338" s="36" t="inlineStr">
@@ -49444,12 +49444,12 @@
       </c>
       <c r="H339" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Silver | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I339" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J339" s="36" t="inlineStr">
@@ -49588,12 +49588,12 @@
       </c>
       <c r="H340" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Off-White | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I340" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J340" s="36" t="inlineStr">
@@ -49736,12 +49736,12 @@
       </c>
       <c r="H341" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Gold | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I341" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J341" s="36" t="inlineStr">
@@ -49880,12 +49880,12 @@
       </c>
       <c r="H342" s="36" t="inlineStr">
         <is>
-          <t>CAPARICA 20" X 20" Pillow in Teal | GOODDEGG</t>
+          <t>CAPARICA 20" X 20" Pillow | GOODDEGG</t>
         </is>
       </c>
       <c r="I342" s="36" t="inlineStr">
         <is>
-          <t>The CAPARICA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA 20" X 20" Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J342" s="36" t="inlineStr">
@@ -50024,12 +50024,12 @@
       </c>
       <c r="H343" s="25" t="inlineStr">
         <is>
-          <t>CAPARICA Throw in Black | GOODDEGG</t>
+          <t>CAPARICA Throw | GOODDEGG</t>
         </is>
       </c>
       <c r="I343" s="25" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J343" s="25" t="inlineStr">
@@ -50168,12 +50168,12 @@
       </c>
       <c r="H344" s="25" t="inlineStr">
         <is>
-          <t>CAPARICA Throw in Charcoal | GOODDEGG</t>
+          <t>CAPARICA Throw | GOODDEGG</t>
         </is>
       </c>
       <c r="I344" s="25" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J344" s="25" t="inlineStr">
@@ -50312,12 +50312,12 @@
       </c>
       <c r="H345" s="25" t="inlineStr">
         <is>
-          <t>CAPARICA Throw in Blush | GOODDEGG</t>
+          <t>CAPARICA Throw | GOODDEGG</t>
         </is>
       </c>
       <c r="I345" s="25" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J345" s="25" t="inlineStr">
@@ -50456,12 +50456,12 @@
       </c>
       <c r="H346" s="25" t="inlineStr">
         <is>
-          <t>CAPARICA Throw in Silver | GOODDEGG</t>
+          <t>CAPARICA Throw | GOODDEGG</t>
         </is>
       </c>
       <c r="I346" s="25" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J346" s="25" t="inlineStr">
@@ -50600,12 +50600,12 @@
       </c>
       <c r="H347" s="25" t="inlineStr">
         <is>
-          <t>CAPARICA Throw in Off-White | GOODDEGG</t>
+          <t>CAPARICA Throw | GOODDEGG</t>
         </is>
       </c>
       <c r="I347" s="25" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Pillow supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J347" s="25" t="inlineStr">
@@ -50747,12 +50747,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>CICI 18" X 18" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>CICI 18" X 18" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>The CICI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CICI 18" X 18" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -50893,12 +50893,12 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>CICI 20" X 20" Pillow (2 CTN) in Navy | GOODDEGG</t>
+          <t>CICI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>The CICI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CICI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -51039,12 +51039,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>CICI 22" X 22" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>CICI 22" X 22" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>The CICI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CICI 22" X 22" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -51185,12 +51185,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Dakotha 20" X 20" Pillow (2 ctn) in Multi | GOODDEGG</t>
+          <t>DAKOTHA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>The DAKOTHA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DAKOTHA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -51326,12 +51326,12 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>DEE 20" X 20" Pillow (2 CTN) in Indigo | GOODDEGG</t>
+          <t>DEE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>The DEE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -51472,12 +51472,12 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>DINA 20" X 20" Pillow (2 CTN) in Navy | GOODDEGG</t>
+          <t>DINA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>The DINA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DINA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -51618,12 +51618,12 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>DIOR 17" X 17" Pillow (2 CTN) in Black | GOODDEGG</t>
+          <t>DIOR 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>The DIOR Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIOR 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -51764,12 +51764,12 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>DIOR 21" X 21" Pillow (2 CTN) in Black | GOODDEGG</t>
+          <t>DIOR 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>The DIOR Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIOR 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
@@ -51910,12 +51910,12 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>DOLLY 20" X 20" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>DOLLY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>The DOLLY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DOLLY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
@@ -52056,12 +52056,12 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>DORA 17" X 17" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>DORA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>The DORA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DORA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -52202,12 +52202,12 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>DORA 21" X 21" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>DORA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>The DORA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DORA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -52348,12 +52348,12 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>ELSA 20" X 20" Pillow (2 CTN) in Beige | GOODDEGG</t>
+          <t>ELSA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>The ELSA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ELSA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -52500,12 +52500,12 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>EMMIE 20" X 20" Pillow Summer Time (2 CTN) in White Multi | GO</t>
+          <t>EMMIE 20" X 20" Pillow, Summer Time (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>The EMMIE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>EMMIE 20" X 20" Pillow, Summer Time (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -52641,12 +52641,12 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>FAWN 20" X 20" Pillow (2 CTN) in Sand | GOODDEGG</t>
+          <t>FAWN 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>The FAWN Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FAWN 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -52787,12 +52787,12 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>FIFI 18" X 18" Pillow (2 CTN) in Green | GOODDEGG</t>
+          <t>FIFI 18" X 18" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>The FIFI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIFI 18" X 18" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -52933,12 +52933,12 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>FIFI 22" X 22" Pillow (2 CTN) in Green | GOODDEGG</t>
+          <t>FIFI 22" X 22" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>The FIFI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>FIFI 22" X 22" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -53079,12 +53079,12 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>JANE 20" X 20" Pillow (2 CTN) in Gold | GOODDEGG</t>
+          <t>JANE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>The JANE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JANE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -53225,12 +53225,12 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>JET 20" X 20" Pillow (2 CTN) in Black | GOODDEGG</t>
+          <t>JET 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>The JET Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JET 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -53371,12 +53371,12 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>JILL 17" X 17" Pillow (2 CTN) in Yellow Multi | GOODDEGG</t>
+          <t>JILL 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>The JILL Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JILL 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -53517,12 +53517,12 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>JILL 21" X 21" Pillow (2 CTN) in Yellow Multi | GOODDEGG</t>
+          <t>JILL 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>The JILL Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JILL 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -53669,12 +53669,12 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>JODY 20" X 20" Pillow Crab (2 CTN) in White Blue | GOODDEGG</t>
+          <t>JODY 20" X 20" Pillow, Crab (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>The JODY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JODY 20" X 20" Pillow, Crab (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -53811,12 +53811,12 @@
       </c>
       <c r="H369" s="59" t="inlineStr">
         <is>
-          <t>JORJA 20" X 20" Pillow (2 CTN) in Beige Purple | GOODDEGG</t>
+          <t>JORJA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I369" s="59" t="inlineStr">
         <is>
-          <t>The JORJA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JORJA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J369" s="59" t="inlineStr">
@@ -53959,12 +53959,12 @@
       </c>
       <c r="H370" s="59" t="inlineStr">
         <is>
-          <t>JORJA 20" X 20" Pillow (2 CTN) in Purple | GOODDEGG</t>
+          <t>JORJA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I370" s="59" t="inlineStr">
         <is>
-          <t>The JORJA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JORJA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J370" s="59" t="inlineStr">
@@ -54106,12 +54106,12 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>JOY 20" X 20" Pillow (2 CTN) in Cream Gray | GOODDEGG</t>
+          <t>JOY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>The JOY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
@@ -54252,12 +54252,12 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>JUDE 20" X 20" Pillow (2 CTN) in White Blue | GOODDEGG</t>
+          <t>JUDE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>The JUDE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JUDE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
@@ -54399,12 +54399,12 @@
       </c>
       <c r="H373" s="30" t="inlineStr">
         <is>
-          <t>KARI 20" X 20" Pillow (2 CTN) in Dark Gray | GOODDEGG</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I373" s="30" t="inlineStr">
         <is>
-          <t>The KARI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J373" s="30" t="inlineStr">
@@ -54547,12 +54547,12 @@
       </c>
       <c r="H374" s="30" t="inlineStr">
         <is>
-          <t>KARI 20" X 20" Pillow (2 CTN) in Silver | GOODDEGG</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I374" s="30" t="inlineStr">
         <is>
-          <t>The KARI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J374" s="30" t="inlineStr">
@@ -54695,12 +54695,12 @@
       </c>
       <c r="H375" s="30" t="inlineStr">
         <is>
-          <t>KARI 20" X 20" Pillow (2 CTN) in Orange | GOODDEGG</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I375" s="30" t="inlineStr">
         <is>
-          <t>The KARI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J375" s="30" t="inlineStr">
@@ -54843,12 +54843,12 @@
       </c>
       <c r="H376" s="30" t="inlineStr">
         <is>
-          <t>KARI 20" X 20" Pillow (2 CTN) in Teal | GOODDEGG</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I376" s="30" t="inlineStr">
         <is>
-          <t>The KARI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KARI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J376" s="30" t="inlineStr">
@@ -54990,12 +54990,12 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>KARIN 20" X 20" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>KARIN 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>The KARIN Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KARIN 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -55136,12 +55136,12 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>KATIA 20" X 20" Pillow (2 CTN) in Beige Blue | GOODDEGG</t>
+          <t>KATIA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>The KATIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KATIA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -55282,12 +55282,12 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>KIMMY 20" X 20" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>KIMMY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>The KIMMY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KIMMY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -55428,12 +55428,12 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>KYLA 20" X 20" Pillow (2 CTN) in Purple | GOODDEGG</t>
+          <t>KYLA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>The KYLA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>KYLA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -55574,12 +55574,12 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>LALA 18" X 18" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>LALA 18" X 18" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>The LALA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALA 18" X 18" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -55720,12 +55720,12 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>LALA 22" X 22" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>LALA 22" X 22" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>The LALA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LALA 22" X 22" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -55866,12 +55866,12 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>LATI 20" X 20" Pillow (2 CTN) in Latte | GOODDEGG</t>
+          <t>LATI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>The LATI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LATI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -56013,12 +56013,12 @@
       </c>
       <c r="H384" s="54" t="inlineStr">
         <is>
-          <t>LEYLA 20" X 20" Pillow (2 CTN) in Silver | GOODDEGG</t>
+          <t>LEYLA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I384" s="54" t="inlineStr">
         <is>
-          <t>The LEYLA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEYLA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J384" s="54" t="inlineStr">
@@ -56161,12 +56161,12 @@
       </c>
       <c r="H385" s="54" t="inlineStr">
         <is>
-          <t>LEYLA 20" X 20" Pillow (2 CTN) in Green | GOODDEGG</t>
+          <t>LEYLA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I385" s="54" t="inlineStr">
         <is>
-          <t>The LEYLA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEYLA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J385" s="54" t="inlineStr">
@@ -56308,12 +56308,12 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>LILY 20" X 20" Pillow (2 CTN) in Beige Teal | GOODDEGG</t>
+          <t>LILY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>The LILY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LILY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -56455,12 +56455,12 @@
       </c>
       <c r="H387" s="32" t="inlineStr">
         <is>
-          <t>LINA 20" X 20" Pillow (2 CTN) in Ivory Pink | GOODDEGG</t>
+          <t>LINA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I387" s="32" t="inlineStr">
         <is>
-          <t>The LINA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LINA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J387" s="32" t="inlineStr">
@@ -56603,12 +56603,12 @@
       </c>
       <c r="H388" s="32" t="inlineStr">
         <is>
-          <t>LINA 20" X 20" Pillow (2 CTN) in Ivory Pink | GOODDEGG</t>
+          <t>LINA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I388" s="32" t="inlineStr">
         <is>
-          <t>The LINA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LINA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J388" s="32" t="inlineStr">
@@ -56750,12 +56750,12 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>LINDY 17" X 17" Pillow (2 CTN) in Purple | GOODDEGG</t>
+          <t>LINDY 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>The LINDY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LINDY 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
@@ -56896,12 +56896,12 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>LINDY 21" X 21" Pillow (2 CTN) in Purple | GOODDEGG</t>
+          <t>LINDY 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>The LINDY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LINDY 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -57043,12 +57043,12 @@
       </c>
       <c r="H391" s="39" t="inlineStr">
         <is>
-          <t>LORRIE 20" X 20" Pillow (2 CTN) in White Teal | GOODDEGG</t>
+          <t>LORRIE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I391" s="39" t="inlineStr">
         <is>
-          <t>The LORRIE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LORRIE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J391" s="39" t="inlineStr">
@@ -57191,12 +57191,12 @@
       </c>
       <c r="H392" s="39" t="inlineStr">
         <is>
-          <t>LORRIE 20" X 20" Pillow (2 CTN) in White Blue | GOODDEGG</t>
+          <t>LORRIE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I392" s="39" t="inlineStr">
         <is>
-          <t>The LORRIE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LORRIE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J392" s="39" t="inlineStr">
@@ -57338,12 +57338,12 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>LUCY 20" X 20" Pillow (2 CTN) in Latte | GOODDEGG</t>
+          <t>LUCY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>The LUCY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUCY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -57484,12 +57484,12 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>LULU 18" X 18" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>LULU 18" X 18" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>The LULU Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LULU 18" X 18" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -57630,12 +57630,12 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>LULU 22" X 22" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>LULU 22" X 22" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>The LULU Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LULU 22" X 22" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -57776,12 +57776,12 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>MACIE 20" X 20" Pillow (2 CTN) in Silver Gray | GOODDEGG</t>
+          <t>MACIE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>The MACIE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACIE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -57922,12 +57922,12 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>MACY 20" X 20" Pillow (2 CTN) in Beige | GOODDEGG</t>
+          <t>MACY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>The MACY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MACY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -58069,12 +58069,12 @@
       </c>
       <c r="H398" s="48" t="inlineStr">
         <is>
-          <t>MALIA 17" X 17" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>MALIA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I398" s="48" t="inlineStr">
         <is>
-          <t>The MALIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J398" s="48" t="inlineStr">
@@ -58217,12 +58217,12 @@
       </c>
       <c r="H399" s="48" t="inlineStr">
         <is>
-          <t>MALIA 17" X 17" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>MALIA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I399" s="48" t="inlineStr">
         <is>
-          <t>The MALIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J399" s="48" t="inlineStr">
@@ -58365,12 +58365,12 @@
       </c>
       <c r="H400" s="48" t="inlineStr">
         <is>
-          <t>MALIA 17" X 17" Pillow (2 CTN) in Yellow | GOODDEGG</t>
+          <t>MALIA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I400" s="48" t="inlineStr">
         <is>
-          <t>The MALIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J400" s="48" t="inlineStr">
@@ -58513,12 +58513,12 @@
       </c>
       <c r="H401" s="64" t="inlineStr">
         <is>
-          <t>MALIA 21" X 21" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>MALIA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I401" s="64" t="inlineStr">
         <is>
-          <t>The MALIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J401" s="64" t="inlineStr">
@@ -58661,12 +58661,12 @@
       </c>
       <c r="H402" s="64" t="inlineStr">
         <is>
-          <t>MALIA 21" X 21" Pillow (2 CTN) in Red | GOODDEGG</t>
+          <t>MALIA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I402" s="64" t="inlineStr">
         <is>
-          <t>The MALIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J402" s="64" t="inlineStr">
@@ -58809,12 +58809,12 @@
       </c>
       <c r="H403" s="64" t="inlineStr">
         <is>
-          <t>MALIA 21" X 21" Pillow (2 CTN) in Yellow | GOODDEGG</t>
+          <t>MALIA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I403" s="64" t="inlineStr">
         <is>
-          <t>The MALIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MALIA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J403" s="64" t="inlineStr">
@@ -58962,12 +58962,12 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>MAURA 20" X 20" Pillow Octopus (2 CTN) in White Blue | GOODDEG</t>
+          <t>MAURA 20" X 20" Pillow, Octopus (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>The MAURA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAURA 20" X 20" Pillow, Octopus (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -59103,12 +59103,12 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>MAY 20" X 20" Pillow (2 CTN) in Teal | GOODDEGG</t>
+          <t>MAY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>The MAY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MAY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -59249,12 +59249,12 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>NANA 20" X 20" Pillow (2 CTN) in Dark Gray | GOODDEGG</t>
+          <t>NANA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>The NANA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NANA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -59395,12 +59395,12 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>OLIVE 17" X 17" Pillow (2 CTN) in Brown | GOODDEGG</t>
+          <t>OLIVE 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>The OLIVE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVE 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -59541,12 +59541,12 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>OLIVE 21" X 21" Pillow (2 CTN) in Brown | GOODDEGG</t>
+          <t>OLIVE 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>The OLIVE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>OLIVE 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -59687,12 +59687,12 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>ORGON 20" X 20" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>ORGON 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>The ORGON Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ORGON 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -59828,12 +59828,12 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>PAM 20" X 20" Pillow (2 CTN) in Ivory Yellow | GOODDEGG</t>
+          <t>PAM 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>The PAM Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PAM 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -59975,12 +59975,12 @@
       </c>
       <c r="H411" s="25" t="inlineStr">
         <is>
-          <t>RICKI 17" X 17" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>RICKI 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I411" s="25" t="inlineStr">
         <is>
-          <t>The RICKI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RICKI 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J411" s="25" t="inlineStr">
@@ -60123,12 +60123,12 @@
       </c>
       <c r="H412" s="25" t="inlineStr">
         <is>
-          <t>RICKI 17" X 17" Pillow (2 CTN) in Brown | GOODDEGG</t>
+          <t>RICKI 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I412" s="25" t="inlineStr">
         <is>
-          <t>The RICKI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RICKI 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J412" s="25" t="inlineStr">
@@ -60271,12 +60271,12 @@
       </c>
       <c r="H413" s="32" t="inlineStr">
         <is>
-          <t>RICKI 21" X 21" Pillow (2 CTN) in Blue | GOODDEGG</t>
+          <t>RICKI 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I413" s="32" t="inlineStr">
         <is>
-          <t>The RICKI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RICKI 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J413" s="32" t="inlineStr">
@@ -60419,12 +60419,12 @@
       </c>
       <c r="H414" s="32" t="inlineStr">
         <is>
-          <t>RICKI 21" X 21" Pillow (2 CTN) in Brown | GOODDEGG</t>
+          <t>RICKI 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I414" s="32" t="inlineStr">
         <is>
-          <t>The RICKI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RICKI 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J414" s="32" t="inlineStr">
@@ -60567,12 +60567,12 @@
       </c>
       <c r="H415" s="68" t="inlineStr">
         <is>
-          <t>RINA 20" X 20" Pillow (2 CTN) in Light Pink | GOODDEGG</t>
+          <t>RINA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I415" s="68" t="inlineStr">
         <is>
-          <t>The RINA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RINA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J415" s="68" t="inlineStr">
@@ -60715,12 +60715,12 @@
       </c>
       <c r="H416" s="68" t="inlineStr">
         <is>
-          <t>RINA 20" X 20" Pillow (2 CTN) in Beige | GOODDEGG</t>
+          <t>RINA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I416" s="68" t="inlineStr">
         <is>
-          <t>The RINA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RINA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J416" s="68" t="inlineStr">
@@ -60863,12 +60863,12 @@
       </c>
       <c r="H417" s="68" t="inlineStr">
         <is>
-          <t>RINA 20" X 20" Pillow (2 CTN) in Purple | GOODDEGG</t>
+          <t>RINA 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I417" s="68" t="inlineStr">
         <is>
-          <t>The RINA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>RINA 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J417" s="68" t="inlineStr">
@@ -61010,12 +61010,12 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>SALLY 20" X 20" Pillow (2 CTN) in Teal | GOODDEGG</t>
+          <t>SALLY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>The SALLY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SALLY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -61156,12 +61156,12 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>SAM 20" X 20" Pillow (2 CTN) in Silver Gold | GOODDEGG</t>
+          <t>SAM 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>The SAM Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SAM 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -61302,12 +61302,12 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>SHARY 20" X 20" Pillow (2 CTN) in Silver | GOODDEGG</t>
+          <t>SHARY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>The SHARY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHARY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -61448,12 +61448,12 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>SHERI 20" X 20" Pillow (2 CTN) in White | GOODDEGG</t>
+          <t>SHERI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>The SHERI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHERI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
@@ -61594,12 +61594,12 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>SIERRA 17" X 17" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>SIERRA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>The SIERRA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIERRA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
@@ -61735,12 +61735,12 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>SIERRA 21" X 21" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>SIERRA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>The SIERRA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SIERRA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -61876,12 +61876,12 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>SNOW 20" X 20" Pillow (2 CTN) in Silver | GOODDEGG</t>
+          <t>SNOW 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>The SNOW Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SNOW 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -62022,12 +62022,12 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>TANIA 17" X 17" Pillow (2 CTN) in Brown Multi | GOODDEGG</t>
+          <t>TANIA 17" X 17" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>The TANIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANIA 17" X 17" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -62168,12 +62168,12 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>TANIA 21" X 21" Pillow (2 CTN) in Brown Multi | GOODDEGG</t>
+          <t>TANIA 21" X 21" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>The TANIA Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TANIA 21" X 21" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -62314,12 +62314,12 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>TERI 20" X 20" Pillow (2 CTN) in Beige Indigo | GOODDEGG</t>
+          <t>TERI 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>The TERI Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TERI 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -62460,12 +62460,12 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>TERRIE 20" X 20" Pillow (2 CTN) in Teal | GOODDEGG</t>
+          <t>TERRIE 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>The TERRIE Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TERRIE 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -62606,12 +62606,12 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>TEXIS 20" X 20" Pillow (2 CTN) in Multi | GOODDEGG</t>
+          <t>TEXIS 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>The TEXIS Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TEXIS 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -62748,12 +62748,12 @@
       </c>
       <c r="H430" s="25" t="inlineStr">
         <is>
-          <t>TRUDY 20" X 20" Pillow (2 CTN) in Beige | GOODDEGG</t>
+          <t>TRUDY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I430" s="25" t="inlineStr">
         <is>
-          <t>The TRUDY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRUDY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J430" s="25" t="inlineStr">
@@ -62896,12 +62896,12 @@
       </c>
       <c r="H431" s="25" t="inlineStr">
         <is>
-          <t>TRUDY 20" X 20" Pillow (2 CTN) in Gray | GOODDEGG</t>
+          <t>TRUDY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I431" s="25" t="inlineStr">
         <is>
-          <t>The TRUDY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRUDY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J431" s="25" t="inlineStr">
@@ -63044,12 +63044,12 @@
       </c>
       <c r="H432" s="25" t="inlineStr">
         <is>
-          <t>TRUDY 20" X 20" Pillow (2 CTN) in Silver | GOODDEGG</t>
+          <t>TRUDY 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I432" s="25" t="inlineStr">
         <is>
-          <t>The TRUDY Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRUDY 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J432" s="25" t="inlineStr">
@@ -63191,12 +63191,12 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Washton 20" X 20" Pillow (2 ctn) in Multi | GOODDEGG</t>
+          <t>WASHTON 20" X 20" Pillow (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>The WASHTON Pillow brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>WASHTON 20" X 20" Pillow (2 / CTN) supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -63335,12 +63335,12 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>APHRODITE Vanity Set in White | GOODDEGG</t>
+          <t>APHRODITE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>The APHRODITE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>APHRODITE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -63474,12 +63474,12 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>ASHBOURNE Vanity Set w/ Stool in Black | GOODDEGG</t>
+          <t>ASHBOURNE Vanity Set w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>The ASHBOURNE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ASHBOURNE Vanity Set w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -63611,12 +63611,12 @@
       </c>
       <c r="H436" s="64" t="inlineStr">
         <is>
-          <t>ATHY Vanity w/ Stool in Silver | GOODDEGG</t>
+          <t>ATHY Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I436" s="64" t="inlineStr">
         <is>
-          <t>The ATHY Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ATHY Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J436" s="64" t="inlineStr">
@@ -63757,12 +63757,12 @@
       </c>
       <c r="H437" s="64" t="inlineStr">
         <is>
-          <t>ATHY Vanity w/ Stool in White | GOODDEGG</t>
+          <t>ATHY Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I437" s="64" t="inlineStr">
         <is>
-          <t>The ATHY Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ATHY Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J437" s="64" t="inlineStr">
@@ -63903,12 +63903,12 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>CLARISSE Vanity w/ Stool in Silver | GOODDEGG</t>
+          <t>CLARISSE Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>The CLARISSE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CLARISSE Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -64046,12 +64046,12 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>CLEBURNE Vanity Set w/ Stool in Light Gray | GOODDEGG</t>
+          <t>CLEBURNE Vanity Set w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>The CLEBURNE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CLEBURNE Vanity Set w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -64186,12 +64186,12 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>HARRIET Vanity w/ Stool in Silver | GOODDEGG</t>
+          <t>HARRIET Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>The HARRIET Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HARRIET Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -64329,12 +64329,12 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>HAZELINE Vanity Set w/ Stool in White | GOODDEGG</t>
+          <t>HAZELINE Vanity Set w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>The HAZELINE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HAZELINE Vanity Set w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -64469,12 +64469,12 @@
       </c>
       <c r="H442" s="51" t="inlineStr">
         <is>
-          <t>JOYCE Vanity w/ Stool in Silver | GOODDEGG</t>
+          <t>JOYCE Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I442" s="51" t="inlineStr">
         <is>
-          <t>The JOYCE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOYCE Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J442" s="51" t="inlineStr">
@@ -64615,12 +64615,12 @@
       </c>
       <c r="H443" s="51" t="inlineStr">
         <is>
-          <t>JOYCE Vanity w/ Stool in White | GOODDEGG</t>
+          <t>JOYCE Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I443" s="51" t="inlineStr">
         <is>
-          <t>The JOYCE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>JOYCE Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J443" s="51" t="inlineStr">
@@ -64759,12 +64759,12 @@
       </c>
       <c r="H444" s="68" t="inlineStr">
         <is>
-          <t>LISMORE Vanity w/ Stool in Champagne | GOODDEGG</t>
+          <t>LISMORE Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I444" s="68" t="inlineStr">
         <is>
-          <t>The LISMORE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LISMORE Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J444" s="68" t="inlineStr">
@@ -64903,12 +64903,12 @@
       </c>
       <c r="H445" s="68" t="inlineStr">
         <is>
-          <t>LISMORE Vanity w/ Stool in Chrome | GOODDEGG</t>
+          <t>LISMORE Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I445" s="68" t="inlineStr">
         <is>
-          <t>The LISMORE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LISMORE Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J445" s="68" t="inlineStr">
@@ -65048,12 +65048,12 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>LOUISE Vanity w/ Stool in White | GOODDEGG</t>
+          <t>LOUISE Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>The LOUISE Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LOUISE Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -65187,12 +65187,12 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>MADONNA Vanity Set in White Black | GOODDEGG</t>
+          <t>MADONNA Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>The MADONNA Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MADONNA Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -65329,12 +65329,12 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>MARGRET Vanity Set in White Gray | GOODDEGG</t>
+          <t>MARGRET Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>The MARGRET Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MARGRET Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -65470,12 +65470,12 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>STELLA MIA Vanity Set w/ Stool in Creamy White | GOODDEGG</t>
+          <t>STELLA MIA Vanity Set w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>The STELLA MIA Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STELLA MIA Vanity Set w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -65611,12 +65611,12 @@
       </c>
       <c r="H450" s="59" t="inlineStr">
         <is>
-          <t>STEPHANIE Vanity Set in Obsidian Gray | GOODDEGG</t>
+          <t>STEPHANIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I450" s="59" t="inlineStr">
         <is>
-          <t>The STEPHANIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STEPHANIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J450" s="59" t="inlineStr">
@@ -65760,12 +65760,12 @@
       </c>
       <c r="H451" s="59" t="inlineStr">
         <is>
-          <t>STEPHANIE Vanity Set in Luminous White | GOODDEGG</t>
+          <t>STEPHANIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I451" s="59" t="inlineStr">
         <is>
-          <t>The STEPHANIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STEPHANIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J451" s="59" t="inlineStr">
@@ -65908,12 +65908,12 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>STOHOLM Vanity Set in White | GOODDEGG</t>
+          <t>STOHOLM Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
         <is>
-          <t>The STOHOLM Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STOHOLM Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -66049,12 +66049,12 @@
       </c>
       <c r="H453" s="36" t="inlineStr">
         <is>
-          <t>TRACIE Vanity Set in Obsidian Gray | GOODDEGG</t>
+          <t>TRACIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I453" s="36" t="inlineStr">
         <is>
-          <t>The TRACIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRACIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J453" s="36" t="inlineStr">
@@ -66194,12 +66194,12 @@
       </c>
       <c r="H454" s="36" t="inlineStr">
         <is>
-          <t>TRACIE Vanity Set in Tiffany Blush | GOODDEGG</t>
+          <t>TRACIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I454" s="36" t="inlineStr">
         <is>
-          <t>The TRACIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRACIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J454" s="36" t="inlineStr">
@@ -66339,12 +66339,12 @@
       </c>
       <c r="H455" s="36" t="inlineStr">
         <is>
-          <t>TRACIE Vanity Set in Luminous White | GOODDEGG</t>
+          <t>TRACIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I455" s="36" t="inlineStr">
         <is>
-          <t>The TRACIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRACIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J455" s="36" t="inlineStr">
@@ -66483,12 +66483,12 @@
       </c>
       <c r="H456" s="54" t="inlineStr">
         <is>
-          <t>TRACY Vanity w/ Stool in Rose Gold | GOODDEGG</t>
+          <t>TRACY Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I456" s="54" t="inlineStr">
         <is>
-          <t>The TRACY Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRACY Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J456" s="54" t="inlineStr">
@@ -66633,12 +66633,12 @@
       </c>
       <c r="H457" s="54" t="inlineStr">
         <is>
-          <t>TRACY Vanity w/ Stool in Silver | GOODDEGG</t>
+          <t>TRACY Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I457" s="54" t="inlineStr">
         <is>
-          <t>The TRACY Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRACY Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J457" s="54" t="inlineStr">
@@ -66779,12 +66779,12 @@
       </c>
       <c r="H458" s="54" t="inlineStr">
         <is>
-          <t>TRACY Vanity w/ Stool in White | GOODDEGG</t>
+          <t>TRACY Vanity w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I458" s="54" t="inlineStr">
         <is>
-          <t>The TRACY Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TRACY Vanity w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J458" s="54" t="inlineStr">
@@ -66926,12 +66926,12 @@
       </c>
       <c r="H459" s="32" t="inlineStr">
         <is>
-          <t>VALENTINA Vanity Set in Obsidian Gray | GOODDEGG</t>
+          <t>VALENTINA Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I459" s="32" t="inlineStr">
         <is>
-          <t>The VALENTINA Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALENTINA Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J459" s="32" t="inlineStr">
@@ -67075,12 +67075,12 @@
       </c>
       <c r="H460" s="32" t="inlineStr">
         <is>
-          <t>VALENTINA Vanity Set in Luminous White | GOODDEGG</t>
+          <t>VALENTINA Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I460" s="32" t="inlineStr">
         <is>
-          <t>The VALENTINA Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALENTINA Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J460" s="32" t="inlineStr">
@@ -67223,12 +67223,12 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>VENTNOR Vanity Set w/ Stool in Gray | GOODDEGG</t>
+          <t>VENTNOR Vanity Set w/ Stool | GOODDEGG</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>The VENTNOR Vanity w/ Stool brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VENTNOR Vanity Set w/ Stool supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -67364,12 +67364,12 @@
       </c>
       <c r="H462" s="45" t="inlineStr">
         <is>
-          <t>VICKIE Vanity Set in Obsidian Gray | GOODDEGG</t>
+          <t>VICKIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I462" s="45" t="inlineStr">
         <is>
-          <t>The VICKIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VICKIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J462" s="45" t="inlineStr">
@@ -67513,12 +67513,12 @@
       </c>
       <c r="H463" s="45" t="inlineStr">
         <is>
-          <t>VICKIE Vanity Set in Luminous White | GOODDEGG</t>
+          <t>VICKIE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I463" s="45" t="inlineStr">
         <is>
-          <t>The VICKIE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VICKIE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J463" s="45" t="inlineStr">
@@ -67662,12 +67662,12 @@
       </c>
       <c r="H464" s="66" t="inlineStr">
         <is>
-          <t>YASMINE Vanity Set in Tiffany Blush | GOODDEGG</t>
+          <t>YASMINE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I464" s="66" t="inlineStr">
         <is>
-          <t>The YASMINE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YASMINE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J464" s="66" t="inlineStr">
@@ -67811,12 +67811,12 @@
       </c>
       <c r="H465" s="66" t="inlineStr">
         <is>
-          <t>YASMINE Vanity Set in Luminous White | GOODDEGG</t>
+          <t>YASMINE Vanity Set | GOODDEGG</t>
         </is>
       </c>
       <c r="I465" s="66" t="inlineStr">
         <is>
-          <t>The YASMINE Vanity brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>YASMINE Vanity Set supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J465" s="66" t="inlineStr">
@@ -67956,12 +67956,12 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>ARGON Office Chair in Black Silver Red | GOODDEGG</t>
+          <t>ARGON Office Chair | GOODDEGG</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>The ARGON Office Chair adds comfortable seating and style to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ARGON Office Chair supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -68098,12 +68098,12 @@
       </c>
       <c r="H467" s="32" t="inlineStr">
         <is>
-          <t>CAPARICA Throw Blanket in Gold | GOODDEGG</t>
+          <t>CAPARICA Throw Blanket | GOODDEGG</t>
         </is>
       </c>
       <c r="I467" s="32" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw Blanket brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Blanket supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J467" s="32" t="inlineStr">
@@ -68242,12 +68242,12 @@
       </c>
       <c r="H468" s="32" t="inlineStr">
         <is>
-          <t>CAPARICA Throw Blanket in Teal | GOODDEGG</t>
+          <t>CAPARICA Throw Blanket | GOODDEGG</t>
         </is>
       </c>
       <c r="I468" s="32" t="inlineStr">
         <is>
-          <t>The CAPARICA Throw Blanket brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CAPARICA Throw Blanket supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J468" s="32" t="inlineStr">
@@ -68387,12 +68387,12 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>CATALIA Book Stand in Dark Oak Espresso | GOODDEGG</t>
+          <t>CATALIA Book Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>The CATALIA Book Stand organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>CATALIA Book Stand Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -68531,12 +68531,12 @@
       </c>
       <c r="H470" s="45" t="inlineStr">
         <is>
-          <t>DELLA Shoe Cabinet in Oak | GOODDEGG</t>
+          <t>DELLA Shoe Cabinet | GOODDEGG</t>
         </is>
       </c>
       <c r="I470" s="45" t="inlineStr">
         <is>
-          <t>The DELLA Shoe Cabinet organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DELLA Shoe Cabinet Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J470" s="45" t="inlineStr">
@@ -68681,12 +68681,12 @@
       </c>
       <c r="H471" s="45" t="inlineStr">
         <is>
-          <t>DELLA Shoe Cabinet in Espresso | GOODDEGG</t>
+          <t>DELLA Shoe Cabinet | GOODDEGG</t>
         </is>
       </c>
       <c r="I471" s="45" t="inlineStr">
         <is>
-          <t>The DELLA Shoe Cabinet organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DELLA Shoe Cabinet Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J471" s="45" t="inlineStr">
@@ -68826,12 +68826,12 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>DESREE Accent Chest in Multi Antique Walnut | GOODDEGG</t>
+          <t>DESREE Accent Chest | GOODDEGG</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>The DESREE Accent Chest organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DESREE Accent Chest Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -68967,12 +68967,12 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>DIPILOH Bookcase in Black Distressed Dark Oak | GOODDEGG</t>
+          <t>DIPILOH Bookcase | GOODDEGG</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>The DIPILOH Bookcase organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DIPILOH Bookcase Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -69106,12 +69106,12 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>LUGO Ladder Shelf in Antique Oak | GOODDEGG</t>
+          <t>LUGO Ladder Shelf | GOODDEGG</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>The LUGO Ladder Shelf organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUGO Ladder Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -69250,12 +69250,12 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>NECHE Accent Chest in Multi Antique Walnut | GOODDEGG</t>
+          <t>NECHE Accent Chest | GOODDEGG</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
-          <t>The NECHE Accent Chest organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>NECHE Accent Chest Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -69393,12 +69393,12 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>VALENCIA I Media Shelf in Antique Oak | GOODDEGG</t>
+          <t>VALENCIA I Media Shelf | GOODDEGG</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>The VALENCIA I Media Shelf organizes and displays your essentials with ease. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VALENCIA I Media Shelf supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -69536,12 +69536,12 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>DEERING Side Table in White | GOODDEGG</t>
+          <t>DEERING Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
-          <t>The DEERING Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DEERING Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -69677,12 +69677,12 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>DUNDALK Side Table in Oak Multi | GOODDEGG</t>
+          <t>DUNDALK Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
         <is>
-          <t>The DUNDALK Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DUNDALK Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -69821,12 +69821,12 @@
       </c>
       <c r="H479" s="25" t="inlineStr">
         <is>
-          <t>LILITH I Side Table w/ USB in Cherry | GOODDEGG</t>
+          <t>LILITH I Side Table w/ USB | GOODDEGG</t>
         </is>
       </c>
       <c r="I479" s="25" t="inlineStr">
         <is>
-          <t>The LILITH I Side Table w/ USB creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LILITH I Side Table w/ USB supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J479" s="25" t="inlineStr">
@@ -69967,12 +69967,12 @@
       </c>
       <c r="H480" s="25" t="inlineStr">
         <is>
-          <t>LILITH I Side Table w/ USB in Gray | GOODDEGG</t>
+          <t>LILITH I Side Table w/ USB | GOODDEGG</t>
         </is>
       </c>
       <c r="I480" s="25" t="inlineStr">
         <is>
-          <t>The LILITH I Side Table w/ USB creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LILITH I Side Table w/ USB supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J480" s="25" t="inlineStr">
@@ -70112,12 +70112,12 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>MENTON Side Table in Antique Gray | GOODDEGG</t>
+          <t>MENTON Side Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
         <is>
-          <t>The MENTON Side Table creates a welcoming place for meals and gatherings. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MENTON Side Table supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -70253,12 +70253,12 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>DORRIT 55" Electric Fireplace in White | GOODDEGG</t>
+          <t>DORRIT 55" Electric Fireplace | GOODDEGG</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
         <is>
-          <t>The DORRIT Electric Fireplace brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>DORRIT 55" Electric Fireplace TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
@@ -70394,12 +70394,12 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>LUKEN 71" TV Stand w/ Electric Fireplace in White | GOODDEGG</t>
+          <t>LUKEN 71" TV Stand w/ Electric Fireplace | GOODDEGG</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>LUKEN TV Stand w/ Electric Fireplace brings everyday comfort and function to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LUKEN 71" TV Stand w/ Electric Fireplace supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -70535,12 +70535,12 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>MEDEA 71" TV Stand w/ Electric Fireplace in White | GOODDEGG</t>
+          <t>MEDEA 71" TV Stand w/ Electric Fireplace | GOODDEGG</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
         <is>
-          <t>MEDEA TV Stand w/ Electric Fireplace brings everyday comfort and function to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>MEDEA 71" TV Stand w/ Electric Fireplace supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -70676,12 +70676,12 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>PESEUX 71" TV Stand w/ Electric Fireplace in White | GOODDEGG</t>
+          <t>PESEUX 71" TV Stand w/ Electric Fireplace | GOODDEGG</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
         <is>
-          <t>PESEUX TV Stand w/ Electric Fireplace brings everyday comfort and function to your. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PESEUX 71" TV Stand w/ Electric Fireplace supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -70817,12 +70817,12 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>ESTELLE Bowl w/ Spheres (2 CTN) in Champagne | GOODDEGG</t>
+          <t>ESTELLE Bowl w/ Spheres (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>The ESTELLE Bowl w/ Spheres brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ESTELLE Bowl w/ Spheres (2 / CTN) Recreation supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -70958,12 +70958,12 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>ESTELLE Candle Holder Set (4 CTN) in Champagne | GOODDEGG</t>
+          <t>ESTELLE Candle Holder Set (4/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>The ESTELLE Candle Holder brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ESTELLE Candle Holder Set (4/CTN) Recreation supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
@@ -71099,12 +71099,12 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>ESTELLE Decorative Piece (4 CTN) in Champagne | GOODDEGG</t>
+          <t>ESTELLE Decorative Piece (4/CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>The ESTELLE Decorative brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ESTELLE Decorative Piece (4/CTN) Recreation supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -71240,12 +71240,12 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>ESTELLE Decorative Vase (2 CTN) in Champagne | GOODDEGG</t>
+          <t>ESTELLE Decorative Vase (2 / CTN) | GOODDEGG</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>The ESTELLE Decorative Vase brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>ESTELLE Decorative Vase (2 / CTN) Recreation supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -71382,12 +71382,12 @@
       </c>
       <c r="H490" s="42" t="inlineStr">
         <is>
-          <t>GRAINNE Storage Bench in Green | GOODDEGG</t>
+          <t>GRAINNE Storage Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I490" s="42" t="inlineStr">
         <is>
-          <t>The GRAINNE Storage Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRAINNE Storage Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J490" s="42" t="inlineStr">
@@ -71526,12 +71526,12 @@
       </c>
       <c r="H491" s="42" t="inlineStr">
         <is>
-          <t>GRAINNE Storage Bench in White | GOODDEGG</t>
+          <t>GRAINNE Storage Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I491" s="42" t="inlineStr">
         <is>
-          <t>The GRAINNE Storage Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>GRAINNE Storage Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J491" s="42" t="inlineStr">
@@ -71669,12 +71669,12 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>LAKEPORT Storage Chaise in Black | GOODDEGG</t>
+          <t>LAKEPORT Storage Chaise | GOODDEGG</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>The LAKEPORT Storage Chaise adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAKEPORT Storage Chaise Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
@@ -71812,12 +71812,12 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Stella Mia Bench in Creamy White | GOODDEGG</t>
+          <t>STELLA MIA Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>The STELLA MIA Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STELLA MIA Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J493" t="inlineStr">
@@ -71956,12 +71956,12 @@
       </c>
       <c r="H494" s="30" t="inlineStr">
         <is>
-          <t>TAYAH Bench in Beige | GOODDEGG</t>
+          <t>TAYAH Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I494" s="30" t="inlineStr">
         <is>
-          <t>The TAYAH Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TAYAH Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J494" s="30" t="inlineStr">
@@ -72102,12 +72102,12 @@
       </c>
       <c r="H495" s="30" t="inlineStr">
         <is>
-          <t>TAYAH Bench in Gray | GOODDEGG</t>
+          <t>TAYAH Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I495" s="30" t="inlineStr">
         <is>
-          <t>The TAYAH Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TAYAH Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J495" s="30" t="inlineStr">
@@ -72248,12 +72248,12 @@
       </c>
       <c r="H496" s="30" t="inlineStr">
         <is>
-          <t>TAYAH Bench in Beige | GOODDEGG</t>
+          <t>TAYAH Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I496" s="30" t="inlineStr">
         <is>
-          <t>The TAYAH Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TAYAH Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J496" s="30" t="inlineStr">
@@ -72394,12 +72394,12 @@
       </c>
       <c r="H497" s="30" t="inlineStr">
         <is>
-          <t>TAYAH Bench in Gray | GOODDEGG</t>
+          <t>TAYAH Bench | GOODDEGG</t>
         </is>
       </c>
       <c r="I497" s="30" t="inlineStr">
         <is>
-          <t>The TAYAH Bench adds flexible seating where you need it most. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>TAYAH Bench supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J497" s="30" t="inlineStr">
@@ -72538,12 +72538,12 @@
       </c>
       <c r="H498" s="68" t="inlineStr">
         <is>
-          <t>HOMILI Last Supper Plaque in Multi | GOODDEGG</t>
+          <t>HOMILI Last Supper Plaque | GOODDEGG</t>
         </is>
       </c>
       <c r="I498" s="68" t="inlineStr">
         <is>
-          <t>The HOMILI Last Supper Plaque brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOMILI Last Supper Plaque Wall Art supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J498" s="68" t="inlineStr">
@@ -72682,12 +72682,12 @@
       </c>
       <c r="H499" s="68" t="inlineStr">
         <is>
-          <t>HOMILI Last Supper Plaque in Multi | GOODDEGG</t>
+          <t>HOMILI Last Supper Plaque | GOODDEGG</t>
         </is>
       </c>
       <c r="I499" s="68" t="inlineStr">
         <is>
-          <t>The HOMILI Last Supper Plaque brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>HOMILI Last Supper Plaque Wall Art supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J499" s="68" t="inlineStr">
@@ -72827,12 +72827,12 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>LAUNCES Storage Chest in Solid Wood, Wood Veneer, Others | GOODDEGG</t>
+          <t>LAUNCES Storage Chest | GOODDEGG</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>The LAUNCES Storage Chest brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LAUNCES Storage Chest Cabinet supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
@@ -72973,12 +72973,12 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>LEOVANNI Curio in Dark Brown | GOODDEGG</t>
+          <t>LEOVANNI Curio | GOODDEGG</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>The LEOVANNI Curio brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>LEOVANNI Curio supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
@@ -73113,12 +73113,12 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>PROMENADE Curio Cabinet in Dark Brown | GOODDEGG</t>
+          <t>PROMENADE Curio Cabinet | GOODDEGG</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>The PROMENADE Curio Cabinet brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>PROMENADE Curio Cabinet supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
@@ -73257,12 +73257,12 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>STELLA MIA Curio Cabinet in Ivory | GOODDEGG</t>
+          <t>STELLA MIA Curio Cabinet | GOODDEGG</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>The STELLA MIA Curio Cabinet brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>STELLA MIA Curio Cabinet supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -73398,12 +73398,12 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>SCEPTRUM Fireplace TV Stand in Silver | GOODDEGG</t>
+          <t>SCEPTRUM Fireplace / TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>The SCEPTRUM Fireplace or TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SCEPTRUM Fireplace / TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
@@ -73539,12 +73539,12 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>SEGINUS Fireplace TV Stand in Silver | GOODDEGG</t>
+          <t>SEGINUS Fireplace / TV Stand | GOODDEGG</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>The SEGINUS Fireplace or TV Stand brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SEGINUS Fireplace / TV Stand supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -73680,12 +73680,12 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>SHERBROOKE Sofa Table in Gold | GOODDEGG</t>
+          <t>SHERBROOKE Sofa Table | GOODDEGG</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>The SHERBROOKE Sofa Table brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>SHERBROOKE Sofa Table Hallway supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J506" t="inlineStr">
@@ -73823,12 +73823,12 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>VAUGH Ottoman in Rustic Brown | GOODDEGG</t>
+          <t>VAUGH Ottoman | GOODDEGG</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>The VAUGH Ottoman brings everyday comfort and function to your space. Shop at GOODDEGG for a great selection and guaranteed lowest prices.</t>
+          <t>VAUGH Ottoman supports deeper, more comfortable sleep night after night. Shop at GOODDEGG for great selection and low prices.</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">

--- a/FOA Singles/Accent-Single.xlsx
+++ b/FOA Singles/Accent-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/FOA Singles/Accent-Single.xlsx
+++ b/FOA Singles/Accent-Single.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
